--- a/progression_validation/freshman_senior_progression_summary.xlsx
+++ b/progression_validation/freshman_senior_progression_summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/28edc9c7244f203a/StX_XC_Track/track_report_site/reports_simple/progression_validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{FD0781AF-2203-462A-BB5A-3D7DB617690B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{521ACF55-A37F-4488-B400-A51A3C08C192}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{FD0781AF-2203-462A-BB5A-3D7DB617690B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDFE6B49-5C5A-4758-A094-D6E2E21EABB0}"/>
   <bookViews>
     <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D50CECB0-75FC-479B-95E7-BB327A7E9C00}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="51" r:id="rId3"/>
+    <pivotCache cacheId="9" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="223">
   <si>
     <t>competitor_name</t>
   </si>
@@ -379,9 +379,6 @@
     <t>Levi Thornton</t>
   </si>
   <si>
-    <t>13.120000000000005</t>
-  </si>
-  <si>
     <t>Matthew Meirose</t>
   </si>
   <si>
@@ -430,9 +427,6 @@
     <t>Quenton Horton</t>
   </si>
   <si>
-    <t>2.570999999999998</t>
-  </si>
-  <si>
     <t>Owen Mayes</t>
   </si>
   <si>
@@ -442,9 +436,6 @@
     <t>Bobby Poston</t>
   </si>
   <si>
-    <t>1.5519999999999925</t>
-  </si>
-  <si>
     <t>Jimmy Greer</t>
   </si>
   <si>
@@ -698,6 +689,18 @@
   </si>
   <si>
     <t>Sum of freshman_sort</t>
+  </si>
+  <si>
+    <t>15.180000000000007</t>
+  </si>
+  <si>
+    <t>4.2309999999999945</t>
+  </si>
+  <si>
+    <t>7.7479999999999905</t>
+  </si>
+  <si>
+    <t>3.3160000000000025</t>
   </si>
 </sst>
 </file>
@@ -1239,169 +1242,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="66">
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m\.ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m\.ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m\.ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m\.ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m\.ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m\.ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m\.ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m\.ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m\.ss"/>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <numFmt numFmtId="28" formatCode="mm:ss"/>
     </dxf>
@@ -1452,7 +1293,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Bob" refreshedDate="46151.76582291667" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="242" xr:uid="{BFECE650-F83A-48EC-BE10-3B521D634170}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Bob" refreshedDate="46151.79671516204" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="242" xr:uid="{BFECE650-F83A-48EC-BE10-3B521D634170}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:T1048576" sheet="Raw_data"/>
   </cacheSource>
@@ -1512,13 +1353,13 @@
         <s v="Ray Laracy"/>
         <s v="Leo Falk"/>
         <s v="Nathan Worley"/>
+        <s v="Owen Mattingly"/>
         <s v="Ben Lewis"/>
         <s v="Owen Derrick"/>
         <s v="Thomas Dusza"/>
         <s v="Henry Metzger"/>
         <s v="Andrew Reed"/>
         <s v="John Hagedorn"/>
-        <s v="Owen Mattingly"/>
         <s v="Jonah Roach"/>
         <s v="Trevor O'Nan"/>
         <s v="Alex Hartings"/>
@@ -1596,7 +1437,6 @@
         <d v="1899-12-30T00:02:06"/>
         <d v="1899-12-30T00:02:08"/>
         <d v="1899-12-30T00:02:15"/>
-        <d v="1899-12-30T00:02:23"/>
         <d v="1899-12-30T00:02:21"/>
         <d v="1899-12-30T00:02:29"/>
         <d v="1899-12-30T00:02:38"/>
@@ -1670,6 +1510,7 @@
         <d v="1899-12-30T00:21:56"/>
         <d v="1899-12-30T00:20:10"/>
         <d v="1899-12-30T00:21:09"/>
+        <d v="1899-12-30T00:02:23" u="1"/>
       </sharedItems>
       <fieldGroup par="22"/>
     </cacheField>
@@ -2556,16 +2397,16 @@
     <n v="156.18"/>
     <m/>
     <m/>
-    <n v="143.06"/>
+    <n v="141"/>
     <x v="15"/>
     <m/>
     <m/>
-    <n v="143.06"/>
-    <d v="1899-12-30T00:02:23"/>
-    <m/>
-    <m/>
-    <s v="13.120000000000005"/>
-    <n v="13.12"/>
+    <n v="141"/>
+    <d v="1899-12-30T00:02:21"/>
+    <m/>
+    <m/>
+    <s v="15.180000000000007"/>
+    <n v="15.18"/>
     <x v="0"/>
   </r>
   <r>
@@ -2579,7 +2420,7 @@
     <n v="149.16300000000001"/>
     <d v="1899-12-30T00:02:29"/>
     <n v="140.58000000000001"/>
-    <x v="16"/>
+    <x v="15"/>
     <m/>
     <m/>
     <n v="140.58000000000001"/>
@@ -2645,7 +2486,7 @@
     <n v="173.89400000000001"/>
     <d v="1899-12-30T00:02:54"/>
     <n v="148.852"/>
-    <x v="17"/>
+    <x v="16"/>
     <m/>
     <m/>
     <n v="148.852"/>
@@ -2711,7 +2552,7 @@
     <n v="147.25200000000001"/>
     <d v="1899-12-30T00:02:27"/>
     <n v="157.863"/>
-    <x v="18"/>
+    <x v="17"/>
     <m/>
     <m/>
     <n v="147.25200000000001"/>
@@ -2774,18 +2615,18 @@
     <n v="138.23099999999999"/>
     <d v="1899-12-30T00:02:18"/>
     <n v="138.23099999999999"/>
-    <n v="135.66"/>
-    <d v="1899-12-30T00:02:16"/>
-    <m/>
-    <x v="3"/>
-    <m/>
-    <m/>
-    <n v="135.66"/>
-    <d v="1899-12-30T00:02:16"/>
+    <n v="134"/>
+    <d v="1899-12-30T00:02:14"/>
+    <m/>
+    <x v="3"/>
+    <m/>
+    <m/>
+    <n v="134"/>
+    <d v="1899-12-30T00:02:14"/>
     <n v="139.54300000000001"/>
     <d v="1899-12-30T00:02:20"/>
-    <s v="2.570999999999998"/>
-    <n v="2.5710000000000002"/>
+    <s v="4.2309999999999945"/>
+    <n v="4.2309999999999999"/>
     <x v="0"/>
   </r>
   <r>
@@ -2818,18 +2659,18 @@
     <n v="140.74799999999999"/>
     <d v="1899-12-30T00:02:21"/>
     <n v="140.74799999999999"/>
-    <n v="139.196"/>
-    <d v="1899-12-30T00:02:19"/>
-    <m/>
-    <x v="3"/>
-    <m/>
-    <m/>
-    <n v="139.196"/>
-    <d v="1899-12-30T00:02:19"/>
+    <n v="133"/>
+    <d v="1899-12-30T00:02:13"/>
+    <m/>
+    <x v="3"/>
+    <m/>
+    <m/>
+    <n v="133"/>
+    <d v="1899-12-30T00:02:13"/>
     <n v="140.74799999999999"/>
     <d v="1899-12-30T00:02:21"/>
-    <s v="1.5519999999999925"/>
-    <n v="1.552"/>
+    <s v="7.7479999999999905"/>
+    <n v="7.7480000000000002"/>
     <x v="0"/>
   </r>
   <r>
@@ -2884,18 +2725,18 @@
     <n v="147.316"/>
     <d v="1899-12-30T00:02:27"/>
     <n v="147.316"/>
-    <n v="149.232"/>
-    <d v="1899-12-30T00:02:29"/>
-    <m/>
-    <x v="3"/>
-    <m/>
-    <m/>
-    <n v="147.316"/>
-    <d v="1899-12-30T00:02:27"/>
-    <m/>
-    <m/>
-    <n v="0"/>
-    <n v="0"/>
+    <n v="144"/>
+    <d v="1899-12-30T00:02:24"/>
+    <m/>
+    <x v="3"/>
+    <m/>
+    <m/>
+    <n v="144"/>
+    <d v="1899-12-30T00:02:24"/>
+    <m/>
+    <m/>
+    <s v="3.3160000000000025"/>
+    <n v="3.3159999999999998"/>
     <x v="0"/>
   </r>
   <r>
@@ -2928,14 +2769,14 @@
     <m/>
     <m/>
     <n v="999999"/>
-    <n v="153.79400000000001"/>
-    <d v="1899-12-30T00:02:34"/>
-    <m/>
-    <x v="3"/>
-    <m/>
-    <m/>
-    <n v="153.79400000000001"/>
-    <d v="1899-12-30T00:02:34"/>
+    <n v="146"/>
+    <d v="1899-12-30T00:02:26"/>
+    <m/>
+    <x v="3"/>
+    <m/>
+    <m/>
+    <n v="146"/>
+    <d v="1899-12-30T00:02:26"/>
     <m/>
     <m/>
     <m/>
@@ -3057,6 +2898,28 @@
     <x v="3"/>
     <x v="3"/>
     <x v="0"/>
+    <n v="147"/>
+    <d v="1899-12-30T00:02:27"/>
+    <n v="147"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="3"/>
+    <m/>
+    <m/>
+    <n v="147"/>
+    <d v="1899-12-30T00:02:27"/>
+    <n v="159.24299999999999"/>
+    <d v="1899-12-30T00:02:39"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="54"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="0"/>
     <n v="147.72300000000001"/>
     <d v="1899-12-30T00:02:28"/>
     <n v="147.72300000000001"/>
@@ -3075,7 +2938,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="54"/>
+    <x v="55"/>
     <x v="3"/>
     <x v="3"/>
     <x v="0"/>
@@ -3097,7 +2960,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="55"/>
+    <x v="56"/>
     <x v="3"/>
     <x v="3"/>
     <x v="0"/>
@@ -3119,7 +2982,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="56"/>
+    <x v="57"/>
     <x v="3"/>
     <x v="3"/>
     <x v="0"/>
@@ -3141,7 +3004,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="57"/>
+    <x v="58"/>
     <x v="3"/>
     <x v="3"/>
     <x v="0"/>
@@ -3163,7 +3026,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="58"/>
+    <x v="59"/>
     <x v="3"/>
     <x v="3"/>
     <x v="0"/>
@@ -3185,28 +3048,6 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="59"/>
-    <x v="3"/>
-    <x v="3"/>
-    <x v="0"/>
-    <n v="159.24299999999999"/>
-    <d v="1899-12-30T00:02:39"/>
-    <n v="159.24299999999999"/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="3"/>
-    <m/>
-    <m/>
-    <n v="159.24299999999999"/>
-    <d v="1899-12-30T00:02:39"/>
-    <n v="159.24299999999999"/>
-    <d v="1899-12-30T00:02:39"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
     <x v="60"/>
     <x v="3"/>
     <x v="3"/>
@@ -3283,7 +3124,7 @@
     <n v="277.08"/>
     <d v="1899-12-30T00:04:37"/>
     <n v="270.35300000000001"/>
-    <x v="19"/>
+    <x v="18"/>
     <n v="274.19499999999999"/>
     <d v="1899-12-30T00:04:34"/>
     <n v="270.35300000000001"/>
@@ -3305,7 +3146,7 @@
     <n v="275.34500000000003"/>
     <d v="1899-12-30T00:04:35"/>
     <n v="249.2"/>
-    <x v="20"/>
+    <x v="19"/>
     <n v="245.43"/>
     <d v="1899-12-30T00:04:05"/>
     <n v="245.43"/>
@@ -3327,7 +3168,7 @@
     <m/>
     <m/>
     <n v="294.11"/>
-    <x v="21"/>
+    <x v="20"/>
     <m/>
     <m/>
     <n v="294.11"/>
@@ -3349,7 +3190,7 @@
     <m/>
     <m/>
     <n v="295.858"/>
-    <x v="22"/>
+    <x v="21"/>
     <n v="273.57600000000002"/>
     <d v="1899-12-30T00:04:34"/>
     <n v="273.57600000000002"/>
@@ -3371,7 +3212,7 @@
     <m/>
     <m/>
     <n v="273.51"/>
-    <x v="23"/>
+    <x v="22"/>
     <n v="293.83699999999999"/>
     <d v="1899-12-30T00:04:54"/>
     <n v="273.51"/>
@@ -3459,7 +3300,7 @@
     <n v="308.38"/>
     <d v="1899-12-30T00:05:08"/>
     <n v="302.67"/>
-    <x v="24"/>
+    <x v="23"/>
     <m/>
     <m/>
     <n v="302.67"/>
@@ -3481,7 +3322,7 @@
     <n v="337.858"/>
     <d v="1899-12-30T00:05:38"/>
     <n v="317.85300000000001"/>
-    <x v="25"/>
+    <x v="24"/>
     <n v="310.05"/>
     <d v="1899-12-30T00:05:10"/>
     <n v="310.05"/>
@@ -3547,7 +3388,7 @@
     <m/>
     <m/>
     <n v="303.76"/>
-    <x v="26"/>
+    <x v="25"/>
     <n v="290.88299999999998"/>
     <d v="1899-12-30T00:04:51"/>
     <n v="290.88299999999998"/>
@@ -3613,7 +3454,7 @@
     <n v="269.52999999999997"/>
     <d v="1899-12-30T00:04:30"/>
     <n v="266.45400000000001"/>
-    <x v="27"/>
+    <x v="26"/>
     <m/>
     <m/>
     <n v="266.45400000000001"/>
@@ -3635,7 +3476,7 @@
     <n v="278.43599999999998"/>
     <d v="1899-12-30T00:04:38"/>
     <n v="263.536"/>
-    <x v="28"/>
+    <x v="27"/>
     <m/>
     <m/>
     <n v="263.536"/>
@@ -3657,7 +3498,7 @@
     <n v="288.76"/>
     <d v="1899-12-30T00:04:49"/>
     <n v="284.584"/>
-    <x v="29"/>
+    <x v="28"/>
     <m/>
     <m/>
     <n v="284.584"/>
@@ -3679,7 +3520,7 @@
     <n v="301.726"/>
     <d v="1899-12-30T00:05:02"/>
     <n v="287.05799999999999"/>
-    <x v="30"/>
+    <x v="29"/>
     <m/>
     <m/>
     <n v="287.05799999999999"/>
@@ -3701,7 +3542,7 @@
     <n v="300.375"/>
     <d v="1899-12-30T00:05:00"/>
     <n v="291.22699999999998"/>
-    <x v="31"/>
+    <x v="30"/>
     <m/>
     <m/>
     <n v="291.22699999999998"/>
@@ -3723,7 +3564,7 @@
     <n v="293.59300000000002"/>
     <d v="1899-12-30T00:04:54"/>
     <n v="284.351"/>
-    <x v="32"/>
+    <x v="31"/>
     <m/>
     <m/>
     <n v="284.351"/>
@@ -3745,7 +3586,7 @@
     <n v="298.64600000000002"/>
     <d v="1899-12-30T00:04:59"/>
     <n v="286.322"/>
-    <x v="33"/>
+    <x v="32"/>
     <m/>
     <m/>
     <n v="286.322"/>
@@ -3767,7 +3608,7 @@
     <n v="291.45600000000002"/>
     <d v="1899-12-30T00:04:52"/>
     <n v="273.02999999999997"/>
-    <x v="34"/>
+    <x v="33"/>
     <m/>
     <m/>
     <n v="273.02999999999997"/>
@@ -3789,7 +3630,7 @@
     <n v="326.57100000000003"/>
     <d v="1899-12-30T00:05:27"/>
     <n v="288.43700000000001"/>
-    <x v="35"/>
+    <x v="34"/>
     <m/>
     <m/>
     <n v="288.43700000000001"/>
@@ -3855,7 +3696,7 @@
     <n v="311.83999999999997"/>
     <d v="1899-12-30T00:05:12"/>
     <n v="290.62700000000001"/>
-    <x v="31"/>
+    <x v="30"/>
     <m/>
     <m/>
     <n v="290.62700000000001"/>
@@ -3877,7 +3718,7 @@
     <n v="319.68900000000002"/>
     <d v="1899-12-30T00:05:20"/>
     <n v="291.14"/>
-    <x v="31"/>
+    <x v="30"/>
     <m/>
     <m/>
     <n v="291.14"/>
@@ -3921,7 +3762,7 @@
     <m/>
     <m/>
     <n v="334.065"/>
-    <x v="36"/>
+    <x v="35"/>
     <m/>
     <m/>
     <n v="334.065"/>
@@ -3943,7 +3784,7 @@
     <m/>
     <m/>
     <n v="321.89299999999997"/>
-    <x v="37"/>
+    <x v="36"/>
     <m/>
     <m/>
     <n v="321.89299999999997"/>
@@ -3965,7 +3806,7 @@
     <n v="388.779"/>
     <d v="1899-12-30T00:06:29"/>
     <n v="331.25299999999999"/>
-    <x v="38"/>
+    <x v="37"/>
     <m/>
     <m/>
     <n v="331.25299999999999"/>
@@ -3987,7 +3828,7 @@
     <n v="325.90199999999999"/>
     <d v="1899-12-30T00:05:26"/>
     <n v="297.67500000000001"/>
-    <x v="39"/>
+    <x v="38"/>
     <m/>
     <m/>
     <n v="297.67500000000001"/>
@@ -4075,7 +3916,7 @@
     <n v="323.89999999999998"/>
     <d v="1899-12-30T00:05:24"/>
     <n v="336.52100000000002"/>
-    <x v="40"/>
+    <x v="39"/>
     <m/>
     <m/>
     <n v="323.89999999999998"/>
@@ -4417,7 +4258,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="54"/>
+    <x v="55"/>
     <x v="3"/>
     <x v="3"/>
     <x v="1"/>
@@ -4439,7 +4280,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="53"/>
+    <x v="54"/>
     <x v="3"/>
     <x v="3"/>
     <x v="1"/>
@@ -4483,7 +4324,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="56"/>
+    <x v="57"/>
     <x v="3"/>
     <x v="3"/>
     <x v="1"/>
@@ -4505,7 +4346,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="59"/>
+    <x v="53"/>
     <x v="3"/>
     <x v="3"/>
     <x v="1"/>
@@ -4527,7 +4368,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="55"/>
+    <x v="56"/>
     <x v="3"/>
     <x v="3"/>
     <x v="1"/>
@@ -4549,7 +4390,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="57"/>
+    <x v="58"/>
     <x v="3"/>
     <x v="3"/>
     <x v="1"/>
@@ -4571,7 +4412,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="58"/>
+    <x v="59"/>
     <x v="3"/>
     <x v="3"/>
     <x v="1"/>
@@ -4625,7 +4466,7 @@
     <n v="607.65"/>
     <d v="1899-12-30T00:10:08"/>
     <n v="594.69000000000005"/>
-    <x v="41"/>
+    <x v="40"/>
     <n v="595.22500000000002"/>
     <d v="1899-12-30T00:09:55"/>
     <n v="594.69000000000005"/>
@@ -4669,7 +4510,7 @@
     <n v="650.48"/>
     <d v="1899-12-30T00:10:50"/>
     <n v="625"/>
-    <x v="42"/>
+    <x v="41"/>
     <n v="622.20000000000005"/>
     <d v="1899-12-30T00:10:22"/>
     <n v="622.20000000000005"/>
@@ -4691,7 +4532,7 @@
     <n v="625.70000000000005"/>
     <d v="1899-12-30T00:10:26"/>
     <n v="605.5"/>
-    <x v="43"/>
+    <x v="42"/>
     <n v="609.79999999999995"/>
     <d v="1899-12-30T00:10:10"/>
     <n v="605.5"/>
@@ -4713,7 +4554,7 @@
     <n v="603.82000000000005"/>
     <d v="1899-12-30T00:10:04"/>
     <n v="555.72"/>
-    <x v="44"/>
+    <x v="43"/>
     <n v="554.01499999999999"/>
     <d v="1899-12-30T00:09:14"/>
     <n v="554.01499999999999"/>
@@ -4735,7 +4576,7 @@
     <n v="658.24"/>
     <d v="1899-12-30T00:10:58"/>
     <n v="639.79999999999995"/>
-    <x v="45"/>
+    <x v="44"/>
     <m/>
     <m/>
     <n v="639.79999999999995"/>
@@ -4823,7 +4664,7 @@
     <n v="718.93"/>
     <d v="1899-12-30T00:11:59"/>
     <n v="681.76700000000005"/>
-    <x v="46"/>
+    <x v="45"/>
     <n v="675"/>
     <d v="1899-12-30T00:11:15"/>
     <n v="675"/>
@@ -4889,7 +4730,7 @@
     <m/>
     <m/>
     <n v="682"/>
-    <x v="46"/>
+    <x v="45"/>
     <n v="695.89599999999996"/>
     <d v="1899-12-30T00:11:36"/>
     <n v="682"/>
@@ -4911,7 +4752,7 @@
     <n v="580.07000000000005"/>
     <d v="1899-12-30T00:09:40"/>
     <n v="567.99"/>
-    <x v="47"/>
+    <x v="46"/>
     <m/>
     <m/>
     <n v="567.99"/>
@@ -4955,7 +4796,7 @@
     <n v="614.55200000000002"/>
     <d v="1899-12-30T00:10:15"/>
     <n v="567.1"/>
-    <x v="48"/>
+    <x v="47"/>
     <m/>
     <m/>
     <n v="567.1"/>
@@ -4977,7 +4818,7 @@
     <n v="605"/>
     <d v="1899-12-30T00:10:05"/>
     <n v="614.31799999999998"/>
-    <x v="49"/>
+    <x v="48"/>
     <m/>
     <m/>
     <n v="605"/>
@@ -4999,7 +4840,7 @@
     <n v="620.20000000000005"/>
     <d v="1899-12-30T00:10:20"/>
     <n v="589.6"/>
-    <x v="50"/>
+    <x v="49"/>
     <m/>
     <m/>
     <n v="589.6"/>
@@ -5021,7 +4862,7 @@
     <n v="650.4"/>
     <d v="1899-12-30T00:10:50"/>
     <n v="640.9"/>
-    <x v="51"/>
+    <x v="50"/>
     <m/>
     <m/>
     <n v="640.9"/>
@@ -5043,7 +4884,7 @@
     <n v="661.3"/>
     <d v="1899-12-30T00:11:01"/>
     <n v="668.30700000000002"/>
-    <x v="52"/>
+    <x v="51"/>
     <m/>
     <m/>
     <n v="661.3"/>
@@ -5065,7 +4906,7 @@
     <n v="650.90899999999999"/>
     <d v="1899-12-30T00:10:51"/>
     <n v="717.11300000000006"/>
-    <x v="53"/>
+    <x v="52"/>
     <m/>
     <m/>
     <n v="650.90899999999999"/>
@@ -5087,7 +4928,7 @@
     <n v="639.4"/>
     <d v="1899-12-30T00:10:39"/>
     <n v="626.79999999999995"/>
-    <x v="54"/>
+    <x v="53"/>
     <m/>
     <m/>
     <n v="626.79999999999995"/>
@@ -5109,7 +4950,7 @@
     <n v="640.29999999999995"/>
     <d v="1899-12-30T00:10:40"/>
     <n v="615.22299999999996"/>
-    <x v="55"/>
+    <x v="54"/>
     <m/>
     <m/>
     <n v="615.22299999999996"/>
@@ -5131,7 +4972,7 @@
     <n v="677.8"/>
     <d v="1899-12-30T00:11:18"/>
     <n v="622.9"/>
-    <x v="56"/>
+    <x v="55"/>
     <m/>
     <m/>
     <n v="622.9"/>
@@ -5153,7 +4994,7 @@
     <n v="671.17700000000002"/>
     <d v="1899-12-30T00:11:11"/>
     <n v="644.9"/>
-    <x v="57"/>
+    <x v="56"/>
     <m/>
     <m/>
     <n v="644.9"/>
@@ -5197,7 +5038,7 @@
     <m/>
     <m/>
     <n v="649.375"/>
-    <x v="58"/>
+    <x v="57"/>
     <m/>
     <m/>
     <n v="649.375"/>
@@ -5241,7 +5082,7 @@
     <m/>
     <m/>
     <n v="723.9"/>
-    <x v="59"/>
+    <x v="58"/>
     <m/>
     <m/>
     <n v="723.9"/>
@@ -5263,7 +5104,7 @@
     <m/>
     <m/>
     <n v="705.8"/>
-    <x v="60"/>
+    <x v="59"/>
     <m/>
     <m/>
     <n v="705.8"/>
@@ -5285,7 +5126,7 @@
     <m/>
     <m/>
     <n v="718.2"/>
-    <x v="61"/>
+    <x v="60"/>
     <m/>
     <m/>
     <n v="718.2"/>
@@ -5351,7 +5192,7 @@
     <m/>
     <m/>
     <n v="746.36199999999997"/>
-    <x v="62"/>
+    <x v="61"/>
     <m/>
     <m/>
     <n v="746.36199999999997"/>
@@ -5671,7 +5512,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="54"/>
+    <x v="55"/>
     <x v="3"/>
     <x v="3"/>
     <x v="2"/>
@@ -5693,7 +5534,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="53"/>
+    <x v="54"/>
     <x v="3"/>
     <x v="3"/>
     <x v="2"/>
@@ -5715,7 +5556,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="55"/>
+    <x v="56"/>
     <x v="3"/>
     <x v="3"/>
     <x v="2"/>
@@ -5737,7 +5578,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="56"/>
+    <x v="57"/>
     <x v="3"/>
     <x v="3"/>
     <x v="2"/>
@@ -5759,7 +5600,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="59"/>
+    <x v="53"/>
     <x v="3"/>
     <x v="3"/>
     <x v="2"/>
@@ -5781,7 +5622,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="57"/>
+    <x v="58"/>
     <x v="3"/>
     <x v="3"/>
     <x v="2"/>
@@ -5835,7 +5676,7 @@
     <n v="1005.1"/>
     <d v="1899-12-30T00:16:45"/>
     <n v="966.4"/>
-    <x v="63"/>
+    <x v="62"/>
     <n v="949.1"/>
     <d v="1899-12-30T00:15:49"/>
     <n v="949.1"/>
@@ -5857,7 +5698,7 @@
     <n v="1037.5999999999999"/>
     <d v="1899-12-30T00:17:18"/>
     <n v="1013.6"/>
-    <x v="64"/>
+    <x v="63"/>
     <n v="987.2"/>
     <d v="1899-12-30T00:16:27"/>
     <n v="987.2"/>
@@ -5879,7 +5720,7 @@
     <n v="1011.2"/>
     <d v="1899-12-30T00:16:51"/>
     <n v="944.1"/>
-    <x v="65"/>
+    <x v="64"/>
     <n v="901.8"/>
     <d v="1899-12-30T00:15:02"/>
     <n v="901.8"/>
@@ -5901,7 +5742,7 @@
     <n v="1114.9000000000001"/>
     <d v="1899-12-30T00:18:35"/>
     <n v="1036.5999999999999"/>
-    <x v="66"/>
+    <x v="65"/>
     <n v="1057.7"/>
     <d v="1899-12-30T00:17:38"/>
     <n v="1036.5999999999999"/>
@@ -5945,7 +5786,7 @@
     <n v="1069.9000000000001"/>
     <d v="1899-12-30T00:17:50"/>
     <n v="1008.8"/>
-    <x v="67"/>
+    <x v="66"/>
     <n v="1020.1"/>
     <d v="1899-12-30T00:17:00"/>
     <n v="1008.8"/>
@@ -6143,7 +5984,7 @@
     <m/>
     <m/>
     <n v="1115.33"/>
-    <x v="68"/>
+    <x v="67"/>
     <m/>
     <m/>
     <n v="1115.33"/>
@@ -6165,7 +6006,7 @@
     <n v="1233.5999999999999"/>
     <d v="1899-12-30T00:20:34"/>
     <n v="1182.17"/>
-    <x v="69"/>
+    <x v="68"/>
     <m/>
     <m/>
     <n v="1182.17"/>
@@ -6209,7 +6050,7 @@
     <n v="993.7"/>
     <d v="1899-12-30T00:16:34"/>
     <n v="935.3"/>
-    <x v="70"/>
+    <x v="69"/>
     <m/>
     <m/>
     <n v="935.3"/>
@@ -6231,7 +6072,7 @@
     <n v="994"/>
     <d v="1899-12-30T00:16:34"/>
     <n v="984.8"/>
-    <x v="71"/>
+    <x v="70"/>
     <m/>
     <m/>
     <n v="984.8"/>
@@ -6253,7 +6094,7 @@
     <n v="1039.0999999999999"/>
     <d v="1899-12-30T00:17:19"/>
     <n v="1133.2"/>
-    <x v="72"/>
+    <x v="71"/>
     <m/>
     <m/>
     <n v="1039.0999999999999"/>
@@ -6275,7 +6116,7 @@
     <n v="1033.2"/>
     <d v="1899-12-30T00:17:13"/>
     <n v="977.6"/>
-    <x v="73"/>
+    <x v="72"/>
     <m/>
     <m/>
     <n v="977.6"/>
@@ -6319,7 +6160,7 @@
     <n v="1024.56"/>
     <d v="1899-12-30T00:17:05"/>
     <n v="1002.91"/>
-    <x v="74"/>
+    <x v="73"/>
     <m/>
     <m/>
     <n v="1002.91"/>
@@ -6341,7 +6182,7 @@
     <n v="1104.5"/>
     <d v="1899-12-30T00:18:25"/>
     <n v="1080.5999999999999"/>
-    <x v="75"/>
+    <x v="74"/>
     <m/>
     <m/>
     <n v="1080.5999999999999"/>
@@ -6363,7 +6204,7 @@
     <n v="1063.9000000000001"/>
     <d v="1899-12-30T00:17:44"/>
     <n v="1060.4000000000001"/>
-    <x v="76"/>
+    <x v="75"/>
     <m/>
     <m/>
     <n v="1060.4000000000001"/>
@@ -6385,7 +6226,7 @@
     <n v="1048.2"/>
     <d v="1899-12-30T00:17:28"/>
     <n v="1050.2"/>
-    <x v="77"/>
+    <x v="76"/>
     <m/>
     <m/>
     <n v="1048.2"/>
@@ -6429,7 +6270,7 @@
     <n v="1107.7"/>
     <d v="1899-12-30T00:18:28"/>
     <n v="1069.5999999999999"/>
-    <x v="78"/>
+    <x v="77"/>
     <m/>
     <m/>
     <n v="1069.5999999999999"/>
@@ -6451,7 +6292,7 @@
     <n v="1324.8"/>
     <d v="1899-12-30T00:22:05"/>
     <n v="1198.9000000000001"/>
-    <x v="79"/>
+    <x v="78"/>
     <m/>
     <m/>
     <n v="1198.9000000000001"/>
@@ -6473,7 +6314,7 @@
     <n v="1066.5"/>
     <d v="1899-12-30T00:17:46"/>
     <n v="1039.8"/>
-    <x v="80"/>
+    <x v="79"/>
     <m/>
     <m/>
     <n v="1039.8"/>
@@ -6495,7 +6336,7 @@
     <n v="1086"/>
     <d v="1899-12-30T00:18:06"/>
     <n v="1052.3"/>
-    <x v="81"/>
+    <x v="80"/>
     <m/>
     <m/>
     <n v="1052.3"/>
@@ -6517,7 +6358,7 @@
     <n v="1276.8"/>
     <d v="1899-12-30T00:21:17"/>
     <n v="1334.1"/>
-    <x v="82"/>
+    <x v="81"/>
     <m/>
     <m/>
     <n v="1276.8"/>
@@ -6539,7 +6380,7 @@
     <n v="1039.49"/>
     <d v="1899-12-30T00:17:19"/>
     <n v="991.1"/>
-    <x v="83"/>
+    <x v="82"/>
     <m/>
     <m/>
     <n v="991.1"/>
@@ -6561,7 +6402,7 @@
     <n v="1222.4000000000001"/>
     <d v="1899-12-30T00:20:22"/>
     <n v="1169.8"/>
-    <x v="84"/>
+    <x v="83"/>
     <m/>
     <m/>
     <n v="1169.8"/>
@@ -6583,7 +6424,7 @@
     <n v="1074.7"/>
     <d v="1899-12-30T00:17:55"/>
     <n v="1207.7"/>
-    <x v="85"/>
+    <x v="84"/>
     <m/>
     <m/>
     <n v="1074.7"/>
@@ -6627,7 +6468,7 @@
     <n v="1070.4000000000001"/>
     <d v="1899-12-30T00:17:50"/>
     <n v="1169.7"/>
-    <x v="84"/>
+    <x v="83"/>
     <m/>
     <m/>
     <n v="1070.4000000000001"/>
@@ -6649,7 +6490,7 @@
     <n v="1397.4"/>
     <d v="1899-12-30T00:23:17"/>
     <n v="1316.2"/>
-    <x v="86"/>
+    <x v="85"/>
     <m/>
     <m/>
     <n v="1316.2"/>
@@ -6671,7 +6512,7 @@
     <n v="1272.7"/>
     <d v="1899-12-30T00:21:13"/>
     <n v="1209.8"/>
-    <x v="87"/>
+    <x v="86"/>
     <m/>
     <m/>
     <n v="1209.8"/>
@@ -6693,7 +6534,7 @@
     <m/>
     <m/>
     <n v="1268.7"/>
-    <x v="88"/>
+    <x v="87"/>
     <m/>
     <m/>
     <n v="1268.7"/>
@@ -7057,7 +6898,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="56"/>
+    <x v="57"/>
     <x v="3"/>
     <x v="3"/>
     <x v="3"/>
@@ -7079,7 +6920,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="53"/>
+    <x v="54"/>
     <x v="3"/>
     <x v="3"/>
     <x v="3"/>
@@ -7101,7 +6942,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="55"/>
+    <x v="56"/>
     <x v="3"/>
     <x v="3"/>
     <x v="3"/>
@@ -7123,7 +6964,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="54"/>
+    <x v="55"/>
     <x v="3"/>
     <x v="3"/>
     <x v="3"/>
@@ -7145,7 +6986,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="59"/>
+    <x v="53"/>
     <x v="3"/>
     <x v="3"/>
     <x v="3"/>
@@ -7214,31 +7055,31 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C40C4673-9275-42B8-90A8-EA84E10FDE10}" name="PivotTable1" cacheId="51" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C40C4673-9275-42B8-90A8-EA84E10FDE10}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="A4:I91" firstHeaderRow="1" firstDataRow="2" firstDataCol="3" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="23">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="ascending" defaultSubtotal="0">
       <items count="73">
-        <item x="57"/>
+        <item x="58"/>
         <item x="0"/>
-        <item x="53"/>
+        <item x="54"/>
         <item x="49"/>
         <item x="48"/>
-        <item x="56"/>
+        <item x="57"/>
         <item x="1"/>
         <item x="2"/>
-        <item x="58"/>
+        <item x="59"/>
         <item x="60"/>
         <item x="51"/>
         <item x="12"/>
         <item x="52"/>
         <item x="6"/>
-        <item x="54"/>
-        <item x="59"/>
+        <item x="55"/>
+        <item x="53"/>
         <item x="50"/>
         <item x="10"/>
         <item x="4"/>
-        <item x="55"/>
+        <item x="56"/>
         <item x="13"/>
         <item x="61"/>
         <item x="9"/>
@@ -7361,82 +7202,82 @@
         <item x="1"/>
         <item x="10"/>
         <item x="14"/>
-        <item x="16"/>
         <item x="15"/>
+        <item m="1" x="88"/>
         <item x="7"/>
         <item x="6"/>
+        <item x="16"/>
         <item x="17"/>
+        <item x="19"/>
+        <item x="27"/>
+        <item x="26"/>
         <item x="18"/>
-        <item x="20"/>
+        <item x="33"/>
+        <item x="22"/>
+        <item x="31"/>
         <item x="28"/>
-        <item x="27"/>
-        <item x="19"/>
-        <item x="34"/>
-        <item x="23"/>
         <item x="32"/>
         <item x="29"/>
-        <item x="33"/>
+        <item x="34"/>
         <item x="30"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="38"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="24"/>
+        <item x="36"/>
+        <item x="37"/>
         <item x="35"/>
-        <item x="31"/>
-        <item x="21"/>
-        <item x="22"/>
         <item x="39"/>
-        <item x="24"/>
-        <item x="26"/>
-        <item x="25"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="36"/>
+        <item x="43"/>
+        <item x="47"/>
+        <item x="46"/>
+        <item x="49"/>
         <item x="40"/>
+        <item x="42"/>
+        <item x="48"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="41"/>
+        <item x="53"/>
         <item x="44"/>
-        <item x="48"/>
-        <item x="47"/>
         <item x="50"/>
-        <item x="41"/>
-        <item x="43"/>
-        <item x="49"/>
-        <item x="55"/>
         <item x="56"/>
-        <item x="42"/>
-        <item x="54"/>
+        <item x="57"/>
+        <item x="51"/>
         <item x="45"/>
-        <item x="51"/>
-        <item x="57"/>
+        <item x="59"/>
+        <item x="52"/>
+        <item x="60"/>
         <item x="58"/>
-        <item x="52"/>
-        <item x="46"/>
-        <item x="60"/>
-        <item x="53"/>
         <item x="61"/>
-        <item x="59"/>
+        <item x="69"/>
+        <item x="64"/>
         <item x="62"/>
+        <item x="72"/>
         <item x="70"/>
+        <item x="82"/>
+        <item x="73"/>
+        <item x="66"/>
+        <item x="63"/>
         <item x="65"/>
-        <item x="63"/>
-        <item x="73"/>
+        <item x="79"/>
+        <item x="76"/>
+        <item x="80"/>
+        <item x="75"/>
+        <item x="77"/>
+        <item x="74"/>
+        <item x="67"/>
         <item x="71"/>
         <item x="83"/>
-        <item x="74"/>
-        <item x="67"/>
-        <item x="64"/>
-        <item x="66"/>
-        <item x="80"/>
-        <item x="77"/>
+        <item x="68"/>
+        <item x="78"/>
+        <item x="84"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="85"/>
         <item x="81"/>
-        <item x="76"/>
-        <item x="78"/>
-        <item x="75"/>
-        <item x="68"/>
-        <item x="72"/>
-        <item x="84"/>
-        <item x="69"/>
-        <item x="79"/>
-        <item x="85"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="86"/>
-        <item x="82"/>
         <item x="3"/>
         <item t="default"/>
       </items>
@@ -7922,6 +7763,10 @@
       <x/>
     </i>
     <i r="1">
+      <x v="15"/>
+      <x v="1"/>
+    </i>
+    <i r="1">
       <x v="2"/>
       <x v="1"/>
     </i>
@@ -7947,10 +7792,6 @@
     </i>
     <i r="1">
       <x v="8"/>
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="15"/>
       <x v="1"/>
     </i>
     <i r="1">
@@ -8013,7 +7854,7 @@
     <dataField name="Sum of freshman_sort" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="65">
+    <format dxfId="11">
       <pivotArea outline="0" fieldPosition="0">
         <references count="4">
           <reference field="4294967294" count="1" selected="0">
@@ -8031,7 +7872,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="64">
+    <format dxfId="10">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -8040,7 +7881,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="63">
+    <format dxfId="9">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -8049,7 +7890,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="62">
+    <format dxfId="8">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -8058,7 +7899,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="61">
+    <format dxfId="7">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -8067,7 +7908,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="60">
+    <format dxfId="6">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -8426,15 +8267,15 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -8456,19 +8297,19 @@
         <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F5" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G5" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="H5" t="s">
         <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -10057,47 +9898,47 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C78">
         <v>2029</v>
       </c>
       <c r="D78" s="4">
-        <v>1.712962962962963E-3</v>
+        <v>1.7013888888888892E-3</v>
       </c>
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
       <c r="H78" s="6">
-        <v>1.712962962962963E-3</v>
+        <v>1.7013888888888892E-3</v>
       </c>
       <c r="I78" s="7">
-        <v>147.72300000000001</v>
+        <v>147</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C79">
         <v>2029</v>
       </c>
       <c r="D79" s="4">
-        <v>1.736111111111111E-3</v>
+        <v>1.712962962962963E-3</v>
       </c>
       <c r="E79" s="5"/>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
       <c r="H79" s="6">
-        <v>1.736111111111111E-3</v>
+        <v>1.712962962962963E-3</v>
       </c>
       <c r="I79" s="7">
-        <v>149.66800000000001</v>
+        <v>147.72300000000001</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C80">
         <v>2029</v>
@@ -10112,111 +9953,111 @@
         <v>1.736111111111111E-3</v>
       </c>
       <c r="I80" s="7">
-        <v>149.733</v>
+        <v>149.66800000000001</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C81">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="D81" s="4">
-        <v>1.7476851851851852E-3</v>
-      </c>
-      <c r="E81" s="5">
-        <v>1.712962962962963E-3</v>
-      </c>
-      <c r="F81" s="5">
-        <v>1.689814814814815E-3</v>
-      </c>
+        <v>1.736111111111111E-3</v>
+      </c>
+      <c r="E81" s="5"/>
+      <c r="F81" s="5"/>
       <c r="G81" s="5"/>
       <c r="H81" s="6">
-        <v>1.689814814814815E-3</v>
+        <v>1.736111111111111E-3</v>
       </c>
       <c r="I81" s="7">
-        <v>150.82</v>
+        <v>149.733</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C82">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="D82" s="4">
-        <v>1.7708333333333332E-3</v>
-      </c>
-      <c r="E82" s="5"/>
-      <c r="F82" s="5"/>
+        <v>1.7476851851851852E-3</v>
+      </c>
+      <c r="E82" s="5">
+        <v>1.712962962962963E-3</v>
+      </c>
+      <c r="F82" s="5">
+        <v>1.689814814814815E-3</v>
+      </c>
       <c r="G82" s="5"/>
       <c r="H82" s="6">
-        <v>1.7708333333333332E-3</v>
+        <v>1.689814814814815E-3</v>
       </c>
       <c r="I82" s="7">
-        <v>152.66</v>
+        <v>150.82</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C83">
         <v>2029</v>
       </c>
       <c r="D83" s="4">
-        <v>1.7824074074074072E-3</v>
+        <v>1.7708333333333332E-3</v>
       </c>
       <c r="E83" s="5"/>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
       <c r="H83" s="6">
-        <v>1.7824074074074072E-3</v>
+        <v>1.7708333333333332E-3</v>
       </c>
       <c r="I83" s="7">
-        <v>154.40700000000001</v>
+        <v>152.66</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C84">
         <v>2029</v>
       </c>
       <c r="D84" s="4">
-        <v>1.8171296296296297E-3</v>
+        <v>1.7824074074074072E-3</v>
       </c>
       <c r="E84" s="5"/>
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
       <c r="H84" s="6">
-        <v>1.8171296296296297E-3</v>
+        <v>1.7824074074074072E-3</v>
       </c>
       <c r="I84" s="7">
-        <v>156.70400000000001</v>
+        <v>154.40700000000001</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C85">
         <v>2029</v>
       </c>
       <c r="D85" s="4">
-        <v>1.8402777777777777E-3</v>
+        <v>1.8171296296296297E-3</v>
       </c>
       <c r="E85" s="5"/>
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
       <c r="H85" s="6">
-        <v>1.8402777777777777E-3</v>
+        <v>1.8171296296296297E-3</v>
       </c>
       <c r="I85" s="7">
-        <v>159.24299999999999</v>
+        <v>156.70400000000001</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.35">
@@ -10336,7 +10177,7 @@
         <v>64</v>
       </c>
       <c r="D91" s="4">
-        <v>6.2842712842712855E-3</v>
+        <v>6.2824675324675335E-3</v>
       </c>
       <c r="E91" s="5">
         <v>6.0234152421652443E-3</v>
@@ -10348,10 +10189,10 @@
         <v>5.6472222222222227E-3</v>
       </c>
       <c r="H91" s="6">
-        <v>6.1299019607843168E-3</v>
+        <v>6.1282679738562133E-3</v>
       </c>
       <c r="I91" s="7">
-        <v>8041796.6699999999</v>
+        <v>8041784.4270000001</v>
       </c>
     </row>
   </sheetData>
@@ -10373,7 +10214,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5618C841-8876-4D0C-80DF-C05F2AAF82DF}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:T242"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -10411,7 +10251,7 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H1" t="s">
         <v>80</v>
@@ -10450,10 +10290,10 @@
         <v>11</v>
       </c>
       <c r="T1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -10512,10 +10352,10 @@
         <v>12.64</v>
       </c>
       <c r="T2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -10568,10 +10408,10 @@
         <v>2.75</v>
       </c>
       <c r="T3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -10630,10 +10470,10 @@
         <v>12.295</v>
       </c>
       <c r="T4" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -10668,10 +10508,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -10724,10 +10564,10 @@
         <v>10.872999999999999</v>
       </c>
       <c r="T6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -10762,10 +10602,10 @@
         <v>0</v>
       </c>
       <c r="T7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -10824,10 +10664,10 @@
         <v>31.068000000000001</v>
       </c>
       <c r="T8" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>46</v>
       </c>
@@ -10868,10 +10708,10 @@
         <v>2.23</v>
       </c>
       <c r="T9" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>45</v>
       </c>
@@ -10912,10 +10752,10 @@
         <v>0</v>
       </c>
       <c r="T10" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -10968,10 +10808,10 @@
         <v>5.2110000000000003</v>
       </c>
       <c r="T11" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -11030,10 +10870,10 @@
         <v>20.704999999999998</v>
       </c>
       <c r="T12" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -11068,7 +10908,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.35">
@@ -11112,10 +10952,10 @@
         <v>1.3622685185185185E-3</v>
       </c>
       <c r="T14" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -11150,10 +10990,10 @@
         <v>1.4212962962962964E-3</v>
       </c>
       <c r="T15" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -11182,10 +11022,10 @@
         <v>1.9548611111111112E-3</v>
       </c>
       <c r="T16" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -11232,10 +11072,10 @@
         <v>8.5190000000000001</v>
       </c>
       <c r="T17" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>89</v>
       </c>
@@ -11282,10 +11122,10 @@
         <v>10.74</v>
       </c>
       <c r="T18" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>91</v>
       </c>
@@ -11320,10 +11160,10 @@
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>92</v>
       </c>
@@ -11370,10 +11210,10 @@
         <v>9.5860000000000003</v>
       </c>
       <c r="T20" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>94</v>
       </c>
@@ -11420,10 +11260,10 @@
         <v>3.278</v>
       </c>
       <c r="T21" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>96</v>
       </c>
@@ -11470,10 +11310,10 @@
         <v>9.6479999999999997</v>
       </c>
       <c r="T22" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -11520,10 +11360,10 @@
         <v>10.545</v>
       </c>
       <c r="T23" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>100</v>
       </c>
@@ -11570,10 +11410,10 @@
         <v>8.3970000000000002</v>
       </c>
       <c r="T24" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>102</v>
       </c>
@@ -11620,10 +11460,10 @@
         <v>12.962999999999999</v>
       </c>
       <c r="T25" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>104</v>
       </c>
@@ -11670,10 +11510,10 @@
         <v>14.66</v>
       </c>
       <c r="T26" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>106</v>
       </c>
@@ -11720,10 +11560,10 @@
         <v>15.279</v>
       </c>
       <c r="T27" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>108</v>
       </c>
@@ -11764,10 +11604,10 @@
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>109</v>
       </c>
@@ -11802,10 +11642,10 @@
         <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>110</v>
       </c>
@@ -11852,10 +11692,10 @@
         <v>21.039000000000001</v>
       </c>
       <c r="T30" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>112</v>
       </c>
@@ -11896,10 +11736,10 @@
         <v>10.67</v>
       </c>
       <c r="T31" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>114</v>
       </c>
@@ -11922,30 +11762,30 @@
         <v>156.18</v>
       </c>
       <c r="J32">
-        <v>143.06</v>
+        <v>141</v>
       </c>
       <c r="K32" s="1">
-        <v>1.6562499999999997E-3</v>
+        <v>1.6319444444444445E-3</v>
       </c>
       <c r="N32">
-        <v>143.06</v>
+        <v>141</v>
       </c>
       <c r="O32" s="1">
-        <v>1.6562499999999997E-3</v>
+        <v>1.6319444444444445E-3</v>
       </c>
       <c r="R32" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="S32">
+        <v>15.18</v>
+      </c>
+      <c r="T32" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>115</v>
-      </c>
-      <c r="S32">
-        <v>13.12</v>
-      </c>
-      <c r="T32" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>116</v>
       </c>
       <c r="B33">
         <v>2027</v>
@@ -11984,18 +11824,18 @@
         <v>1.6273148148148147E-3</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="S33">
         <v>17.003</v>
       </c>
       <c r="T33" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B34">
         <v>2027</v>
@@ -12028,12 +11868,12 @@
         <v>0</v>
       </c>
       <c r="T34" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B35">
         <v>2027</v>
@@ -12066,12 +11906,12 @@
         <v>0</v>
       </c>
       <c r="T35" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B36">
         <v>2027</v>
@@ -12110,18 +11950,18 @@
         <v>1.7233796296296294E-3</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="S36">
         <v>24.271000000000001</v>
       </c>
       <c r="T36" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B37">
         <v>2027</v>
@@ -12154,18 +11994,18 @@
         <v>1.9224537037037038E-3</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="S37">
         <v>12.055</v>
       </c>
       <c r="T37" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B38">
         <v>2027</v>
@@ -12198,18 +12038,18 @@
         <v>2.0868055555555557E-3</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="S38">
         <v>17.32</v>
       </c>
       <c r="T38" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B39">
         <v>2027</v>
@@ -12242,12 +12082,12 @@
         <v>1.7048611111111112E-3</v>
       </c>
       <c r="T39" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B40">
         <v>2027</v>
@@ -12274,18 +12114,18 @@
         <v>2.0104166666666669E-3</v>
       </c>
       <c r="T40" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B41">
         <v>2028</v>
       </c>
       <c r="C41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D41">
         <v>800</v>
@@ -12318,24 +12158,24 @@
         <v>1.5000000000000002E-3</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="S41">
         <v>4.6929999999999996</v>
       </c>
       <c r="T41" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B42">
         <v>2028</v>
       </c>
       <c r="C42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D42">
         <v>800</v>
@@ -12350,16 +12190,16 @@
         <v>138.23099999999999</v>
       </c>
       <c r="H42">
-        <v>135.66</v>
+        <v>134</v>
       </c>
       <c r="I42" s="1">
-        <v>1.5706018518518519E-3</v>
+        <v>1.5509259259259261E-3</v>
       </c>
       <c r="N42">
-        <v>135.66</v>
+        <v>134</v>
       </c>
       <c r="O42" s="1">
-        <v>1.5706018518518519E-3</v>
+        <v>1.5509259259259261E-3</v>
       </c>
       <c r="P42">
         <v>139.54300000000001</v>
@@ -12368,24 +12208,24 @@
         <v>1.6145833333333333E-3</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>132</v>
+        <v>220</v>
       </c>
       <c r="S42">
-        <v>2.5710000000000002</v>
+        <v>4.2309999999999999</v>
       </c>
       <c r="T42" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B43">
         <v>2028</v>
       </c>
       <c r="C43" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D43">
         <v>800</v>
@@ -12412,24 +12252,24 @@
         <v>1.511574074074074E-3</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="S43">
         <v>8.1739999999999995</v>
       </c>
       <c r="T43" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B44">
         <v>2028</v>
       </c>
       <c r="C44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D44">
         <v>800</v>
@@ -12444,16 +12284,16 @@
         <v>140.74799999999999</v>
       </c>
       <c r="H44">
-        <v>139.196</v>
+        <v>133</v>
       </c>
       <c r="I44" s="1">
-        <v>1.6111111111111109E-3</v>
+        <v>1.5393518518518519E-3</v>
       </c>
       <c r="N44">
-        <v>139.196</v>
+        <v>133</v>
       </c>
       <c r="O44" s="1">
-        <v>1.6111111111111109E-3</v>
+        <v>1.5393518518518519E-3</v>
       </c>
       <c r="P44">
         <v>140.74799999999999</v>
@@ -12462,24 +12302,24 @@
         <v>1.6284722222222221E-3</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>136</v>
+        <v>221</v>
       </c>
       <c r="S44">
-        <v>1.552</v>
+        <v>7.7480000000000002</v>
       </c>
       <c r="T44" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B45">
         <v>2028</v>
       </c>
       <c r="C45" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D45">
         <v>800</v>
@@ -12512,18 +12352,18 @@
         <v>0</v>
       </c>
       <c r="T45" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B46">
         <v>2028</v>
       </c>
       <c r="C46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D46">
         <v>800</v>
@@ -12556,24 +12396,24 @@
         <v>1.6747685185185184E-3</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="S46">
         <v>11.638999999999999</v>
       </c>
       <c r="T46" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B47">
         <v>2028</v>
       </c>
       <c r="C47" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D47">
         <v>800</v>
@@ -12588,36 +12428,36 @@
         <v>147.316</v>
       </c>
       <c r="H47">
-        <v>149.232</v>
+        <v>144</v>
       </c>
       <c r="I47" s="1">
-        <v>1.7268518518518518E-3</v>
+        <v>1.6666666666666668E-3</v>
       </c>
       <c r="N47">
-        <v>147.316</v>
+        <v>144</v>
       </c>
       <c r="O47" s="1">
-        <v>1.7048611111111112E-3</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
+        <v>1.6666666666666668E-3</v>
+      </c>
+      <c r="R47" s="2" t="s">
+        <v>222</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>3.3159999999999998</v>
       </c>
       <c r="T47" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B48">
         <v>2028</v>
       </c>
       <c r="C48" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D48">
         <v>800</v>
@@ -12644,18 +12484,18 @@
         <v>0</v>
       </c>
       <c r="T48" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B49">
         <v>2028</v>
       </c>
       <c r="C49" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D49">
         <v>800</v>
@@ -12664,22 +12504,22 @@
         <v>999999</v>
       </c>
       <c r="H49">
-        <v>153.79400000000001</v>
+        <v>146</v>
       </c>
       <c r="I49" s="1">
-        <v>1.7800925925925927E-3</v>
+        <v>1.689814814814815E-3</v>
       </c>
       <c r="N49">
-        <v>153.79400000000001</v>
+        <v>146</v>
       </c>
       <c r="O49" s="1">
-        <v>1.7800925925925927E-3</v>
+        <v>1.689814814814815E-3</v>
       </c>
       <c r="T49" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>12</v>
       </c>
@@ -12720,10 +12560,10 @@
         <v>0</v>
       </c>
       <c r="T50" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -12764,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="T51" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>16</v>
       </c>
@@ -12808,10 +12648,10 @@
         <v>0</v>
       </c>
       <c r="T52" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -12852,10 +12692,10 @@
         <v>0</v>
       </c>
       <c r="T53" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -12896,12 +12736,12 @@
         <v>0</v>
       </c>
       <c r="T54" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B55">
         <v>2029</v>
@@ -12913,25 +12753,25 @@
         <v>800</v>
       </c>
       <c r="E55">
-        <v>147.72300000000001</v>
+        <v>147</v>
       </c>
       <c r="F55" s="1">
-        <v>1.7094907407407408E-3</v>
+        <v>1.7013888888888892E-3</v>
       </c>
       <c r="G55">
-        <v>147.72300000000001</v>
+        <v>147</v>
       </c>
       <c r="N55">
-        <v>147.72300000000001</v>
+        <v>147</v>
       </c>
       <c r="O55" s="1">
-        <v>1.7094907407407408E-3</v>
+        <v>1.7013888888888892E-3</v>
       </c>
       <c r="P55">
-        <v>147.72300000000001</v>
+        <v>159.24299999999999</v>
       </c>
       <c r="Q55" s="1">
-        <v>1.7094907407407408E-3</v>
+        <v>1.8425925925925927E-3</v>
       </c>
       <c r="R55">
         <v>0</v>
@@ -12940,12 +12780,12 @@
         <v>0</v>
       </c>
       <c r="T55" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B56">
         <v>2029</v>
@@ -12957,25 +12797,25 @@
         <v>800</v>
       </c>
       <c r="E56">
-        <v>149.66800000000001</v>
+        <v>147.72300000000001</v>
       </c>
       <c r="F56" s="1">
-        <v>1.7326388888888888E-3</v>
+        <v>1.7094907407407408E-3</v>
       </c>
       <c r="G56">
-        <v>149.66800000000001</v>
+        <v>147.72300000000001</v>
       </c>
       <c r="N56">
-        <v>149.66800000000001</v>
+        <v>147.72300000000001</v>
       </c>
       <c r="O56" s="1">
-        <v>1.7326388888888888E-3</v>
+        <v>1.7094907407407408E-3</v>
       </c>
       <c r="P56">
-        <v>149.66800000000001</v>
+        <v>147.72300000000001</v>
       </c>
       <c r="Q56" s="1">
-        <v>1.7326388888888888E-3</v>
+        <v>1.7094907407407408E-3</v>
       </c>
       <c r="R56">
         <v>0</v>
@@ -12984,12 +12824,12 @@
         <v>0</v>
       </c>
       <c r="T56" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B57">
         <v>2029</v>
@@ -13001,22 +12841,22 @@
         <v>800</v>
       </c>
       <c r="E57">
-        <v>149.733</v>
+        <v>149.66800000000001</v>
       </c>
       <c r="F57" s="1">
         <v>1.7326388888888888E-3</v>
       </c>
       <c r="G57">
-        <v>149.733</v>
+        <v>149.66800000000001</v>
       </c>
       <c r="N57">
-        <v>149.733</v>
+        <v>149.66800000000001</v>
       </c>
       <c r="O57" s="1">
         <v>1.7326388888888888E-3</v>
       </c>
       <c r="P57">
-        <v>149.733</v>
+        <v>149.66800000000001</v>
       </c>
       <c r="Q57" s="1">
         <v>1.7326388888888888E-3</v>
@@ -13028,12 +12868,12 @@
         <v>0</v>
       </c>
       <c r="T57" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B58">
         <v>2029</v>
@@ -13045,19 +12885,25 @@
         <v>800</v>
       </c>
       <c r="E58">
-        <v>152.66</v>
+        <v>149.733</v>
       </c>
       <c r="F58" s="1">
-        <v>1.767361111111111E-3</v>
+        <v>1.7326388888888888E-3</v>
       </c>
       <c r="G58">
-        <v>152.66</v>
+        <v>149.733</v>
       </c>
       <c r="N58">
-        <v>152.66</v>
+        <v>149.733</v>
       </c>
       <c r="O58" s="1">
-        <v>1.767361111111111E-3</v>
+        <v>1.7326388888888888E-3</v>
+      </c>
+      <c r="P58">
+        <v>149.733</v>
+      </c>
+      <c r="Q58" s="1">
+        <v>1.7326388888888888E-3</v>
       </c>
       <c r="R58">
         <v>0</v>
@@ -13066,12 +12912,12 @@
         <v>0</v>
       </c>
       <c r="T58" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B59">
         <v>2029</v>
@@ -13083,25 +12929,19 @@
         <v>800</v>
       </c>
       <c r="E59">
-        <v>154.40700000000001</v>
+        <v>152.66</v>
       </c>
       <c r="F59" s="1">
-        <v>1.7870370370370368E-3</v>
+        <v>1.767361111111111E-3</v>
       </c>
       <c r="G59">
-        <v>154.40700000000001</v>
+        <v>152.66</v>
       </c>
       <c r="N59">
-        <v>154.40700000000001</v>
+        <v>152.66</v>
       </c>
       <c r="O59" s="1">
-        <v>1.7870370370370368E-3</v>
-      </c>
-      <c r="P59">
-        <v>155.249</v>
-      </c>
-      <c r="Q59" s="1">
-        <v>1.7962962962962965E-3</v>
+        <v>1.767361111111111E-3</v>
       </c>
       <c r="R59">
         <v>0</v>
@@ -13110,12 +12950,12 @@
         <v>0</v>
       </c>
       <c r="T59" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B60">
         <v>2029</v>
@@ -13127,25 +12967,25 @@
         <v>800</v>
       </c>
       <c r="E60">
-        <v>156.70400000000001</v>
+        <v>154.40700000000001</v>
       </c>
       <c r="F60" s="1">
-        <v>1.8136574074074077E-3</v>
+        <v>1.7870370370370368E-3</v>
       </c>
       <c r="G60">
-        <v>156.70400000000001</v>
+        <v>154.40700000000001</v>
       </c>
       <c r="N60">
-        <v>156.70400000000001</v>
+        <v>154.40700000000001</v>
       </c>
       <c r="O60" s="1">
-        <v>1.8136574074074077E-3</v>
+        <v>1.7870370370370368E-3</v>
       </c>
       <c r="P60">
-        <v>156.70400000000001</v>
+        <v>155.249</v>
       </c>
       <c r="Q60" s="1">
-        <v>1.8136574074074077E-3</v>
+        <v>1.7962962962962965E-3</v>
       </c>
       <c r="R60">
         <v>0</v>
@@ -13154,12 +12994,12 @@
         <v>0</v>
       </c>
       <c r="T60" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B61">
         <v>2029</v>
@@ -13171,25 +13011,25 @@
         <v>800</v>
       </c>
       <c r="E61">
-        <v>159.24299999999999</v>
+        <v>156.70400000000001</v>
       </c>
       <c r="F61" s="1">
-        <v>1.8425925925925927E-3</v>
+        <v>1.8136574074074077E-3</v>
       </c>
       <c r="G61">
-        <v>159.24299999999999</v>
+        <v>156.70400000000001</v>
       </c>
       <c r="N61">
-        <v>159.24299999999999</v>
+        <v>156.70400000000001</v>
       </c>
       <c r="O61" s="1">
-        <v>1.8425925925925927E-3</v>
+        <v>1.8136574074074077E-3</v>
       </c>
       <c r="P61">
-        <v>159.24299999999999</v>
+        <v>156.70400000000001</v>
       </c>
       <c r="Q61" s="1">
-        <v>1.8425925925925927E-3</v>
+        <v>1.8136574074074077E-3</v>
       </c>
       <c r="R61">
         <v>0</v>
@@ -13198,10 +13038,10 @@
         <v>0</v>
       </c>
       <c r="T61" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -13236,10 +13076,10 @@
         <v>0</v>
       </c>
       <c r="T62" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>27</v>
       </c>
@@ -13280,10 +13120,10 @@
         <v>0</v>
       </c>
       <c r="T63" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>36</v>
       </c>
@@ -13318,10 +13158,10 @@
         <v>0</v>
       </c>
       <c r="T64" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>30</v>
       </c>
@@ -13380,10 +13220,10 @@
         <v>26.657</v>
       </c>
       <c r="T65" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -13442,10 +13282,10 @@
         <v>54.31</v>
       </c>
       <c r="T66" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>39</v>
       </c>
@@ -13486,10 +13326,10 @@
         <v>10.52</v>
       </c>
       <c r="T67" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>34</v>
       </c>
@@ -13536,10 +13376,10 @@
         <v>35.405000000000001</v>
       </c>
       <c r="T68" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>32</v>
       </c>
@@ -13586,10 +13426,10 @@
         <v>45.237000000000002</v>
       </c>
       <c r="T69" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>45</v>
       </c>
@@ -13624,10 +13464,10 @@
         <v>0</v>
       </c>
       <c r="T70" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>46</v>
       </c>
@@ -13668,10 +13508,10 @@
         <v>0</v>
       </c>
       <c r="T71" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>47</v>
       </c>
@@ -13712,10 +13552,10 @@
         <v>0</v>
       </c>
       <c r="T72" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>41</v>
       </c>
@@ -13768,10 +13608,10 @@
         <v>31.05</v>
       </c>
       <c r="T73" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>43</v>
       </c>
@@ -13830,10 +13670,10 @@
         <v>59.97</v>
       </c>
       <c r="T74" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>48</v>
       </c>
@@ -13874,7 +13714,7 @@
         <v>0</v>
       </c>
       <c r="T75" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.35">
@@ -13906,10 +13746,10 @@
         <v>3.3460648148148152E-3</v>
       </c>
       <c r="T76" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>38</v>
       </c>
@@ -13944,10 +13784,10 @@
         <v>3.3668981481481484E-3</v>
       </c>
       <c r="T77" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>49</v>
       </c>
@@ -13976,10 +13816,10 @@
         <v>4.4270833333333332E-3</v>
       </c>
       <c r="T78" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>91</v>
       </c>
@@ -14014,10 +13854,10 @@
         <v>0</v>
       </c>
       <c r="T79" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>86</v>
       </c>
@@ -14058,16 +13898,16 @@
         <v>3.0844907407407405E-3</v>
       </c>
       <c r="R80" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="S80">
         <v>20.745999999999999</v>
       </c>
       <c r="T80" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>89</v>
       </c>
@@ -14108,16 +13948,16 @@
         <v>3.0497685185185181E-3</v>
       </c>
       <c r="R81" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="S81">
         <v>29.763000000000002</v>
       </c>
       <c r="T81" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="82" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>94</v>
       </c>
@@ -14158,16 +13998,16 @@
         <v>3.2939814814814815E-3</v>
       </c>
       <c r="R82" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="S82">
         <v>16.779</v>
       </c>
       <c r="T82" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="83" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>92</v>
       </c>
@@ -14208,16 +14048,16 @@
         <v>3.3229166666666667E-3</v>
       </c>
       <c r="R83" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="S83">
         <v>16.568999999999999</v>
       </c>
       <c r="T83" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>98</v>
       </c>
@@ -14258,16 +14098,16 @@
         <v>3.3703703703703704E-3</v>
       </c>
       <c r="R84" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="S84">
         <v>16.434000000000001</v>
       </c>
       <c r="T84" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -14308,16 +14148,16 @@
         <v>3.2916666666666667E-3</v>
       </c>
       <c r="R85" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="S85">
         <v>31.202000000000002</v>
       </c>
       <c r="T85" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="86" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>100</v>
       </c>
@@ -14358,16 +14198,16 @@
         <v>3.3136574074074075E-3</v>
       </c>
       <c r="R86" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="S86">
         <v>31.721</v>
       </c>
       <c r="T86" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="87" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>106</v>
       </c>
@@ -14408,16 +14248,16 @@
         <v>3.1597222222222222E-3</v>
       </c>
       <c r="R87" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="S87">
         <v>46.67</v>
       </c>
       <c r="T87" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="88" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>102</v>
       </c>
@@ -14458,18 +14298,18 @@
         <v>3.3379629629629627E-3</v>
       </c>
       <c r="R88" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="S88">
         <v>34.908999999999999</v>
       </c>
       <c r="T88" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="89" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B89">
         <v>2027</v>
@@ -14502,10 +14342,10 @@
         <v>0</v>
       </c>
       <c r="T89" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="90" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>109</v>
       </c>
@@ -14540,10 +14380,10 @@
         <v>0</v>
       </c>
       <c r="T90" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="91" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>104</v>
       </c>
@@ -14584,16 +14424,16 @@
         <v>3.363425925925926E-3</v>
       </c>
       <c r="R91" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="S91">
         <v>51.476999999999997</v>
       </c>
       <c r="T91" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="92" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>110</v>
       </c>
@@ -14634,16 +14474,16 @@
         <v>3.3692129629629627E-3</v>
       </c>
       <c r="R92" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="S92">
         <v>53.86</v>
       </c>
       <c r="T92" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="93" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>108</v>
       </c>
@@ -14684,10 +14524,10 @@
         <v>0</v>
       </c>
       <c r="T93" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="94" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>112</v>
       </c>
@@ -14722,16 +14562,16 @@
         <v>3.8668981481481484E-3</v>
       </c>
       <c r="R94" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="S94">
         <v>17.378</v>
       </c>
       <c r="T94" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="95" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>114</v>
       </c>
@@ -14766,18 +14606,18 @@
         <v>3.7256944444444447E-3</v>
       </c>
       <c r="R95" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="S95">
         <v>30.815000000000001</v>
       </c>
       <c r="T95" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="96" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B96">
         <v>2027</v>
@@ -14816,18 +14656,18 @@
         <v>3.8344907407407407E-3</v>
       </c>
       <c r="R96" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="S96">
         <v>39.646000000000001</v>
       </c>
       <c r="T96" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="97" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B97">
         <v>2027</v>
@@ -14866,18 +14706,18 @@
         <v>3.445601851851852E-3</v>
       </c>
       <c r="R97" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="S97">
         <v>77.646000000000001</v>
       </c>
       <c r="T97" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="98" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B98">
         <v>2027</v>
@@ -14910,12 +14750,12 @@
         <v>0</v>
       </c>
       <c r="T98" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="99" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B99">
         <v>2027</v>
@@ -14948,12 +14788,12 @@
         <v>0</v>
       </c>
       <c r="T99" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="100" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B100">
         <v>2027</v>
@@ -14986,12 +14826,12 @@
         <v>0</v>
       </c>
       <c r="T100" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="101" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B101">
         <v>2027</v>
@@ -15024,18 +14864,18 @@
         <v>3.7488425925925922E-3</v>
       </c>
       <c r="T101" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="102" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="102" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B102">
         <v>2028</v>
       </c>
       <c r="C102" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D102" t="s">
         <v>14</v>
@@ -15068,24 +14908,24 @@
         <v>3.3321759259259264E-3</v>
       </c>
       <c r="R102" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="S102">
         <v>8.2729999999999997</v>
       </c>
       <c r="T102" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="103" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B103">
         <v>2028</v>
       </c>
       <c r="C103" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D103" t="s">
         <v>14</v>
@@ -15124,18 +14964,18 @@
         <v>0</v>
       </c>
       <c r="T103" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="104" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="104" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B104">
         <v>2028</v>
       </c>
       <c r="C104" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D104" t="s">
         <v>14</v>
@@ -15168,24 +15008,24 @@
         <v>3.655092592592593E-3</v>
       </c>
       <c r="R104" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="S104">
         <v>16.376000000000001</v>
       </c>
       <c r="T104" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="105" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="105" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B105">
         <v>2028</v>
       </c>
       <c r="C105" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D105" t="s">
         <v>14</v>
@@ -15218,18 +15058,18 @@
         <v>0</v>
       </c>
       <c r="T105" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="106" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="106" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B106">
         <v>2028</v>
       </c>
       <c r="C106" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D106" t="s">
         <v>14</v>
@@ -15256,24 +15096,24 @@
         <v>3.2337962962962958E-3</v>
       </c>
       <c r="R106" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="S106">
         <v>42.189</v>
       </c>
       <c r="T106" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="107" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="107" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B107">
         <v>2028</v>
       </c>
       <c r="C107" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D107" t="s">
         <v>14</v>
@@ -15306,24 +15146,24 @@
         <v>3.8310185185185183E-3</v>
       </c>
       <c r="R107" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="S107">
         <v>10.643000000000001</v>
       </c>
       <c r="T107" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="108" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="108" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B108">
         <v>2028</v>
       </c>
       <c r="C108" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D108" t="s">
         <v>14</v>
@@ -15350,24 +15190,24 @@
         <v>3.6828703703703706E-3</v>
       </c>
       <c r="R108" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="S108">
         <v>17.855</v>
       </c>
       <c r="T108" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="109" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="109" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B109">
         <v>2028</v>
       </c>
       <c r="C109" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D109" t="s">
         <v>14</v>
@@ -15394,18 +15234,18 @@
         <v>0</v>
       </c>
       <c r="T109" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="110" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="110" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B110">
         <v>2028</v>
       </c>
       <c r="C110" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D110" t="s">
         <v>14</v>
@@ -15432,24 +15272,24 @@
         <v>3.9733796296296297E-3</v>
       </c>
       <c r="R110" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="S110">
         <v>20.46</v>
       </c>
       <c r="T110" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="111" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="111" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B111">
         <v>2028</v>
       </c>
       <c r="C111" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D111" t="s">
         <v>14</v>
@@ -15482,10 +15322,10 @@
         <v>0</v>
       </c>
       <c r="T111" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="112" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="112" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>12</v>
       </c>
@@ -15526,10 +15366,10 @@
         <v>0</v>
       </c>
       <c r="T112" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="113" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="113" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>15</v>
       </c>
@@ -15570,10 +15410,10 @@
         <v>0</v>
       </c>
       <c r="T113" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="114" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="114" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>16</v>
       </c>
@@ -15608,10 +15448,10 @@
         <v>0</v>
       </c>
       <c r="T114" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="115" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="115" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>17</v>
       </c>
@@ -15652,10 +15492,10 @@
         <v>0</v>
       </c>
       <c r="T115" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="116" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="116" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -15696,10 +15536,10 @@
         <v>0</v>
       </c>
       <c r="T116" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="117" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="117" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>19</v>
       </c>
@@ -15740,10 +15580,10 @@
         <v>0</v>
       </c>
       <c r="T117" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="118" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="118" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>20</v>
       </c>
@@ -15778,10 +15618,10 @@
         <v>0</v>
       </c>
       <c r="T118" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="119" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="119" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>21</v>
       </c>
@@ -15816,10 +15656,10 @@
         <v>0</v>
       </c>
       <c r="T119" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="120" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="120" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>22</v>
       </c>
@@ -15854,10 +15694,10 @@
         <v>0</v>
       </c>
       <c r="T120" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="121" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="121" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>23</v>
       </c>
@@ -15892,10 +15732,10 @@
         <v>0</v>
       </c>
       <c r="T121" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="122" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="122" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>24</v>
       </c>
@@ -15930,10 +15770,10 @@
         <v>0</v>
       </c>
       <c r="T122" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="123" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="123" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>25</v>
       </c>
@@ -15968,10 +15808,10 @@
         <v>0</v>
       </c>
       <c r="T123" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="124" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="124" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>26</v>
       </c>
@@ -16006,10 +15846,10 @@
         <v>0</v>
       </c>
       <c r="T124" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="125" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="125" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>27</v>
       </c>
@@ -16044,10 +15884,10 @@
         <v>0</v>
       </c>
       <c r="T125" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="126" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="126" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>30</v>
       </c>
@@ -16100,10 +15940,10 @@
         <v>59.16</v>
       </c>
       <c r="T126" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="127" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="127" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>39</v>
       </c>
@@ -16144,10 +15984,10 @@
         <v>0.92</v>
       </c>
       <c r="T127" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="128" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="128" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>32</v>
       </c>
@@ -16200,10 +16040,10 @@
         <v>33.700000000000003</v>
       </c>
       <c r="T128" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="129" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="129" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>34</v>
       </c>
@@ -16256,10 +16096,10 @@
         <v>53.96</v>
       </c>
       <c r="T129" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="130" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="130" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>28</v>
       </c>
@@ -16312,10 +16152,10 @@
         <v>122.97499999999999</v>
       </c>
       <c r="T130" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="131" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="131" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>41</v>
       </c>
@@ -16362,10 +16202,10 @@
         <v>39.96</v>
       </c>
       <c r="T131" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="132" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="132" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>45</v>
       </c>
@@ -16400,10 +16240,10 @@
         <v>0</v>
       </c>
       <c r="T132" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="133" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="133" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>47</v>
       </c>
@@ -16444,10 +16284,10 @@
         <v>0</v>
       </c>
       <c r="T133" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="134" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="134" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>46</v>
       </c>
@@ -16482,10 +16322,10 @@
         <v>0</v>
       </c>
       <c r="T134" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="135" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="135" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>43</v>
       </c>
@@ -16538,10 +16378,10 @@
         <v>121.3</v>
       </c>
       <c r="T135" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="136" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="136" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>48</v>
       </c>
@@ -16576,10 +16416,10 @@
         <v>0</v>
       </c>
       <c r="T136" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="137" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="137" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>54</v>
       </c>
@@ -16614,10 +16454,10 @@
         <v>0</v>
       </c>
       <c r="T137" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="138" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="138" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>38</v>
       </c>
@@ -16652,10 +16492,10 @@
         <v>7.8935185185185185E-3</v>
       </c>
       <c r="T138" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="139" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="139" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>86</v>
       </c>
@@ -16696,16 +16536,16 @@
         <v>6.5740740740740733E-3</v>
       </c>
       <c r="R139" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="S139">
         <v>44.54</v>
       </c>
       <c r="T139" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="140" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="140" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>91</v>
       </c>
@@ -16740,10 +16580,10 @@
         <v>0</v>
       </c>
       <c r="T140" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="141" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="141" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>89</v>
       </c>
@@ -16784,16 +16624,16 @@
         <v>6.5636574074074069E-3</v>
       </c>
       <c r="R141" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S141">
         <v>68.39</v>
       </c>
       <c r="T141" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="142" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="142" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>94</v>
       </c>
@@ -16834,16 +16674,16 @@
         <v>7.0023148148148154E-3</v>
       </c>
       <c r="R142" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="S142">
         <v>32.31</v>
       </c>
       <c r="T142" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="143" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="143" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>106</v>
       </c>
@@ -16884,16 +16724,16 @@
         <v>6.8240740740740735E-3</v>
       </c>
       <c r="R143" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="S143">
         <v>67.91</v>
       </c>
       <c r="T143" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="144" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="144" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>92</v>
       </c>
@@ -16934,16 +16774,16 @@
         <v>7.4178240740740741E-3</v>
       </c>
       <c r="R144" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="S144">
         <v>23.37</v>
       </c>
       <c r="T144" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="145" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="145" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>96</v>
       </c>
@@ -16984,16 +16824,16 @@
         <v>7.6539351851851846E-3</v>
       </c>
       <c r="R145" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="S145">
         <v>17.82</v>
       </c>
       <c r="T145" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="146" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="146" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>98</v>
       </c>
@@ -17034,16 +16874,16 @@
         <v>7.533564814814815E-3</v>
       </c>
       <c r="R146" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="S146">
         <v>35.320999999999998</v>
       </c>
       <c r="T146" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="147" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="147" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>102</v>
       </c>
@@ -17084,16 +16924,16 @@
         <v>7.2546296296296308E-3</v>
       </c>
       <c r="R147" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="S147">
         <v>62.17</v>
       </c>
       <c r="T147" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="148" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="148" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>100</v>
       </c>
@@ -17134,16 +16974,16 @@
         <v>7.1203703703703707E-3</v>
       </c>
       <c r="R148" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="S148">
         <v>74.316999999999993</v>
       </c>
       <c r="T148" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="149" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="149" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>110</v>
       </c>
@@ -17184,18 +17024,18 @@
         <v>7.2094907407407394E-3</v>
       </c>
       <c r="R149" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="S149">
         <v>84.84</v>
       </c>
       <c r="T149" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="150" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="150" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B150">
         <v>2027</v>
@@ -17234,16 +17074,16 @@
         <v>7.4641203703703701E-3</v>
       </c>
       <c r="R150" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="S150">
         <v>85.33</v>
       </c>
       <c r="T150" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="151" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="151" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>109</v>
       </c>
@@ -17278,10 +17118,10 @@
         <v>0</v>
       </c>
       <c r="T151" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="152" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="152" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>104</v>
       </c>
@@ -17316,16 +17156,16 @@
         <v>7.5162037037037046E-3</v>
       </c>
       <c r="R152" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="S152">
         <v>96.165000000000006</v>
       </c>
       <c r="T152" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="153" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="153" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>108</v>
       </c>
@@ -17360,10 +17200,10 @@
         <v>0</v>
       </c>
       <c r="T153" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="154" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="154" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>114</v>
       </c>
@@ -17398,18 +17238,18 @@
         <v>8.3784722222222229E-3</v>
       </c>
       <c r="R154" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="S154">
         <v>50.2</v>
       </c>
       <c r="T154" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="155" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="155" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B155">
         <v>2027</v>
@@ -17442,16 +17282,16 @@
         <v>8.1689814814814819E-3</v>
       </c>
       <c r="R155" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="S155">
         <v>71.8</v>
       </c>
       <c r="T155" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="156" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="156" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>112</v>
       </c>
@@ -17486,18 +17326,18 @@
         <v>8.3125000000000004E-3</v>
       </c>
       <c r="R156" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="S156">
         <v>69.33</v>
       </c>
       <c r="T156" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="157" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="157" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B157">
         <v>2027</v>
@@ -17530,18 +17370,18 @@
         <v>9.2175925925925932E-3</v>
       </c>
       <c r="R157" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="S157">
         <v>131.46</v>
       </c>
       <c r="T157" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="158" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="158" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B158">
         <v>2027</v>
@@ -17574,12 +17414,12 @@
         <v>0</v>
       </c>
       <c r="T158" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="159" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="159" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B159">
         <v>2027</v>
@@ -17606,18 +17446,18 @@
         <v>8.6388888888888887E-3</v>
       </c>
       <c r="T159" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="160" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="160" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B160">
         <v>2028</v>
       </c>
       <c r="C160" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D160" t="s">
         <v>50</v>
@@ -17644,24 +17484,24 @@
         <v>7.0856481481481473E-3</v>
       </c>
       <c r="R160" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="S160">
         <v>5.1479999999999997</v>
       </c>
       <c r="T160" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="161" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="161" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B161">
         <v>2028</v>
       </c>
       <c r="C161" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D161" t="s">
         <v>50</v>
@@ -17688,24 +17528,24 @@
         <v>7.363425925925926E-3</v>
       </c>
       <c r="R161" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="S161">
         <v>11.185</v>
       </c>
       <c r="T161" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="162" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="162" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B162">
         <v>2028</v>
       </c>
       <c r="C162" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D162" t="s">
         <v>50</v>
@@ -17732,24 +17572,24 @@
         <v>7.1793981481481474E-3</v>
       </c>
       <c r="R162" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="S162">
         <v>37.823</v>
       </c>
       <c r="T162" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="163" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="163" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B163">
         <v>2028</v>
       </c>
       <c r="C163" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D163" t="s">
         <v>50</v>
@@ -17776,24 +17616,24 @@
         <v>7.2511574074074076E-3</v>
       </c>
       <c r="R163" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="S163">
         <v>43.6</v>
       </c>
       <c r="T163" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="164" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="164" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B164">
         <v>2028</v>
       </c>
       <c r="C164" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D164" t="s">
         <v>50</v>
@@ -17820,24 +17660,24 @@
         <v>7.84375E-3</v>
       </c>
       <c r="R164" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="S164">
         <v>34.9</v>
       </c>
       <c r="T164" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="165" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="165" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B165">
         <v>2028</v>
       </c>
       <c r="C165" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D165" t="s">
         <v>50</v>
@@ -17864,18 +17704,18 @@
         <v>0</v>
       </c>
       <c r="T165" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="166" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="166" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B166">
         <v>2028</v>
       </c>
       <c r="C166" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D166" t="s">
         <v>50</v>
@@ -17908,18 +17748,18 @@
         <v>0</v>
       </c>
       <c r="T166" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="167" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="167" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B167">
         <v>2028</v>
       </c>
       <c r="C167" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D167" t="s">
         <v>50</v>
@@ -17952,18 +17792,18 @@
         <v>0</v>
       </c>
       <c r="T167" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="168" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="168" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B168">
         <v>2028</v>
       </c>
       <c r="C168" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D168" t="s">
         <v>50</v>
@@ -17984,10 +17824,10 @@
         <v>8.4328703703703701E-3</v>
       </c>
       <c r="T168" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="169" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="169" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>12</v>
       </c>
@@ -18022,10 +17862,10 @@
         <v>0</v>
       </c>
       <c r="T169" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="170" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="170" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>16</v>
       </c>
@@ -18060,10 +17900,10 @@
         <v>0</v>
       </c>
       <c r="T170" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="171" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="171" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>17</v>
       </c>
@@ -18098,10 +17938,10 @@
         <v>0</v>
       </c>
       <c r="T171" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="172" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="172" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -18136,10 +17976,10 @@
         <v>0</v>
       </c>
       <c r="T172" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="173" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="173" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>15</v>
       </c>
@@ -18174,10 +18014,10 @@
         <v>0</v>
       </c>
       <c r="T173" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="174" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="174" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>19</v>
       </c>
@@ -18212,10 +18052,10 @@
         <v>0</v>
       </c>
       <c r="T174" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="175" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="175" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>20</v>
       </c>
@@ -18250,10 +18090,10 @@
         <v>0</v>
       </c>
       <c r="T175" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="176" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="176" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>24</v>
       </c>
@@ -18288,10 +18128,10 @@
         <v>0</v>
       </c>
       <c r="T176" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="177" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="177" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>22</v>
       </c>
@@ -18326,10 +18166,10 @@
         <v>0</v>
       </c>
       <c r="T177" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="178" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="178" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>23</v>
       </c>
@@ -18364,10 +18204,10 @@
         <v>0</v>
       </c>
       <c r="T178" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="179" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="179" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>25</v>
       </c>
@@ -18402,10 +18242,10 @@
         <v>0</v>
       </c>
       <c r="T179" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="180" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="180" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>27</v>
       </c>
@@ -18440,10 +18280,10 @@
         <v>0</v>
       </c>
       <c r="T180" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="181" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="181" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>30</v>
       </c>
@@ -18496,10 +18336,10 @@
         <v>163.19999999999999</v>
       </c>
       <c r="T181" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="182" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="182" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>34</v>
       </c>
@@ -18552,10 +18392,10 @@
         <v>125.5</v>
       </c>
       <c r="T182" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="183" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="183" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>28</v>
       </c>
@@ -18608,10 +18448,10 @@
         <v>223.9</v>
       </c>
       <c r="T183" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="184" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="184" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>39</v>
       </c>
@@ -18664,10 +18504,10 @@
         <v>92.3</v>
       </c>
       <c r="T184" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="185" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="185" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>46</v>
       </c>
@@ -18708,10 +18548,10 @@
         <v>0</v>
       </c>
       <c r="T185" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="186" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="186" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>41</v>
       </c>
@@ -18764,10 +18604,10 @@
         <v>175.1</v>
       </c>
       <c r="T186" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="187" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="187" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>76</v>
       </c>
@@ -18802,10 +18642,10 @@
         <v>0</v>
       </c>
       <c r="T187" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="188" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="188" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>49</v>
       </c>
@@ -18846,10 +18686,10 @@
         <v>0</v>
       </c>
       <c r="T188" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="189" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="189" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>77</v>
       </c>
@@ -18884,10 +18724,10 @@
         <v>0</v>
       </c>
       <c r="T189" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="190" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="190" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>48</v>
       </c>
@@ -18922,10 +18762,10 @@
         <v>0</v>
       </c>
       <c r="T190" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="191" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="191" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>54</v>
       </c>
@@ -18960,10 +18800,10 @@
         <v>0</v>
       </c>
       <c r="T191" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="192" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="192" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>78</v>
       </c>
@@ -18998,10 +18838,10 @@
         <v>0</v>
       </c>
       <c r="T192" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="193" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>79</v>
       </c>
@@ -19036,7 +18876,7 @@
         <v>0</v>
       </c>
       <c r="T193" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="194" spans="1:20" x14ac:dyDescent="0.35">
@@ -19068,10 +18908,10 @@
         <v>1.1369212962962963E-2</v>
       </c>
       <c r="T194" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="195" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>38</v>
       </c>
@@ -19100,10 +18940,10 @@
         <v>1.2908564814814815E-2</v>
       </c>
       <c r="T195" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="196" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="196" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>43</v>
       </c>
@@ -19138,10 +18978,10 @@
         <v>1.3682870370370371E-2</v>
       </c>
       <c r="T196" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="197" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="197" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>91</v>
       </c>
@@ -19176,10 +19016,10 @@
         <v>0</v>
       </c>
       <c r="T197" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="198" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="198" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>86</v>
       </c>
@@ -19220,16 +19060,16 @@
         <v>1.0825231481481483E-2</v>
       </c>
       <c r="R198" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="S198">
         <v>90.7</v>
       </c>
       <c r="T198" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="199" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="199" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>94</v>
       </c>
@@ -19270,16 +19110,16 @@
         <v>1.1398148148148149E-2</v>
       </c>
       <c r="R199" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="S199">
         <v>97.8</v>
       </c>
       <c r="T199" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="200" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="200" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>92</v>
       </c>
@@ -19320,16 +19160,16 @@
         <v>1.2026620370370373E-2</v>
       </c>
       <c r="R200" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="S200">
         <v>60.4</v>
       </c>
       <c r="T200" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="201" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="201" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>89</v>
       </c>
@@ -19370,16 +19210,16 @@
         <v>1.1314814814814814E-2</v>
       </c>
       <c r="R201" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="S201">
         <v>127</v>
       </c>
       <c r="T201" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="202" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="202" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>109</v>
       </c>
@@ -19414,10 +19254,10 @@
         <v>0</v>
       </c>
       <c r="T202" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="203" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="203" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>106</v>
       </c>
@@ -19458,16 +19298,16 @@
         <v>1.160763888888889E-2</v>
       </c>
       <c r="R203" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="S203">
         <v>108.99</v>
       </c>
       <c r="T203" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="204" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="204" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>102</v>
       </c>
@@ -19514,10 +19354,10 @@
         <v>47.5</v>
       </c>
       <c r="T204" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="205" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="205" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>96</v>
       </c>
@@ -19558,16 +19398,16 @@
         <v>1.2273148148148146E-2</v>
       </c>
       <c r="R205" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="S205">
         <v>100.1</v>
       </c>
       <c r="T205" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="206" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="206" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>104</v>
       </c>
@@ -19614,12 +19454,12 @@
         <v>113.5</v>
       </c>
       <c r="T206" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="207" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="207" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B207">
         <v>2027</v>
@@ -19658,10 +19498,10 @@
         <v>0</v>
       </c>
       <c r="T207" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="208" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="208" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>110</v>
       </c>
@@ -19702,18 +19542,18 @@
         <v>1.2379629629629631E-2</v>
       </c>
       <c r="R208" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="S208">
         <v>115.4</v>
       </c>
       <c r="T208" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="209" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="209" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B209">
         <v>2027</v>
@@ -19752,16 +19592,16 @@
         <v>1.3876157407407406E-2</v>
       </c>
       <c r="R209" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="S209">
         <v>19.399999999999999</v>
       </c>
       <c r="T209" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="210" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="210" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>98</v>
       </c>
@@ -19802,18 +19642,18 @@
         <v>1.2034722222222223E-2</v>
       </c>
       <c r="R210" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="S210">
         <v>186.2</v>
       </c>
       <c r="T210" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="211" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="211" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B211">
         <v>2027</v>
@@ -19852,18 +19692,18 @@
         <v>1.2179398148148148E-2</v>
       </c>
       <c r="R211" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="S211">
         <v>197.2</v>
       </c>
       <c r="T211" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="212" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="212" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B212">
         <v>2027</v>
@@ -19902,16 +19742,16 @@
         <v>1.4777777777777779E-2</v>
       </c>
       <c r="R212" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="S212">
         <v>22.2</v>
       </c>
       <c r="T212" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="213" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="213" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>100</v>
       </c>
@@ -19952,16 +19792,16 @@
         <v>1.1471064814814816E-2</v>
       </c>
       <c r="R213" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="S213">
         <v>322.8</v>
       </c>
       <c r="T213" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="214" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="214" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>114</v>
       </c>
@@ -20002,16 +19842,16 @@
         <v>1.3539351851851851E-2</v>
       </c>
       <c r="R214" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="S214">
         <v>153.30000000000001</v>
       </c>
       <c r="T214" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="215" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="215" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>108</v>
       </c>
@@ -20052,18 +19892,18 @@
         <v>1.2438657407407407E-2</v>
       </c>
       <c r="R215" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="S215">
         <v>257.89999999999998</v>
       </c>
       <c r="T215" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="216" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="216" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B216">
         <v>2027</v>
@@ -20096,10 +19936,10 @@
         <v>0</v>
       </c>
       <c r="T216" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="217" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="217" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>112</v>
       </c>
@@ -20140,18 +19980,18 @@
         <v>1.2388888888888889E-2</v>
       </c>
       <c r="R217" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="S217">
         <v>384.8</v>
       </c>
       <c r="T217" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="218" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="218" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B218">
         <v>2027</v>
@@ -20196,12 +20036,12 @@
         <v>288</v>
       </c>
       <c r="T218" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="219" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="219" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B219">
         <v>2027</v>
@@ -20234,12 +20074,12 @@
         <v>1.4002314814814815E-2</v>
       </c>
       <c r="T219" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="220" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="220" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B220">
         <v>2027</v>
@@ -20266,18 +20106,18 @@
         <v>1.4684027777777777E-2</v>
       </c>
       <c r="T220" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="221" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="221" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B221">
         <v>2028</v>
       </c>
       <c r="C221" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D221" t="s">
         <v>55</v>
@@ -20304,24 +20144,24 @@
         <v>1.1395833333333334E-2</v>
       </c>
       <c r="R221" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="S221">
         <v>58</v>
       </c>
       <c r="T221" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="222" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="222" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B222">
         <v>2028</v>
       </c>
       <c r="C222" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D222" t="s">
         <v>55</v>
@@ -20348,24 +20188,24 @@
         <v>1.1818287037037037E-2</v>
       </c>
       <c r="R222" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="S222">
         <v>55.9</v>
       </c>
       <c r="T222" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="223" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="223" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B223">
         <v>2028</v>
       </c>
       <c r="C223" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D223" t="s">
         <v>55</v>
@@ -20398,18 +20238,18 @@
         <v>8</v>
       </c>
       <c r="T223" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="224" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="224" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B224">
         <v>2028</v>
       </c>
       <c r="C224" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D224" t="s">
         <v>55</v>
@@ -20436,24 +20276,24 @@
         <v>1.2068287037037037E-2</v>
       </c>
       <c r="R224" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="S224">
         <v>53.3</v>
       </c>
       <c r="T224" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="225" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="225" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B225">
         <v>2028</v>
       </c>
       <c r="C225" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D225" t="s">
         <v>55</v>
@@ -20480,18 +20320,18 @@
         <v>0</v>
       </c>
       <c r="T225" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="226" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="226" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B226">
         <v>2028</v>
       </c>
       <c r="C226" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D226" t="s">
         <v>55</v>
@@ -20518,24 +20358,24 @@
         <v>1.3283564814814816E-2</v>
       </c>
       <c r="R226" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="S226">
         <v>21.3</v>
       </c>
       <c r="T226" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="227" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="227" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B227">
         <v>2028</v>
       </c>
       <c r="C227" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D227" t="s">
         <v>55</v>
@@ -20562,24 +20402,24 @@
         <v>1.3644675925925926E-2</v>
       </c>
       <c r="R227" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="S227">
         <v>5.2</v>
       </c>
       <c r="T227" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="228" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="228" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B228">
         <v>2028</v>
       </c>
       <c r="C228" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D228" t="s">
         <v>55</v>
@@ -20612,18 +20452,18 @@
         <v>50</v>
       </c>
       <c r="T228" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="229" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="229" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B229">
         <v>2028</v>
       </c>
       <c r="C229" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D229" t="s">
         <v>55</v>
@@ -20650,24 +20490,24 @@
         <v>1.3021990740740738E-2</v>
       </c>
       <c r="R229" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="S229">
         <v>66.2</v>
       </c>
       <c r="T229" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="230" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="230" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B230">
         <v>2028</v>
       </c>
       <c r="C230" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D230" t="s">
         <v>55</v>
@@ -20694,24 +20534,24 @@
         <v>1.3306712962962963E-2</v>
       </c>
       <c r="R230" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="S230">
         <v>59.1</v>
       </c>
       <c r="T230" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="231" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="231" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B231">
         <v>2028</v>
       </c>
       <c r="C231" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D231" t="s">
         <v>55</v>
@@ -20738,16 +20578,16 @@
         <v>1.4431712962962964E-2</v>
       </c>
       <c r="R231" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="S231">
         <v>216.7</v>
       </c>
       <c r="T231" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="232" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="232" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>12</v>
       </c>
@@ -20782,10 +20622,10 @@
         <v>0</v>
       </c>
       <c r="T232" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="233" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="233" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>15</v>
       </c>
@@ -20820,10 +20660,10 @@
         <v>0</v>
       </c>
       <c r="T233" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="234" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="234" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>17</v>
       </c>
@@ -20858,10 +20698,10 @@
         <v>0</v>
       </c>
       <c r="T234" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="235" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="235" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>18</v>
       </c>
@@ -20896,10 +20736,10 @@
         <v>0</v>
       </c>
       <c r="T235" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="236" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="236" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>21</v>
       </c>
@@ -20934,10 +20774,10 @@
         <v>0</v>
       </c>
       <c r="T236" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="237" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="237" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>22</v>
       </c>
@@ -20972,10 +20812,10 @@
         <v>0</v>
       </c>
       <c r="T237" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="238" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="238" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>20</v>
       </c>
@@ -21010,10 +20850,10 @@
         <v>0</v>
       </c>
       <c r="T238" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="239" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="239" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>24</v>
       </c>
@@ -21048,10 +20888,10 @@
         <v>0</v>
       </c>
       <c r="T239" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="240" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="240" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>19</v>
       </c>
@@ -21086,10 +20926,10 @@
         <v>0</v>
       </c>
       <c r="T240" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="241" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="241" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>23</v>
       </c>
@@ -21124,10 +20964,10 @@
         <v>0</v>
       </c>
       <c r="T241" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="242" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="242" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>27</v>
       </c>
@@ -21162,17 +21002,10 @@
         <v>0</v>
       </c>
       <c r="T242" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T242" xr:uid="{5618C841-8876-4D0C-80DF-C05F2AAF82DF}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Marshall Wilson"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/progression_validation/freshman_senior_progression_summary.xlsx
+++ b/progression_validation/freshman_senior_progression_summary.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/28edc9c7244f203a/StX_XC_Track/track_report_site/reports_simple/progression_validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{FD0781AF-2203-462A-BB5A-3D7DB617690B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3369E6ED-B199-4C31-ADC9-12B3E989601A}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{FD0781AF-2203-462A-BB5A-3D7DB617690B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB6EB2A6-9913-46D1-9E42-4D0B942D09DB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D50CECB0-75FC-479B-95E7-BB327A7E9C00}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D50CECB0-75FC-479B-95E7-BB327A7E9C00}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary_pivot" sheetId="2" r:id="rId1"/>
     <sheet name="Raw_data" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Raw_data!$A$1:$T$242</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId3"/>
+    <pivotCache cacheId="345" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,15 +39,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="223">
   <si>
     <t>class_group</t>
   </si>
@@ -725,7 +723,7 @@
     <numFmt numFmtId="164" formatCode="m:ss"/>
     <numFmt numFmtId="165" formatCode="m\.ss"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -861,7 +859,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1041,8 +1039,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1157,6 +1161,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1202,7 +1215,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -1211,6 +1224,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1256,24 +1272,34 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="26">
     <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m\.ss"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1304,7 +1330,94 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="m\.ss"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="28" formatCode="mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="28" formatCode="mm:ss"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="m:ss"/>
@@ -1316,10 +1429,7 @@
       <numFmt numFmtId="164" formatCode="m:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
+      <numFmt numFmtId="165" formatCode="m\.ss"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -7097,7 +7207,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C40C4673-9275-42B8-90A8-EA84E10FDE10}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C40C4673-9275-42B8-90A8-EA84E10FDE10}" name="PivotTable1" cacheId="345" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="A4:I207" firstHeaderRow="1" firstDataRow="2" firstDataCol="3" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="23">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="ascending" defaultSubtotal="0">
@@ -8360,7 +8470,7 @@
     <dataField name="Sum of freshman_sort" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="15">
+    <format dxfId="20">
       <pivotArea outline="0" fieldPosition="0">
         <references count="4">
           <reference field="4294967294" count="1" selected="0">
@@ -8378,7 +8488,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
+    <format dxfId="21">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -8387,7 +8497,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="22">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -8396,7 +8506,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="23">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -8405,7 +8515,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="11">
+    <format dxfId="24">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -8414,7 +8524,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="10">
+    <format dxfId="25">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -8754,7 +8864,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C822FE-4873-461A-B0D5-CE2B07A9E622}">
   <dimension ref="A1:I207"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
@@ -8768,7 +8878,7 @@
     <col min="10" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -8776,7 +8886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -8784,12 +8894,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="D4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -8818,7 +8928,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -8843,7 +8953,7 @@
         <v>285.04399999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="B7" t="s">
         <v>16</v>
       </c>
@@ -8863,7 +8973,7 @@
         <v>286.41000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -8887,7 +8997,7 @@
         <v>287.2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -8907,7 +9017,7 @@
         <v>287.95</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="B10" t="s">
         <v>19</v>
       </c>
@@ -8927,7 +9037,7 @@
         <v>291.54199999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="B11" t="s">
         <v>20</v>
       </c>
@@ -8947,7 +9057,7 @@
         <v>293.22500000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="B12" t="s">
         <v>21</v>
       </c>
@@ -8971,7 +9081,7 @@
         <v>293.29899999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="B13" t="s">
         <v>22</v>
       </c>
@@ -8993,7 +9103,7 @@
         <v>296.63799999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="B14" t="s">
         <v>23</v>
       </c>
@@ -9019,7 +9129,7 @@
         <v>297.01</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="B15" t="s">
         <v>24</v>
       </c>
@@ -9045,7 +9155,7 @@
         <v>299.74</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="B16" t="s">
         <v>25</v>
       </c>
@@ -9069,7 +9179,7 @@
         <v>301.363</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9">
       <c r="B17" t="s">
         <v>26</v>
       </c>
@@ -9093,7 +9203,7 @@
         <v>303.62700000000001</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9">
       <c r="B18" t="s">
         <v>27</v>
       </c>
@@ -9115,7 +9225,7 @@
         <v>304.286</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9">
       <c r="B19" t="s">
         <v>28</v>
       </c>
@@ -9137,7 +9247,7 @@
         <v>304.63</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9">
       <c r="B20" t="s">
         <v>29</v>
       </c>
@@ -9157,7 +9267,7 @@
         <v>307.44</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9">
       <c r="B21" t="s">
         <v>30</v>
       </c>
@@ -9181,7 +9291,7 @@
         <v>307.661</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9">
       <c r="B22" t="s">
         <v>31</v>
       </c>
@@ -9205,7 +9315,7 @@
         <v>308.98099999999999</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9">
       <c r="B23" t="s">
         <v>32</v>
       </c>
@@ -9225,7 +9335,7 @@
         <v>310.56599999999997</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9">
       <c r="B24" t="s">
         <v>33</v>
       </c>
@@ -9247,7 +9357,7 @@
         <v>311.89</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9">
       <c r="B25" t="s">
         <v>34</v>
       </c>
@@ -9271,7 +9381,7 @@
         <v>315.553</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9">
       <c r="B26" t="s">
         <v>35</v>
       </c>
@@ -9295,7 +9405,7 @@
         <v>318.04300000000001</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9">
       <c r="B27" t="s">
         <v>36</v>
       </c>
@@ -9319,7 +9429,7 @@
         <v>318.74700000000001</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9">
       <c r="B28" t="s">
         <v>37</v>
       </c>
@@ -9343,7 +9453,7 @@
         <v>319.7</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9">
       <c r="B29" t="s">
         <v>38</v>
       </c>
@@ -9365,7 +9475,7 @@
         <v>321.54300000000001</v>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:9">
       <c r="B30" t="s">
         <v>39</v>
       </c>
@@ -9389,7 +9499,7 @@
         <v>323.346</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:9">
       <c r="B31" t="s">
         <v>40</v>
       </c>
@@ -9411,7 +9521,7 @@
         <v>331.04500000000002</v>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9">
       <c r="B32" t="s">
         <v>41</v>
       </c>
@@ -9435,7 +9545,7 @@
         <v>333.72</v>
       </c>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:9">
       <c r="B33" t="s">
         <v>42</v>
       </c>
@@ -9455,7 +9565,7 @@
         <v>335.142</v>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:9">
       <c r="B34" t="s">
         <v>43</v>
       </c>
@@ -9477,7 +9587,7 @@
         <v>336.02499999999998</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9">
       <c r="B35" t="s">
         <v>44</v>
       </c>
@@ -9497,7 +9607,7 @@
         <v>341.75900000000001</v>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9">
       <c r="B36" t="s">
         <v>45</v>
       </c>
@@ -9521,7 +9631,7 @@
         <v>342.10399999999998</v>
       </c>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9">
       <c r="B37" t="s">
         <v>46</v>
       </c>
@@ -9541,7 +9651,7 @@
         <v>343.30900000000003</v>
       </c>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:9">
       <c r="B38" t="s">
         <v>47</v>
       </c>
@@ -9565,7 +9675,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9">
       <c r="B39" t="s">
         <v>48</v>
       </c>
@@ -9587,7 +9697,7 @@
         <v>345.358</v>
       </c>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9">
       <c r="B40" t="s">
         <v>49</v>
       </c>
@@ -9607,7 +9717,7 @@
         <v>347.14100000000002</v>
       </c>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9">
       <c r="B41" t="s">
         <v>50</v>
       </c>
@@ -9627,7 +9737,7 @@
         <v>348.47300000000001</v>
       </c>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9">
       <c r="B42" t="s">
         <v>51</v>
       </c>
@@ -9647,7 +9757,7 @@
         <v>349.51299999999998</v>
       </c>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9">
       <c r="B43" t="s">
         <v>52</v>
       </c>
@@ -9669,7 +9779,7 @@
         <v>351.44299999999998</v>
       </c>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9">
       <c r="B44" t="s">
         <v>53</v>
       </c>
@@ -9691,7 +9801,7 @@
         <v>352.70800000000003</v>
       </c>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9">
       <c r="B45" t="s">
         <v>54</v>
       </c>
@@ -9711,7 +9821,7 @@
         <v>356.565</v>
       </c>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9">
       <c r="B46" t="s">
         <v>55</v>
       </c>
@@ -9731,7 +9841,7 @@
         <v>359.07</v>
       </c>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9">
       <c r="B47" t="s">
         <v>56</v>
       </c>
@@ -9753,7 +9863,7 @@
         <v>363.714</v>
       </c>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:9">
       <c r="B48" t="s">
         <v>57</v>
       </c>
@@ -9779,7 +9889,7 @@
         <v>370.02</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9">
       <c r="B49" t="s">
         <v>58</v>
       </c>
@@ -9803,7 +9913,7 @@
         <v>370.899</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9">
       <c r="B50" t="s">
         <v>59</v>
       </c>
@@ -9827,7 +9937,7 @@
         <v>375.32100000000003</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9">
       <c r="B51" t="s">
         <v>60</v>
       </c>
@@ -9849,7 +9959,7 @@
         <v>376.50599999999997</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9">
       <c r="B52" t="s">
         <v>61</v>
       </c>
@@ -9869,7 +9979,7 @@
         <v>392.5</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9">
       <c r="B53" t="s">
         <v>62</v>
       </c>
@@ -9889,7 +9999,7 @@
         <v>420.24900000000002</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9">
       <c r="B54" t="s">
         <v>63</v>
       </c>
@@ -9909,7 +10019,7 @@
         <v>476.8</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9">
       <c r="B55" t="s">
         <v>64</v>
       </c>
@@ -9931,7 +10041,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9">
       <c r="B56" t="s">
         <v>65</v>
       </c>
@@ -9953,7 +10063,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9">
       <c r="B57" t="s">
         <v>66</v>
       </c>
@@ -9973,7 +10083,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9">
       <c r="A58" t="s">
         <v>67</v>
       </c>
@@ -10000,7 +10110,7 @@
         <v>612.53</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9">
       <c r="B59" t="s">
         <v>15</v>
       </c>
@@ -10022,7 +10132,7 @@
         <v>617.29999999999995</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9">
       <c r="B60" t="s">
         <v>21</v>
       </c>
@@ -10046,7 +10156,7 @@
         <v>635.49</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9">
       <c r="B61" t="s">
         <v>25</v>
       </c>
@@ -10070,7 +10180,7 @@
         <v>637.30999999999995</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9">
       <c r="B62" t="s">
         <v>16</v>
       </c>
@@ -10090,7 +10200,7 @@
         <v>642.70000000000005</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9">
       <c r="B63" t="s">
         <v>22</v>
       </c>
@@ -10112,7 +10222,7 @@
         <v>647.38499999999999</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9">
       <c r="B64" t="s">
         <v>19</v>
       </c>
@@ -10132,7 +10242,7 @@
         <v>651.1</v>
       </c>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9">
       <c r="B65" t="s">
         <v>23</v>
       </c>
@@ -10158,7 +10268,7 @@
         <v>653.85</v>
       </c>
     </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9">
       <c r="B66" t="s">
         <v>28</v>
       </c>
@@ -10180,7 +10290,7 @@
         <v>655.5</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9">
       <c r="B67" t="s">
         <v>36</v>
       </c>
@@ -10206,7 +10316,7 @@
         <v>655.9</v>
       </c>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9">
       <c r="B68" t="s">
         <v>37</v>
       </c>
@@ -10230,7 +10340,7 @@
         <v>657.51</v>
       </c>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9">
       <c r="B69" t="s">
         <v>27</v>
       </c>
@@ -10252,7 +10362,7 @@
         <v>658.12300000000005</v>
       </c>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9">
       <c r="B70" t="s">
         <v>31</v>
       </c>
@@ -10278,7 +10388,7 @@
         <v>659.46</v>
       </c>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9">
       <c r="B71" t="s">
         <v>20</v>
       </c>
@@ -10298,7 +10408,7 @@
         <v>660.6</v>
       </c>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:9">
       <c r="B72" t="s">
         <v>29</v>
       </c>
@@ -10318,7 +10428,7 @@
         <v>663.9</v>
       </c>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:9">
       <c r="B73" t="s">
         <v>26</v>
       </c>
@@ -10342,7 +10452,7 @@
         <v>664.27</v>
       </c>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:9">
       <c r="B74" t="s">
         <v>18</v>
       </c>
@@ -10362,7 +10472,7 @@
         <v>664.31799999999998</v>
       </c>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:9">
       <c r="B75" t="s">
         <v>38</v>
       </c>
@@ -10384,7 +10494,7 @@
         <v>670.1</v>
       </c>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:9">
       <c r="B76" t="s">
         <v>24</v>
       </c>
@@ -10410,7 +10520,7 @@
         <v>676.99</v>
       </c>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:9">
       <c r="B77" t="s">
         <v>34</v>
       </c>
@@ -10434,7 +10544,7 @@
         <v>679.12</v>
       </c>
     </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:9">
       <c r="B78" t="s">
         <v>41</v>
       </c>
@@ -10458,7 +10568,7 @@
         <v>679.76</v>
       </c>
     </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:9">
       <c r="B79" t="s">
         <v>30</v>
       </c>
@@ -10482,7 +10592,7 @@
         <v>686.23</v>
       </c>
     </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:9">
       <c r="B80" t="s">
         <v>32</v>
       </c>
@@ -10502,7 +10612,7 @@
         <v>687.1</v>
       </c>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:9">
       <c r="B81" t="s">
         <v>39</v>
       </c>
@@ -10526,7 +10636,7 @@
         <v>688.97</v>
       </c>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:9">
       <c r="B82" t="s">
         <v>35</v>
       </c>
@@ -10550,7 +10660,7 @@
         <v>689.54</v>
       </c>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9">
       <c r="B83" t="s">
         <v>47</v>
       </c>
@@ -10574,7 +10684,7 @@
         <v>707.74</v>
       </c>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9">
       <c r="B84" t="s">
         <v>42</v>
       </c>
@@ -10594,7 +10704,7 @@
         <v>712.23500000000001</v>
       </c>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9">
       <c r="B85" t="s">
         <v>43</v>
       </c>
@@ -10616,7 +10726,7 @@
         <v>712.6</v>
       </c>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:9">
       <c r="B86" t="s">
         <v>33</v>
       </c>
@@ -10636,7 +10746,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:9">
       <c r="B87" t="s">
         <v>40</v>
       </c>
@@ -10658,7 +10768,7 @@
         <v>725.1</v>
       </c>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9">
       <c r="B88" t="s">
         <v>59</v>
       </c>
@@ -10682,7 +10792,7 @@
         <v>730.23</v>
       </c>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9">
       <c r="B89" t="s">
         <v>50</v>
       </c>
@@ -10702,7 +10812,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9">
       <c r="B90" t="s">
         <v>46</v>
       </c>
@@ -10722,7 +10832,7 @@
         <v>744.73800000000006</v>
       </c>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9">
       <c r="B91" t="s">
         <v>45</v>
       </c>
@@ -10744,7 +10854,7 @@
         <v>745.54</v>
       </c>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9">
       <c r="B92" t="s">
         <v>48</v>
       </c>
@@ -10764,7 +10874,7 @@
         <v>746.46</v>
       </c>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9">
       <c r="B93" t="s">
         <v>49</v>
       </c>
@@ -10784,7 +10894,7 @@
         <v>747.6</v>
       </c>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9">
       <c r="B94" t="s">
         <v>53</v>
       </c>
@@ -10806,7 +10916,7 @@
         <v>774.1</v>
       </c>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:9">
       <c r="B95" t="s">
         <v>58</v>
       </c>
@@ -10828,7 +10938,7 @@
         <v>777.6</v>
       </c>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:9">
       <c r="B96" t="s">
         <v>52</v>
       </c>
@@ -10850,7 +10960,7 @@
         <v>787.53</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9">
       <c r="B97" t="s">
         <v>60</v>
       </c>
@@ -10872,7 +10982,7 @@
         <v>790.9</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9">
       <c r="B98" t="s">
         <v>51</v>
       </c>
@@ -10892,7 +11002,7 @@
         <v>795.5</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9">
       <c r="B99" t="s">
         <v>57</v>
       </c>
@@ -10918,7 +11028,7 @@
         <v>796.3</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9">
       <c r="B100" t="s">
         <v>55</v>
       </c>
@@ -10938,7 +11048,7 @@
         <v>810.7</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9">
       <c r="B101" t="s">
         <v>63</v>
       </c>
@@ -10960,7 +11070,7 @@
         <v>927.86</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9">
       <c r="B102" t="s">
         <v>62</v>
       </c>
@@ -10980,7 +11090,7 @@
         <v>984.94</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9">
       <c r="B103" t="s">
         <v>68</v>
       </c>
@@ -11000,7 +11110,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9">
       <c r="B104" t="s">
         <v>56</v>
       </c>
@@ -11020,7 +11130,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9">
       <c r="B105" t="s">
         <v>64</v>
       </c>
@@ -11042,7 +11152,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9">
       <c r="A106" t="s">
         <v>69</v>
       </c>
@@ -11069,7 +11179,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9">
       <c r="B107" t="s">
         <v>15</v>
       </c>
@@ -11091,7 +11201,7 @@
         <v>1042.5999999999999</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9">
       <c r="B108" t="s">
         <v>16</v>
       </c>
@@ -11111,7 +11221,7 @@
         <v>1057.4000000000001</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9">
       <c r="B109" t="s">
         <v>18</v>
       </c>
@@ -11131,7 +11241,7 @@
         <v>1067.9000000000001</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9">
       <c r="B110" t="s">
         <v>20</v>
       </c>
@@ -11151,7 +11261,7 @@
         <v>1068.7</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9">
       <c r="B111" t="s">
         <v>27</v>
       </c>
@@ -11173,7 +11283,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9">
       <c r="B112" t="s">
         <v>25</v>
       </c>
@@ -11197,7 +11307,7 @@
         <v>1082.5999999999999</v>
       </c>
     </row>
-    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:9">
       <c r="B113" t="s">
         <v>22</v>
       </c>
@@ -11219,7 +11329,7 @@
         <v>1082.7</v>
       </c>
     </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:9">
       <c r="B114" t="s">
         <v>38</v>
       </c>
@@ -11241,7 +11351,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:9">
       <c r="B115" t="s">
         <v>26</v>
       </c>
@@ -11265,7 +11375,7 @@
         <v>1099.5</v>
       </c>
     </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:9">
       <c r="B116" t="s">
         <v>21</v>
       </c>
@@ -11289,7 +11399,7 @@
         <v>1104.5999999999999</v>
       </c>
     </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:9">
       <c r="B117" t="s">
         <v>29</v>
       </c>
@@ -11309,7 +11419,7 @@
         <v>1111.2</v>
       </c>
     </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:9">
       <c r="B118" t="s">
         <v>37</v>
       </c>
@@ -11333,7 +11443,7 @@
         <v>1111.9000000000001</v>
       </c>
     </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:9">
       <c r="B119" t="s">
         <v>23</v>
       </c>
@@ -11359,7 +11469,7 @@
         <v>1112.3</v>
       </c>
     </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:9">
       <c r="B120" t="s">
         <v>31</v>
       </c>
@@ -11385,7 +11495,7 @@
         <v>1112.7</v>
       </c>
     </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:9">
       <c r="B121" t="s">
         <v>24</v>
       </c>
@@ -11411,7 +11521,7 @@
         <v>1125.7</v>
       </c>
     </row>
-    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:9">
       <c r="B122" t="s">
         <v>39</v>
       </c>
@@ -11435,7 +11545,7 @@
         <v>1128.0999999999999</v>
       </c>
     </row>
-    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:9">
       <c r="B123" t="s">
         <v>28</v>
       </c>
@@ -11461,7 +11571,7 @@
         <v>1128.9000000000001</v>
       </c>
     </row>
-    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:9">
       <c r="B124" t="s">
         <v>34</v>
       </c>
@@ -11485,7 +11595,7 @@
         <v>1160.5</v>
       </c>
     </row>
-    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:9">
       <c r="B125" t="s">
         <v>45</v>
       </c>
@@ -11509,7 +11619,7 @@
         <v>1161.7</v>
       </c>
     </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:9">
       <c r="B126" t="s">
         <v>44</v>
       </c>
@@ -11529,7 +11639,7 @@
         <v>1165.4000000000001</v>
       </c>
     </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:9">
       <c r="B127" t="s">
         <v>33</v>
       </c>
@@ -11551,7 +11661,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:9">
       <c r="B128" t="s">
         <v>46</v>
       </c>
@@ -11571,7 +11681,7 @@
         <v>1180.7</v>
       </c>
     </row>
-    <row r="129" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:9">
       <c r="B129" t="s">
         <v>41</v>
       </c>
@@ -11597,7 +11707,7 @@
         <v>1183.9000000000001</v>
       </c>
     </row>
-    <row r="130" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:9">
       <c r="B130" t="s">
         <v>70</v>
       </c>
@@ -11619,7 +11729,7 @@
         <v>1184.0999999999999</v>
       </c>
     </row>
-    <row r="131" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:9">
       <c r="B131" t="s">
         <v>47</v>
       </c>
@@ -11643,7 +11753,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="132" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:9">
       <c r="B132" t="s">
         <v>42</v>
       </c>
@@ -11663,7 +11773,7 @@
         <v>1186.8</v>
       </c>
     </row>
-    <row r="133" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:9">
       <c r="B133" t="s">
         <v>43</v>
       </c>
@@ -11685,7 +11795,7 @@
         <v>1190.4000000000001</v>
       </c>
     </row>
-    <row r="134" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:9">
       <c r="B134" t="s">
         <v>40</v>
       </c>
@@ -11707,7 +11817,7 @@
         <v>1191.3</v>
       </c>
     </row>
-    <row r="135" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:9">
       <c r="B135" t="s">
         <v>56</v>
       </c>
@@ -11729,7 +11839,7 @@
         <v>1208.8</v>
       </c>
     </row>
-    <row r="136" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:9">
       <c r="B136" t="s">
         <v>50</v>
       </c>
@@ -11749,7 +11859,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="137" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:9">
       <c r="B137" t="s">
         <v>58</v>
       </c>
@@ -11773,7 +11883,7 @@
         <v>1218.3</v>
       </c>
     </row>
-    <row r="138" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:9">
       <c r="B138" t="s">
         <v>30</v>
       </c>
@@ -11797,7 +11907,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="139" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:9">
       <c r="B139" t="s">
         <v>32</v>
       </c>
@@ -11817,7 +11927,7 @@
         <v>1227.4000000000001</v>
       </c>
     </row>
-    <row r="140" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:9">
       <c r="B140" t="s">
         <v>59</v>
       </c>
@@ -11841,7 +11951,7 @@
         <v>1249.5</v>
       </c>
     </row>
-    <row r="141" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:9">
       <c r="B141" t="s">
         <v>61</v>
       </c>
@@ -11865,7 +11975,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="142" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:9">
       <c r="B142" t="s">
         <v>35</v>
       </c>
@@ -11889,7 +11999,7 @@
         <v>1313.9</v>
       </c>
     </row>
-    <row r="143" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:9">
       <c r="B143" t="s">
         <v>49</v>
       </c>
@@ -11909,7 +12019,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="144" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:9">
       <c r="B144" t="s">
         <v>53</v>
       </c>
@@ -11933,7 +12043,7 @@
         <v>1323.1</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9">
       <c r="B145" t="s">
         <v>48</v>
       </c>
@@ -11957,7 +12067,7 @@
         <v>1332.6</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9">
       <c r="B146" t="s">
         <v>55</v>
       </c>
@@ -11977,7 +12087,7 @@
         <v>1423.1</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9">
       <c r="B147" t="s">
         <v>52</v>
       </c>
@@ -12001,7 +12111,7 @@
         <v>1455.2</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9">
       <c r="B148" t="s">
         <v>60</v>
       </c>
@@ -12023,7 +12133,7 @@
         <v>1463.6</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9">
       <c r="B149" t="s">
         <v>62</v>
       </c>
@@ -12047,7 +12157,7 @@
         <v>1604.2</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9">
       <c r="B150" t="s">
         <v>66</v>
       </c>
@@ -12067,7 +12177,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9">
       <c r="B151" t="s">
         <v>68</v>
       </c>
@@ -12089,7 +12199,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9">
       <c r="B152" t="s">
         <v>63</v>
       </c>
@@ -12109,7 +12219,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9">
       <c r="B153" t="s">
         <v>64</v>
       </c>
@@ -12129,7 +12239,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9">
       <c r="B154" t="s">
         <v>57</v>
       </c>
@@ -12151,7 +12261,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9">
       <c r="A155">
         <v>800</v>
       </c>
@@ -12174,7 +12284,7 @@
         <v>128.68899999999999</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9">
       <c r="B156" t="s">
         <v>17</v>
       </c>
@@ -12198,7 +12308,7 @@
         <v>128.77600000000001</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9">
       <c r="B157" t="s">
         <v>18</v>
       </c>
@@ -12218,7 +12328,7 @@
         <v>128.80199999999999</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9">
       <c r="B158" t="s">
         <v>19</v>
       </c>
@@ -12238,7 +12348,7 @@
         <v>129.03399999999999</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9">
       <c r="B159" t="s">
         <v>15</v>
       </c>
@@ -12260,7 +12370,7 @@
         <v>129.20099999999999</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9">
       <c r="B160" t="s">
         <v>31</v>
       </c>
@@ -12286,7 +12396,7 @@
         <v>129.39599999999999</v>
       </c>
     </row>
-    <row r="161" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:9">
       <c r="B161" t="s">
         <v>29</v>
       </c>
@@ -12306,7 +12416,7 @@
         <v>129.85599999999999</v>
       </c>
     </row>
-    <row r="162" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:9">
       <c r="B162" t="s">
         <v>28</v>
       </c>
@@ -12330,7 +12440,7 @@
         <v>130.22999999999999</v>
       </c>
     </row>
-    <row r="163" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:9">
       <c r="B163" t="s">
         <v>21</v>
       </c>
@@ -12354,7 +12464,7 @@
         <v>130.93600000000001</v>
       </c>
     </row>
-    <row r="164" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:9">
       <c r="B164" t="s">
         <v>36</v>
       </c>
@@ -12380,7 +12490,7 @@
         <v>131.52000000000001</v>
       </c>
     </row>
-    <row r="165" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:9">
       <c r="B165" t="s">
         <v>26</v>
       </c>
@@ -12404,7 +12514,7 @@
         <v>131.63999999999999</v>
       </c>
     </row>
-    <row r="166" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:9">
       <c r="B166" t="s">
         <v>23</v>
       </c>
@@ -12430,7 +12540,7 @@
         <v>132.69999999999999</v>
       </c>
     </row>
-    <row r="167" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:9">
       <c r="B167" t="s">
         <v>25</v>
       </c>
@@ -12454,7 +12564,7 @@
         <v>133.35</v>
       </c>
     </row>
-    <row r="168" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:9">
       <c r="B168" t="s">
         <v>34</v>
       </c>
@@ -12478,7 +12588,7 @@
         <v>134.85599999999999</v>
       </c>
     </row>
-    <row r="169" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:9">
       <c r="B169" t="s">
         <v>30</v>
       </c>
@@ -12502,7 +12612,7 @@
         <v>136.35</v>
       </c>
     </row>
-    <row r="170" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:9">
       <c r="B170" t="s">
         <v>20</v>
       </c>
@@ -12522,7 +12632,7 @@
         <v>136.66200000000001</v>
       </c>
     </row>
-    <row r="171" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:9">
       <c r="B171" t="s">
         <v>35</v>
       </c>
@@ -12546,7 +12656,7 @@
         <v>137.541</v>
       </c>
     </row>
-    <row r="172" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:9">
       <c r="B172" t="s">
         <v>39</v>
       </c>
@@ -12570,7 +12680,7 @@
         <v>138.203</v>
       </c>
     </row>
-    <row r="173" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:9">
       <c r="B173" t="s">
         <v>33</v>
       </c>
@@ -12592,7 +12702,7 @@
         <v>138.23099999999999</v>
       </c>
     </row>
-    <row r="174" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:9">
       <c r="B174" t="s">
         <v>27</v>
       </c>
@@ -12614,7 +12724,7 @@
         <v>138.77600000000001</v>
       </c>
     </row>
-    <row r="175" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:9">
       <c r="B175" t="s">
         <v>43</v>
       </c>
@@ -12636,7 +12746,7 @@
         <v>140.74799999999999</v>
       </c>
     </row>
-    <row r="176" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:9">
       <c r="B176" t="s">
         <v>45</v>
       </c>
@@ -12660,7 +12770,7 @@
         <v>140.89699999999999</v>
       </c>
     </row>
-    <row r="177" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:9">
       <c r="B177" t="s">
         <v>22</v>
       </c>
@@ -12682,7 +12792,7 @@
         <v>141.553</v>
       </c>
     </row>
-    <row r="178" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:9">
       <c r="B178" t="s">
         <v>37</v>
       </c>
@@ -12706,7 +12816,7 @@
         <v>141.893</v>
       </c>
     </row>
-    <row r="179" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:9">
       <c r="B179" t="s">
         <v>38</v>
       </c>
@@ -12728,7 +12838,7 @@
         <v>142.512</v>
       </c>
     </row>
-    <row r="180" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:9">
       <c r="B180" t="s">
         <v>24</v>
       </c>
@@ -12754,7 +12864,7 @@
         <v>142.99</v>
       </c>
     </row>
-    <row r="181" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:9">
       <c r="B181" t="s">
         <v>48</v>
       </c>
@@ -12776,7 +12886,7 @@
         <v>145.19</v>
       </c>
     </row>
-    <row r="182" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:9">
       <c r="B182" t="s">
         <v>49</v>
       </c>
@@ -12796,7 +12906,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="183" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:9">
       <c r="B183" t="s">
         <v>40</v>
       </c>
@@ -12818,7 +12928,7 @@
         <v>147.316</v>
       </c>
     </row>
-    <row r="184" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:9">
       <c r="B184" t="s">
         <v>42</v>
       </c>
@@ -12838,7 +12948,7 @@
         <v>147.72300000000001</v>
       </c>
     </row>
-    <row r="185" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:9">
       <c r="B185" t="s">
         <v>32</v>
       </c>
@@ -12858,7 +12968,7 @@
         <v>149.66800000000001</v>
       </c>
     </row>
-    <row r="186" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:9">
       <c r="B186" t="s">
         <v>50</v>
       </c>
@@ -12878,7 +12988,7 @@
         <v>149.733</v>
       </c>
     </row>
-    <row r="187" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:9">
       <c r="B187" t="s">
         <v>41</v>
       </c>
@@ -12902,7 +13012,7 @@
         <v>150.82</v>
       </c>
     </row>
-    <row r="188" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:9">
       <c r="B188" t="s">
         <v>46</v>
       </c>
@@ -12922,7 +13032,7 @@
         <v>152.66</v>
       </c>
     </row>
-    <row r="189" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:9">
       <c r="B189" t="s">
         <v>51</v>
       </c>
@@ -12942,7 +13052,7 @@
         <v>154.40700000000001</v>
       </c>
     </row>
-    <row r="190" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:9">
       <c r="B190" t="s">
         <v>47</v>
       </c>
@@ -12966,7 +13076,7 @@
         <v>155.91</v>
       </c>
     </row>
-    <row r="191" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:9">
       <c r="B191" t="s">
         <v>52</v>
       </c>
@@ -12988,7 +13098,7 @@
         <v>155.99</v>
       </c>
     </row>
-    <row r="192" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:9">
       <c r="B192" t="s">
         <v>53</v>
       </c>
@@ -13010,7 +13120,7 @@
         <v>156.18</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9">
       <c r="B193" t="s">
         <v>54</v>
       </c>
@@ -13030,7 +13140,7 @@
         <v>156.70400000000001</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9">
       <c r="B194" t="s">
         <v>59</v>
       </c>
@@ -13054,7 +13164,7 @@
         <v>157.583</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9">
       <c r="B195" t="s">
         <v>61</v>
       </c>
@@ -13074,7 +13184,7 @@
         <v>161.28</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9">
       <c r="B196" t="s">
         <v>44</v>
       </c>
@@ -13094,7 +13204,7 @@
         <v>161.494</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9">
       <c r="B197" t="s">
         <v>57</v>
       </c>
@@ -13120,7 +13230,7 @@
         <v>162.21</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9">
       <c r="B198" t="s">
         <v>55</v>
       </c>
@@ -13140,7 +13250,7 @@
         <v>162.82499999999999</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9">
       <c r="B199" t="s">
         <v>58</v>
       </c>
@@ -13164,7 +13274,7 @@
         <v>173.12299999999999</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9">
       <c r="B200" t="s">
         <v>63</v>
       </c>
@@ -13186,7 +13296,7 @@
         <v>178.125</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9">
       <c r="B201" t="s">
         <v>62</v>
       </c>
@@ -13208,7 +13318,7 @@
         <v>197.6</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9">
       <c r="B202" t="s">
         <v>68</v>
       </c>
@@ -13228,7 +13338,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9">
       <c r="B203" t="s">
         <v>64</v>
       </c>
@@ -13250,7 +13360,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9">
       <c r="B204" t="s">
         <v>65</v>
       </c>
@@ -13272,7 +13382,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9">
       <c r="B205" t="s">
         <v>66</v>
       </c>
@@ -13296,7 +13406,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9">
       <c r="B206" t="s">
         <v>56</v>
       </c>
@@ -13316,7 +13426,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9">
       <c r="A207" t="s">
         <v>71</v>
       </c>
@@ -13341,16 +13451,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>2029</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
       <formula>2028</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="equal">
       <formula>2027</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="4" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="4" stopIfTrue="1" operator="equal">
       <formula>2026</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13362,7 +13472,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5618C841-8876-4D0C-80DF-C05F2AAF82DF}">
   <dimension ref="A1:T242"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -13378,7 +13488,7 @@
     <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -13440,7 +13550,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -13502,7 +13612,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -13558,7 +13668,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -13620,7 +13730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20">
       <c r="A5" t="s">
         <v>91</v>
       </c>
@@ -13658,7 +13768,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -13714,7 +13824,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20">
       <c r="A7" t="s">
         <v>94</v>
       </c>
@@ -13752,7 +13862,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -13814,7 +13924,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20">
       <c r="A9" t="s">
         <v>96</v>
       </c>
@@ -13858,7 +13968,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20">
       <c r="A10" t="s">
         <v>98</v>
       </c>
@@ -13902,7 +14012,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -13958,7 +14068,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -14020,7 +14130,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20">
       <c r="A13" t="s">
         <v>101</v>
       </c>
@@ -14058,7 +14168,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20">
       <c r="A14" t="s">
         <v>66</v>
       </c>
@@ -14102,7 +14212,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20">
       <c r="A15" t="s">
         <v>64</v>
       </c>
@@ -14140,7 +14250,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20">
       <c r="A16" t="s">
         <v>102</v>
       </c>
@@ -14172,7 +14282,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -14222,7 +14332,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -14272,7 +14382,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20">
       <c r="A19" t="s">
         <v>106</v>
       </c>
@@ -14310,7 +14420,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -14360,7 +14470,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -14410,7 +14520,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -14460,7 +14570,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -14510,7 +14620,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -14560,7 +14670,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -14610,7 +14720,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20">
       <c r="A26" t="s">
         <v>45</v>
       </c>
@@ -14660,7 +14770,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20">
       <c r="A27" t="s">
         <v>37</v>
       </c>
@@ -14710,7 +14820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20">
       <c r="A28" t="s">
         <v>48</v>
       </c>
@@ -14754,7 +14864,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20">
       <c r="A29" t="s">
         <v>115</v>
       </c>
@@ -14792,7 +14902,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20">
       <c r="A30" t="s">
         <v>47</v>
       </c>
@@ -14842,7 +14952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -14886,7 +14996,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20">
       <c r="A32" t="s">
         <v>53</v>
       </c>
@@ -14930,7 +15040,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20">
       <c r="A33" t="s">
         <v>59</v>
       </c>
@@ -14980,7 +15090,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20">
       <c r="A34" t="s">
         <v>120</v>
       </c>
@@ -15018,7 +15128,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20">
       <c r="A35" t="s">
         <v>61</v>
       </c>
@@ -15056,7 +15166,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20">
       <c r="A36" t="s">
         <v>58</v>
       </c>
@@ -15106,7 +15216,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -15150,7 +15260,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20">
       <c r="A38" t="s">
         <v>62</v>
       </c>
@@ -15194,7 +15304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20">
       <c r="A39" t="s">
         <v>65</v>
       </c>
@@ -15232,7 +15342,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20">
       <c r="A40" t="s">
         <v>68</v>
       </c>
@@ -15264,7 +15374,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20">
       <c r="A41" t="s">
         <v>15</v>
       </c>
@@ -15314,7 +15424,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20">
       <c r="A42" t="s">
         <v>33</v>
       </c>
@@ -15364,7 +15474,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -15408,7 +15518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -15458,7 +15568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20">
       <c r="A45" t="s">
         <v>22</v>
       </c>
@@ -15502,7 +15612,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20">
       <c r="A46" t="s">
         <v>38</v>
       </c>
@@ -15552,7 +15662,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20">
       <c r="A47" t="s">
         <v>40</v>
       </c>
@@ -15596,7 +15706,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20">
       <c r="A48" t="s">
         <v>131</v>
       </c>
@@ -15634,7 +15744,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -15666,7 +15776,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20">
       <c r="A50" t="s">
         <v>16</v>
       </c>
@@ -15710,7 +15820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -15754,7 +15864,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20">
       <c r="A52" t="s">
         <v>19</v>
       </c>
@@ -15798,7 +15908,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20">
       <c r="A53" t="s">
         <v>29</v>
       </c>
@@ -15842,7 +15952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20">
       <c r="A54" t="s">
         <v>20</v>
       </c>
@@ -15886,7 +15996,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20">
       <c r="A55" t="s">
         <v>49</v>
       </c>
@@ -15930,7 +16040,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20">
       <c r="A56" t="s">
         <v>42</v>
       </c>
@@ -15974,7 +16084,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20">
       <c r="A57" t="s">
         <v>32</v>
       </c>
@@ -16018,7 +16128,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20">
       <c r="A58" t="s">
         <v>50</v>
       </c>
@@ -16062,7 +16172,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20">
       <c r="A59" t="s">
         <v>46</v>
       </c>
@@ -16100,7 +16210,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20">
       <c r="A60" t="s">
         <v>51</v>
       </c>
@@ -16144,7 +16254,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20">
       <c r="A61" t="s">
         <v>54</v>
       </c>
@@ -16188,7 +16298,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20">
       <c r="A62" t="s">
         <v>44</v>
       </c>
@@ -16226,7 +16336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20">
       <c r="A63" t="s">
         <v>55</v>
       </c>
@@ -16270,7 +16380,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20">
       <c r="A64" t="s">
         <v>91</v>
       </c>
@@ -16308,7 +16418,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20">
       <c r="A65" t="s">
         <v>23</v>
       </c>
@@ -16370,7 +16480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20">
       <c r="A66" t="s">
         <v>24</v>
       </c>
@@ -16432,7 +16542,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20">
       <c r="A67" t="s">
         <v>28</v>
       </c>
@@ -16476,7 +16586,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20">
       <c r="A68" t="s">
         <v>31</v>
       </c>
@@ -16526,7 +16636,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20">
       <c r="A69" t="s">
         <v>36</v>
       </c>
@@ -16576,7 +16686,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20">
       <c r="A70" t="s">
         <v>98</v>
       </c>
@@ -16614,7 +16724,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20">
       <c r="A71" t="s">
         <v>96</v>
       </c>
@@ -16658,7 +16768,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20">
       <c r="A72" t="s">
         <v>94</v>
       </c>
@@ -16702,7 +16812,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20">
       <c r="A73" t="s">
         <v>41</v>
       </c>
@@ -16758,7 +16868,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20">
       <c r="A74" t="s">
         <v>57</v>
       </c>
@@ -16820,7 +16930,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20">
       <c r="A75" t="s">
         <v>101</v>
       </c>
@@ -16864,7 +16974,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20">
       <c r="A76" t="s">
         <v>66</v>
       </c>
@@ -16896,7 +17006,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20">
       <c r="A77" t="s">
         <v>64</v>
       </c>
@@ -16934,7 +17044,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20">
       <c r="A78" t="s">
         <v>102</v>
       </c>
@@ -16966,7 +17076,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20">
       <c r="A79" t="s">
         <v>106</v>
       </c>
@@ -17004,7 +17114,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20">
       <c r="A80" t="s">
         <v>17</v>
       </c>
@@ -17054,7 +17164,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20">
       <c r="A81" t="s">
         <v>21</v>
       </c>
@@ -17104,7 +17214,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20">
       <c r="A82" t="s">
         <v>25</v>
       </c>
@@ -17154,7 +17264,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20">
       <c r="A83" t="s">
         <v>26</v>
       </c>
@@ -17204,7 +17314,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20">
       <c r="A84" t="s">
         <v>30</v>
       </c>
@@ -17254,7 +17364,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20">
       <c r="A85" t="s">
         <v>34</v>
       </c>
@@ -17304,7 +17414,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20">
       <c r="A86" t="s">
         <v>35</v>
       </c>
@@ -17354,7 +17464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20">
       <c r="A87" t="s">
         <v>37</v>
       </c>
@@ -17404,7 +17514,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20">
       <c r="A88" t="s">
         <v>39</v>
       </c>
@@ -17454,7 +17564,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20">
       <c r="A89" t="s">
         <v>148</v>
       </c>
@@ -17492,7 +17602,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20">
       <c r="A90" t="s">
         <v>115</v>
       </c>
@@ -17530,7 +17640,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20">
       <c r="A91" t="s">
         <v>45</v>
       </c>
@@ -17580,7 +17690,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20">
       <c r="A92" t="s">
         <v>47</v>
       </c>
@@ -17630,7 +17740,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20">
       <c r="A93" t="s">
         <v>48</v>
       </c>
@@ -17674,7 +17784,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20">
       <c r="A94" t="s">
         <v>52</v>
       </c>
@@ -17718,7 +17828,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20">
       <c r="A95" t="s">
         <v>53</v>
       </c>
@@ -17762,7 +17872,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20">
       <c r="A96" t="s">
         <v>58</v>
       </c>
@@ -17812,7 +17922,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20">
       <c r="A97" t="s">
         <v>59</v>
       </c>
@@ -17862,7 +17972,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20">
       <c r="A98" t="s">
         <v>61</v>
       </c>
@@ -17900,7 +18010,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20">
       <c r="A99" t="s">
         <v>62</v>
       </c>
@@ -17938,7 +18048,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20">
       <c r="A100" t="s">
         <v>63</v>
       </c>
@@ -17976,7 +18086,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20">
       <c r="A101" t="s">
         <v>65</v>
       </c>
@@ -18014,7 +18124,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20">
       <c r="A102" t="s">
         <v>15</v>
       </c>
@@ -18064,7 +18174,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20">
       <c r="A103" t="s">
         <v>22</v>
       </c>
@@ -18114,7 +18224,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20">
       <c r="A104" t="s">
         <v>27</v>
       </c>
@@ -18164,7 +18274,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20">
       <c r="A105" t="s">
         <v>33</v>
       </c>
@@ -18208,7 +18318,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20">
       <c r="A106" t="s">
         <v>38</v>
       </c>
@@ -18252,7 +18362,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20">
       <c r="A107" t="s">
         <v>40</v>
       </c>
@@ -18302,7 +18412,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20">
       <c r="A108" t="s">
         <v>43</v>
       </c>
@@ -18346,7 +18456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20">
       <c r="A109" t="s">
         <v>131</v>
       </c>
@@ -18384,7 +18494,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20">
       <c r="A110" t="s">
         <v>56</v>
       </c>
@@ -18428,7 +18538,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20">
       <c r="A111" t="s">
         <v>60</v>
       </c>
@@ -18472,7 +18582,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20">
       <c r="A112" t="s">
         <v>16</v>
       </c>
@@ -18516,7 +18626,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:20">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -18560,7 +18670,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:20">
       <c r="A114" t="s">
         <v>19</v>
       </c>
@@ -18598,7 +18708,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:20">
       <c r="A115" t="s">
         <v>20</v>
       </c>
@@ -18642,7 +18752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:20">
       <c r="A116" t="s">
         <v>29</v>
       </c>
@@ -18686,7 +18796,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:20">
       <c r="A117" t="s">
         <v>32</v>
       </c>
@@ -18730,7 +18840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:20">
       <c r="A118" t="s">
         <v>42</v>
       </c>
@@ -18768,7 +18878,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:20">
       <c r="A119" t="s">
         <v>44</v>
       </c>
@@ -18806,7 +18916,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:20">
       <c r="A120" t="s">
         <v>46</v>
       </c>
@@ -18844,7 +18954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:20">
       <c r="A121" t="s">
         <v>49</v>
       </c>
@@ -18882,7 +18992,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:20">
       <c r="A122" t="s">
         <v>50</v>
       </c>
@@ -18920,7 +19030,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:20">
       <c r="A123" t="s">
         <v>51</v>
       </c>
@@ -18958,7 +19068,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:20">
       <c r="A124" t="s">
         <v>54</v>
       </c>
@@ -18996,7 +19106,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:20">
       <c r="A125" t="s">
         <v>55</v>
       </c>
@@ -19034,7 +19144,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:20">
       <c r="A126" t="s">
         <v>23</v>
       </c>
@@ -19090,7 +19200,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:20">
       <c r="A127" t="s">
         <v>28</v>
       </c>
@@ -19134,7 +19244,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:20">
       <c r="A128" t="s">
         <v>36</v>
       </c>
@@ -19190,7 +19300,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:20">
       <c r="A129" t="s">
         <v>31</v>
       </c>
@@ -19246,7 +19356,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:20">
       <c r="A130" t="s">
         <v>24</v>
       </c>
@@ -19302,7 +19412,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:20">
       <c r="A131" t="s">
         <v>41</v>
       </c>
@@ -19352,7 +19462,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:20">
       <c r="A132" t="s">
         <v>98</v>
       </c>
@@ -19390,7 +19500,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:20">
       <c r="A133" t="s">
         <v>94</v>
       </c>
@@ -19434,7 +19544,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:20">
       <c r="A134" t="s">
         <v>96</v>
       </c>
@@ -19472,7 +19582,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:20">
       <c r="A135" t="s">
         <v>57</v>
       </c>
@@ -19528,7 +19638,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:20">
       <c r="A136" t="s">
         <v>101</v>
       </c>
@@ -19566,7 +19676,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:20">
       <c r="A137" t="s">
         <v>168</v>
       </c>
@@ -19604,7 +19714,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:20">
       <c r="A138" t="s">
         <v>64</v>
       </c>
@@ -19642,7 +19752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:20">
       <c r="A139" t="s">
         <v>17</v>
       </c>
@@ -19692,7 +19802,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:20">
       <c r="A140" t="s">
         <v>106</v>
       </c>
@@ -19730,7 +19840,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:20">
       <c r="A141" t="s">
         <v>21</v>
       </c>
@@ -19780,7 +19890,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:20">
       <c r="A142" t="s">
         <v>25</v>
       </c>
@@ -19830,7 +19940,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:20">
       <c r="A143" t="s">
         <v>37</v>
       </c>
@@ -19880,7 +19990,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:20">
       <c r="A144" t="s">
         <v>26</v>
       </c>
@@ -19930,7 +20040,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:20">
       <c r="A145" t="s">
         <v>34</v>
       </c>
@@ -19980,7 +20090,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:20">
       <c r="A146" t="s">
         <v>30</v>
       </c>
@@ -20030,7 +20140,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:20">
       <c r="A147" t="s">
         <v>39</v>
       </c>
@@ -20080,7 +20190,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:20">
       <c r="A148" t="s">
         <v>35</v>
       </c>
@@ -20130,7 +20240,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:20">
       <c r="A149" t="s">
         <v>47</v>
       </c>
@@ -20180,7 +20290,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:20">
       <c r="A150" t="s">
         <v>59</v>
       </c>
@@ -20230,7 +20340,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:20">
       <c r="A151" t="s">
         <v>115</v>
       </c>
@@ -20268,7 +20378,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:20">
       <c r="A152" t="s">
         <v>45</v>
       </c>
@@ -20312,7 +20422,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:20">
       <c r="A153" t="s">
         <v>48</v>
       </c>
@@ -20350,7 +20460,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:20">
       <c r="A154" t="s">
         <v>53</v>
       </c>
@@ -20394,7 +20504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:20">
       <c r="A155" t="s">
         <v>58</v>
       </c>
@@ -20438,7 +20548,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:20">
       <c r="A156" t="s">
         <v>52</v>
       </c>
@@ -20482,7 +20592,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:20">
       <c r="A157" t="s">
         <v>63</v>
       </c>
@@ -20526,7 +20636,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:20">
       <c r="A158" t="s">
         <v>62</v>
       </c>
@@ -20564,7 +20674,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:20">
       <c r="A159" t="s">
         <v>68</v>
       </c>
@@ -20596,7 +20706,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:20">
       <c r="A160" t="s">
         <v>15</v>
       </c>
@@ -20640,7 +20750,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:20">
       <c r="A161" t="s">
         <v>22</v>
       </c>
@@ -20684,7 +20794,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:20">
       <c r="A162" t="s">
         <v>27</v>
       </c>
@@ -20728,7 +20838,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:20">
       <c r="A163" t="s">
         <v>38</v>
       </c>
@@ -20772,7 +20882,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:20">
       <c r="A164" t="s">
         <v>43</v>
       </c>
@@ -20816,7 +20926,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:20">
       <c r="A165" t="s">
         <v>33</v>
       </c>
@@ -20854,7 +20964,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:20">
       <c r="A166" t="s">
         <v>40</v>
       </c>
@@ -20898,7 +21008,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:20">
       <c r="A167" t="s">
         <v>60</v>
       </c>
@@ -20942,7 +21052,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:20">
       <c r="A168" t="s">
         <v>56</v>
       </c>
@@ -20974,7 +21084,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:20">
       <c r="A169" t="s">
         <v>16</v>
       </c>
@@ -21012,7 +21122,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:20">
       <c r="A170" t="s">
         <v>19</v>
       </c>
@@ -21050,7 +21160,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:20">
       <c r="A171" t="s">
         <v>20</v>
       </c>
@@ -21088,7 +21198,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:20">
       <c r="A172" t="s">
         <v>29</v>
       </c>
@@ -21126,7 +21236,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:20">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -21164,7 +21274,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:20">
       <c r="A174" t="s">
         <v>32</v>
       </c>
@@ -21202,7 +21312,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:20">
       <c r="A175" t="s">
         <v>42</v>
       </c>
@@ -21240,7 +21350,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:20">
       <c r="A176" t="s">
         <v>50</v>
       </c>
@@ -21278,7 +21388,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:20">
       <c r="A177" t="s">
         <v>46</v>
       </c>
@@ -21316,7 +21426,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:20">
       <c r="A178" t="s">
         <v>49</v>
       </c>
@@ -21354,7 +21464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:20">
       <c r="A179" t="s">
         <v>51</v>
       </c>
@@ -21392,7 +21502,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:20">
       <c r="A180" t="s">
         <v>55</v>
       </c>
@@ -21430,7 +21540,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:20">
       <c r="A181" t="s">
         <v>23</v>
       </c>
@@ -21486,7 +21596,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:20">
       <c r="A182" t="s">
         <v>31</v>
       </c>
@@ -21542,7 +21652,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:20">
       <c r="A183" t="s">
         <v>24</v>
       </c>
@@ -21598,7 +21708,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:20">
       <c r="A184" t="s">
         <v>28</v>
       </c>
@@ -21654,7 +21764,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:20">
       <c r="A185" t="s">
         <v>96</v>
       </c>
@@ -21698,7 +21808,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:20">
       <c r="A186" t="s">
         <v>41</v>
       </c>
@@ -21754,7 +21864,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:20">
       <c r="A187" t="s">
         <v>194</v>
       </c>
@@ -21792,7 +21902,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:20">
       <c r="A188" t="s">
         <v>102</v>
       </c>
@@ -21836,7 +21946,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:20">
       <c r="A189" t="s">
         <v>195</v>
       </c>
@@ -21874,7 +21984,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:20">
       <c r="A190" t="s">
         <v>101</v>
       </c>
@@ -21912,7 +22022,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:20">
       <c r="A191" t="s">
         <v>168</v>
       </c>
@@ -21950,7 +22060,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:20">
       <c r="A192" t="s">
         <v>196</v>
       </c>
@@ -21988,7 +22098,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:20">
       <c r="A193" t="s">
         <v>197</v>
       </c>
@@ -22026,7 +22136,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:20">
       <c r="A194" t="s">
         <v>66</v>
       </c>
@@ -22058,7 +22168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:20">
       <c r="A195" t="s">
         <v>64</v>
       </c>
@@ -22090,7 +22200,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:20">
       <c r="A196" t="s">
         <v>57</v>
       </c>
@@ -22128,7 +22238,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:20">
       <c r="A197" t="s">
         <v>106</v>
       </c>
@@ -22166,7 +22276,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:20">
       <c r="A198" t="s">
         <v>17</v>
       </c>
@@ -22216,7 +22326,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:20">
       <c r="A199" t="s">
         <v>25</v>
       </c>
@@ -22266,7 +22376,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:20">
       <c r="A200" t="s">
         <v>26</v>
       </c>
@@ -22316,7 +22426,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:20">
       <c r="A201" t="s">
         <v>21</v>
       </c>
@@ -22366,7 +22476,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:20">
       <c r="A202" t="s">
         <v>115</v>
       </c>
@@ -22404,7 +22514,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:20">
       <c r="A203" t="s">
         <v>37</v>
       </c>
@@ -22454,7 +22564,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:20">
       <c r="A204" t="s">
         <v>39</v>
       </c>
@@ -22504,7 +22614,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:20">
       <c r="A205" t="s">
         <v>34</v>
       </c>
@@ -22554,7 +22664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:20">
       <c r="A206" t="s">
         <v>45</v>
       </c>
@@ -22604,7 +22714,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:20">
       <c r="A207" t="s">
         <v>120</v>
       </c>
@@ -22648,7 +22758,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:20">
       <c r="A208" t="s">
         <v>47</v>
       </c>
@@ -22698,7 +22808,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:20">
       <c r="A209" t="s">
         <v>58</v>
       </c>
@@ -22748,7 +22858,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:20">
       <c r="A210" t="s">
         <v>30</v>
       </c>
@@ -22798,7 +22908,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:20">
       <c r="A211" t="s">
         <v>59</v>
       </c>
@@ -22848,7 +22958,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:20">
       <c r="A212" t="s">
         <v>61</v>
       </c>
@@ -22898,7 +23008,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:20">
       <c r="A213" t="s">
         <v>35</v>
       </c>
@@ -22948,7 +23058,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:20">
       <c r="A214" t="s">
         <v>53</v>
       </c>
@@ -22998,7 +23108,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:20">
       <c r="A215" t="s">
         <v>48</v>
       </c>
@@ -23048,7 +23158,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:20">
       <c r="A216" t="s">
         <v>212</v>
       </c>
@@ -23086,7 +23196,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:20">
       <c r="A217" t="s">
         <v>52</v>
       </c>
@@ -23136,7 +23246,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:20">
       <c r="A218" t="s">
         <v>62</v>
       </c>
@@ -23186,7 +23296,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:20">
       <c r="A219" t="s">
         <v>68</v>
       </c>
@@ -23224,7 +23334,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:20">
       <c r="A220" t="s">
         <v>63</v>
       </c>
@@ -23256,7 +23366,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:20">
       <c r="A221" t="s">
         <v>15</v>
       </c>
@@ -23300,7 +23410,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:20">
       <c r="A222" t="s">
         <v>27</v>
       </c>
@@ -23344,7 +23454,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:20">
       <c r="A223" t="s">
         <v>22</v>
       </c>
@@ -23388,7 +23498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="224" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:20">
       <c r="A224" t="s">
         <v>38</v>
       </c>
@@ -23432,7 +23542,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="225" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:20">
       <c r="A225" t="s">
         <v>217</v>
       </c>
@@ -23470,7 +23580,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="226" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:20">
       <c r="A226" t="s">
         <v>33</v>
       </c>
@@ -23514,7 +23624,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="227" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:20">
       <c r="A227" t="s">
         <v>70</v>
       </c>
@@ -23558,7 +23668,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="228" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:20">
       <c r="A228" t="s">
         <v>43</v>
       </c>
@@ -23602,7 +23712,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:20">
       <c r="A229" t="s">
         <v>40</v>
       </c>
@@ -23646,7 +23756,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:20">
       <c r="A230" t="s">
         <v>56</v>
       </c>
@@ -23690,7 +23800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:20">
       <c r="A231" t="s">
         <v>60</v>
       </c>
@@ -23734,7 +23844,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:20">
       <c r="A232" t="s">
         <v>16</v>
       </c>
@@ -23772,7 +23882,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="233" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:20">
       <c r="A233" t="s">
         <v>18</v>
       </c>
@@ -23810,7 +23920,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="234" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:20">
       <c r="A234" t="s">
         <v>20</v>
       </c>
@@ -23848,7 +23958,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="235" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:20">
       <c r="A235" t="s">
         <v>29</v>
       </c>
@@ -23886,7 +23996,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="236" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:20">
       <c r="A236" t="s">
         <v>44</v>
       </c>
@@ -23924,7 +24034,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="237" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:20">
       <c r="A237" t="s">
         <v>46</v>
       </c>
@@ -23962,7 +24072,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="238" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:20">
       <c r="A238" t="s">
         <v>42</v>
       </c>
@@ -24000,7 +24110,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="239" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:20">
       <c r="A239" t="s">
         <v>50</v>
       </c>
@@ -24038,7 +24148,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="240" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:20">
       <c r="A240" t="s">
         <v>32</v>
       </c>
@@ -24076,7 +24186,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="241" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:20">
       <c r="A241" t="s">
         <v>49</v>
       </c>
@@ -24114,7 +24224,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="242" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:20">
       <c r="A242" t="s">
         <v>55</v>
       </c>
@@ -24155,4 +24265,3932 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2E8374D-E337-4E9C-AE50-5FBC9B1207A7}">
+  <dimension ref="A1:AF53"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" customWidth="1"/>
+    <col min="18" max="18" width="18.85546875" customWidth="1"/>
+    <col min="26" max="26" width="20.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32">
+      <c r="D1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="T1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="U1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="V1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="W1" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="X1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE1" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF1" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
+      <c r="A2" s="8">
+        <v>800</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2">
+        <v>2029</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="6">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2">
+        <v>2028</v>
+      </c>
+      <c r="L2" s="4">
+        <v>3.2986111111111111E-3</v>
+      </c>
+      <c r="M2" s="5">
+        <v>3.2060185185185191E-3</v>
+      </c>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="6">
+        <v>3.2060185185185191E-3</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2">
+        <v>2027</v>
+      </c>
+      <c r="T2" s="4">
+        <v>7.0949074074074074E-3</v>
+      </c>
+      <c r="U2" s="5">
+        <v>6.7129629629629622E-3</v>
+      </c>
+      <c r="V2" s="5">
+        <v>6.5740740740740733E-3</v>
+      </c>
+      <c r="W2" s="5"/>
+      <c r="X2" s="6">
+        <v>6.5740740740740733E-3</v>
+      </c>
+      <c r="Y2" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA2">
+        <v>2027</v>
+      </c>
+      <c r="AB2" s="4">
+        <v>1.1875000000000002E-2</v>
+      </c>
+      <c r="AC2" s="5">
+        <v>1.1504629629629629E-2</v>
+      </c>
+      <c r="AD2" s="5">
+        <v>1.082175925925926E-2</v>
+      </c>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="6">
+        <v>1.082175925925926E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3">
+        <v>2027</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1.4583333333333334E-3</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="6">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3">
+        <v>2029</v>
+      </c>
+      <c r="L3" s="4">
+        <v>3.3101851851851851E-3</v>
+      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="6">
+        <v>3.3101851851851851E-3</v>
+      </c>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="S3">
+        <v>2028</v>
+      </c>
+      <c r="T3" s="4">
+        <v>7.1412037037037043E-3</v>
+      </c>
+      <c r="U3" s="5">
+        <v>7.083333333333333E-3</v>
+      </c>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="6">
+        <v>7.083333333333333E-3</v>
+      </c>
+      <c r="Y3" s="8"/>
+      <c r="Z3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA3">
+        <v>2028</v>
+      </c>
+      <c r="AB3" s="4">
+        <v>1.207175925925926E-2</v>
+      </c>
+      <c r="AC3" s="5">
+        <v>1.1400462962962965E-2</v>
+      </c>
+      <c r="AD3" s="5"/>
+      <c r="AE3" s="5"/>
+      <c r="AF3" s="6">
+        <v>1.1400462962962965E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>2029</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="6">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4">
+        <v>2027</v>
+      </c>
+      <c r="L4" s="4">
+        <v>3.3217592592592591E-3</v>
+      </c>
+      <c r="M4" s="5">
+        <v>3.1249999999999997E-3</v>
+      </c>
+      <c r="N4" s="5">
+        <v>3.0787037037037037E-3</v>
+      </c>
+      <c r="O4" s="5"/>
+      <c r="P4" s="6">
+        <v>3.0787037037037037E-3</v>
+      </c>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="S4">
+        <v>2027</v>
+      </c>
+      <c r="T4" s="4">
+        <v>7.3495370370370372E-3</v>
+      </c>
+      <c r="U4" s="5">
+        <v>7.1180555555555554E-3</v>
+      </c>
+      <c r="V4" s="5">
+        <v>6.5624999999999998E-3</v>
+      </c>
+      <c r="W4" s="5"/>
+      <c r="X4" s="6">
+        <v>6.5624999999999998E-3</v>
+      </c>
+      <c r="Y4" s="8"/>
+      <c r="Z4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA4">
+        <v>2029</v>
+      </c>
+      <c r="AB4" s="4">
+        <v>1.2233796296296296E-2</v>
+      </c>
+      <c r="AC4" s="5"/>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="6">
+        <v>1.2233796296296296E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5">
+        <v>2029</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="6">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5">
+        <v>2029</v>
+      </c>
+      <c r="L5" s="4">
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="6">
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="S5">
+        <v>2027</v>
+      </c>
+      <c r="T5" s="4">
+        <v>7.3726851851851861E-3</v>
+      </c>
+      <c r="U5" s="5">
+        <v>7.0023148148148154E-3</v>
+      </c>
+      <c r="V5" s="5">
+        <v>7.106481481481481E-3</v>
+      </c>
+      <c r="W5" s="5"/>
+      <c r="X5" s="6">
+        <v>7.0023148148148154E-3</v>
+      </c>
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA5">
+        <v>2029</v>
+      </c>
+      <c r="AB5" s="4">
+        <v>1.2361111111111113E-2</v>
+      </c>
+      <c r="AC5" s="5"/>
+      <c r="AD5" s="5"/>
+      <c r="AE5" s="5"/>
+      <c r="AF5" s="6">
+        <v>1.2361111111111113E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>2028</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1.4467592592592594E-3</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="6">
+        <v>1.4467592592592594E-3</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6">
+        <v>2029</v>
+      </c>
+      <c r="L6" s="4">
+        <v>3.37962962962963E-3</v>
+      </c>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="6">
+        <v>3.37962962962963E-3</v>
+      </c>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="S6">
+        <v>2029</v>
+      </c>
+      <c r="T6" s="4">
+        <v>7.4421296296296293E-3</v>
+      </c>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="6">
+        <v>7.4421296296296293E-3</v>
+      </c>
+      <c r="Y6" s="8"/>
+      <c r="Z6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA6">
+        <v>2029</v>
+      </c>
+      <c r="AB6" s="4">
+        <v>1.2372685185185186E-2</v>
+      </c>
+      <c r="AC6" s="5"/>
+      <c r="AD6" s="5"/>
+      <c r="AE6" s="5"/>
+      <c r="AF6" s="6">
+        <v>1.2372685185185186E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1.3773148148148147E-3</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1.3541666666666667E-3</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1.3773148148148147E-3</v>
+      </c>
+      <c r="H7" s="6">
+        <v>1.3541666666666667E-3</v>
+      </c>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>2029</v>
+      </c>
+      <c r="L7" s="4">
+        <v>3.3912037037037036E-3</v>
+      </c>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="6">
+        <v>3.3912037037037036E-3</v>
+      </c>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="S7">
+        <v>2028</v>
+      </c>
+      <c r="T7" s="4">
+        <v>7.4884259259259262E-3</v>
+      </c>
+      <c r="U7" s="5">
+        <v>7.3611111111111108E-3</v>
+      </c>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="6">
+        <v>7.3611111111111108E-3</v>
+      </c>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7">
+        <v>2028</v>
+      </c>
+      <c r="AB7" s="4">
+        <v>1.2465277777777777E-2</v>
+      </c>
+      <c r="AC7" s="5">
+        <v>1.1817129629629629E-2</v>
+      </c>
+      <c r="AD7" s="5"/>
+      <c r="AE7" s="5"/>
+      <c r="AF7" s="6">
+        <v>1.1817129629629629E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8">
+        <v>2029</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1.5046296296296294E-3</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="6">
+        <v>1.5046296296296294E-3</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8">
+        <v>2027</v>
+      </c>
+      <c r="L8" s="4">
+        <v>3.3912037037037036E-3</v>
+      </c>
+      <c r="M8" s="5">
+        <v>3.2175925925925926E-3</v>
+      </c>
+      <c r="N8" s="5">
+        <v>3.0555555555555557E-3</v>
+      </c>
+      <c r="O8" s="5"/>
+      <c r="P8" s="6">
+        <v>3.0555555555555557E-3</v>
+      </c>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="S8">
+        <v>2029</v>
+      </c>
+      <c r="T8" s="4">
+        <v>7.5347222222222213E-3</v>
+      </c>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="6">
+        <v>7.5347222222222213E-3</v>
+      </c>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA8">
+        <v>2027</v>
+      </c>
+      <c r="AB8" s="4">
+        <v>1.2534722222222223E-2</v>
+      </c>
+      <c r="AC8" s="5">
+        <v>1.1504629629629629E-2</v>
+      </c>
+      <c r="AD8" s="5">
+        <v>1.1400462962962965E-2</v>
+      </c>
+      <c r="AE8" s="5"/>
+      <c r="AF8" s="6">
+        <v>1.1400462962962965E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9">
+        <v>2026</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1.5046296296296294E-3</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1.4699074074074074E-3</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="6">
+        <v>1.4699074074074074E-3</v>
+      </c>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9">
+        <v>2028</v>
+      </c>
+      <c r="L9" s="4">
+        <v>3.4375E-3</v>
+      </c>
+      <c r="M9" s="5">
+        <v>3.4490740740740745E-3</v>
+      </c>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="6">
+        <v>3.4375E-3</v>
+      </c>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="S9">
+        <v>2026</v>
+      </c>
+      <c r="T9" s="4">
+        <v>7.5694444444444446E-3</v>
+      </c>
+      <c r="U9" s="5">
+        <v>7.037037037037037E-3</v>
+      </c>
+      <c r="V9" s="5">
+        <v>6.8865740740740736E-3</v>
+      </c>
+      <c r="W9" s="5">
+        <v>6.8865740740740736E-3</v>
+      </c>
+      <c r="X9" s="6">
+        <v>6.8865740740740736E-3</v>
+      </c>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA9">
+        <v>2028</v>
+      </c>
+      <c r="AB9" s="4">
+        <v>1.2534722222222223E-2</v>
+      </c>
+      <c r="AC9" s="5">
+        <v>1.2442129629629629E-2</v>
+      </c>
+      <c r="AD9" s="5"/>
+      <c r="AE9" s="5"/>
+      <c r="AF9" s="6">
+        <v>1.2442129629629629E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10">
+        <v>2027</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1.5162037037037036E-3</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1.5624999999999999E-3</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="6">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10">
+        <v>2026</v>
+      </c>
+      <c r="L10" s="4">
+        <v>3.4375E-3</v>
+      </c>
+      <c r="M10" s="5">
+        <v>3.2060185185185191E-3</v>
+      </c>
+      <c r="N10" s="5">
+        <v>3.1249999999999997E-3</v>
+      </c>
+      <c r="O10" s="5">
+        <v>3.1712962962962958E-3</v>
+      </c>
+      <c r="P10" s="6">
+        <v>3.1249999999999997E-3</v>
+      </c>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="S10">
+        <v>2026</v>
+      </c>
+      <c r="T10" s="4">
+        <v>7.5925925925925926E-3</v>
+      </c>
+      <c r="U10" s="5">
+        <v>7.5810185185185182E-3</v>
+      </c>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="6">
+        <v>7.5810185185185182E-3</v>
+      </c>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA10">
+        <v>2028</v>
+      </c>
+      <c r="AB10" s="4">
+        <v>1.2685185185185183E-2</v>
+      </c>
+      <c r="AC10" s="5">
+        <v>1.207175925925926E-2</v>
+      </c>
+      <c r="AD10" s="5"/>
+      <c r="AE10" s="5"/>
+      <c r="AF10" s="6">
+        <v>1.207175925925926E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11">
+        <v>2026</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1.5277777777777779E-3</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1.4699074074074074E-3</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1.3773148148148147E-3</v>
+      </c>
+      <c r="G11" s="5">
+        <v>1.423611111111111E-3</v>
+      </c>
+      <c r="H11" s="6">
+        <v>1.3773148148148147E-3</v>
+      </c>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11">
+        <v>2026</v>
+      </c>
+      <c r="L11" s="4">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="M11" s="5">
+        <v>3.1828703703703702E-3</v>
+      </c>
+      <c r="N11" s="5">
+        <v>2.8819444444444444E-3</v>
+      </c>
+      <c r="O11" s="5">
+        <v>2.8356481481481479E-3</v>
+      </c>
+      <c r="P11" s="6">
+        <v>2.8356481481481479E-3</v>
+      </c>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="S11">
+        <v>2026</v>
+      </c>
+      <c r="T11" s="4">
+        <v>7.5925925925925926E-3</v>
+      </c>
+      <c r="U11" s="5">
+        <v>7.5231481481481477E-3</v>
+      </c>
+      <c r="V11" s="5">
+        <v>7.2337962962962963E-3</v>
+      </c>
+      <c r="W11" s="5">
+        <v>7.1990740740740739E-3</v>
+      </c>
+      <c r="X11" s="6">
+        <v>7.1990740740740739E-3</v>
+      </c>
+      <c r="Y11" s="8"/>
+      <c r="Z11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA11">
+        <v>2027</v>
+      </c>
+      <c r="AB11" s="4">
+        <v>1.2719907407407407E-2</v>
+      </c>
+      <c r="AC11" s="5">
+        <v>1.2025462962962962E-2</v>
+      </c>
+      <c r="AD11" s="5">
+        <v>1.3113425925925926E-2</v>
+      </c>
+      <c r="AE11" s="5"/>
+      <c r="AF11" s="6">
+        <v>1.2025462962962962E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12">
+        <v>2027</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1.5277777777777779E-3</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1.4467592592592594E-3</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1.4120370370370369E-3</v>
+      </c>
+      <c r="G12" s="5"/>
+      <c r="H12" s="6">
+        <v>1.4120370370370369E-3</v>
+      </c>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12">
+        <v>2027</v>
+      </c>
+      <c r="L12" s="4">
+        <v>3.483796296296296E-3</v>
+      </c>
+      <c r="M12" s="5">
+        <v>3.3449074074074071E-3</v>
+      </c>
+      <c r="N12" s="5">
+        <v>3.2986111111111111E-3</v>
+      </c>
+      <c r="O12" s="5"/>
+      <c r="P12" s="6">
+        <v>3.2986111111111111E-3</v>
+      </c>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="S12">
+        <v>2027</v>
+      </c>
+      <c r="T12" s="4">
+        <v>7.6157407407407415E-3</v>
+      </c>
+      <c r="U12" s="5">
+        <v>7.1759259259259259E-3</v>
+      </c>
+      <c r="V12" s="5">
+        <v>6.828703703703704E-3</v>
+      </c>
+      <c r="W12" s="5"/>
+      <c r="X12" s="6">
+        <v>6.828703703703704E-3</v>
+      </c>
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA12">
+        <v>2027</v>
+      </c>
+      <c r="AB12" s="4">
+        <v>1.2789351851851852E-2</v>
+      </c>
+      <c r="AC12" s="5">
+        <v>1.1956018518518517E-2</v>
+      </c>
+      <c r="AD12" s="5">
+        <v>1.1319444444444444E-2</v>
+      </c>
+      <c r="AE12" s="5"/>
+      <c r="AF12" s="6">
+        <v>1.1319444444444444E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13">
+        <v>2026</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1.5393518518518519E-3</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1.4583333333333334E-3</v>
+      </c>
+      <c r="F13" s="5">
+        <v>1.4120370370370369E-3</v>
+      </c>
+      <c r="G13" s="5">
+        <v>1.4120370370370369E-3</v>
+      </c>
+      <c r="H13" s="6">
+        <v>1.4120370370370369E-3</v>
+      </c>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13">
+        <v>2027</v>
+      </c>
+      <c r="L13" s="4">
+        <v>3.5185185185185185E-3</v>
+      </c>
+      <c r="M13" s="5">
+        <v>3.4953703703703705E-3</v>
+      </c>
+      <c r="N13" s="5">
+        <v>3.3217592592592591E-3</v>
+      </c>
+      <c r="O13" s="5"/>
+      <c r="P13" s="6">
+        <v>3.3217592592592591E-3</v>
+      </c>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="S13">
+        <v>2028</v>
+      </c>
+      <c r="T13" s="4">
+        <v>7.6157407407407415E-3</v>
+      </c>
+      <c r="U13" s="5">
+        <v>7.1759259259259259E-3</v>
+      </c>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="6">
+        <v>7.1759259259259259E-3</v>
+      </c>
+      <c r="Y13" s="8"/>
+      <c r="Z13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA13">
+        <v>2029</v>
+      </c>
+      <c r="AB13" s="4">
+        <v>1.2858796296296297E-2</v>
+      </c>
+      <c r="AC13" s="5"/>
+      <c r="AD13" s="5"/>
+      <c r="AE13" s="5"/>
+      <c r="AF13" s="6">
+        <v>1.2858796296296297E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14">
+        <v>2027</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1.5393518518518519E-3</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1.5277777777777779E-3</v>
+      </c>
+      <c r="F14" s="5">
+        <v>1.5046296296296294E-3</v>
+      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="6">
+        <v>1.5046296296296294E-3</v>
+      </c>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14">
+        <v>2028</v>
+      </c>
+      <c r="L14" s="4">
+        <v>3.5185185185185185E-3</v>
+      </c>
+      <c r="M14" s="5">
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="6">
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="S14">
+        <v>2026</v>
+      </c>
+      <c r="T14" s="4">
+        <v>7.6388888888888886E-3</v>
+      </c>
+      <c r="U14" s="5">
+        <v>7.2453703703703708E-3</v>
+      </c>
+      <c r="V14" s="5">
+        <v>7.0023148148148154E-3</v>
+      </c>
+      <c r="W14" s="5">
+        <v>7.0601851851851841E-3</v>
+      </c>
+      <c r="X14" s="6">
+        <v>7.0023148148148154E-3</v>
+      </c>
+      <c r="Y14" s="8"/>
+      <c r="Z14" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA14">
+        <v>2027</v>
+      </c>
+      <c r="AB14" s="4">
+        <v>1.2870370370370372E-2</v>
+      </c>
+      <c r="AC14" s="5">
+        <v>1.1863425925925925E-2</v>
+      </c>
+      <c r="AD14" s="5">
+        <v>1.1608796296296296E-2</v>
+      </c>
+      <c r="AE14" s="5"/>
+      <c r="AF14" s="6">
+        <v>1.1608796296296296E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15">
+        <v>2027</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1.5624999999999999E-3</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1.5046296296296294E-3</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1.4467592592592594E-3</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="6">
+        <v>1.4467592592592594E-3</v>
+      </c>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K15">
+        <v>2026</v>
+      </c>
+      <c r="L15" s="4">
+        <v>3.530092592592592E-3</v>
+      </c>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5">
+        <v>3.4027777777777784E-3</v>
+      </c>
+      <c r="O15" s="5"/>
+      <c r="P15" s="6">
+        <v>3.4027777777777784E-3</v>
+      </c>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="S15">
+        <v>2029</v>
+      </c>
+      <c r="T15" s="4">
+        <v>7.6504629629629631E-3</v>
+      </c>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="6">
+        <v>7.6504629629629631E-3</v>
+      </c>
+      <c r="Y15" s="8"/>
+      <c r="Z15" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA15">
+        <v>2026</v>
+      </c>
+      <c r="AB15" s="4">
+        <v>1.2870370370370372E-2</v>
+      </c>
+      <c r="AC15" s="5">
+        <v>1.1631944444444445E-2</v>
+      </c>
+      <c r="AD15" s="5">
+        <v>1.1180555555555556E-2</v>
+      </c>
+      <c r="AE15" s="5">
+        <v>1.0983796296296297E-2</v>
+      </c>
+      <c r="AF15" s="6">
+        <v>1.0983796296296297E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16">
+        <v>2027</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1.5740740740740741E-3</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1.4814814814814814E-3</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1.4583333333333334E-3</v>
+      </c>
+      <c r="G16" s="5"/>
+      <c r="H16" s="6">
+        <v>1.4583333333333334E-3</v>
+      </c>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K16">
+        <v>2029</v>
+      </c>
+      <c r="L16" s="4">
+        <v>3.5532407407407405E-3</v>
+      </c>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="6">
+        <v>3.5532407407407405E-3</v>
+      </c>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="S16">
+        <v>2029</v>
+      </c>
+      <c r="T16" s="4">
+        <v>7.6851851851851847E-3</v>
+      </c>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="6">
+        <v>7.6851851851851847E-3</v>
+      </c>
+      <c r="Y16" s="8"/>
+      <c r="Z16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA16">
+        <v>2026</v>
+      </c>
+      <c r="AB16" s="4">
+        <v>1.2881944444444446E-2</v>
+      </c>
+      <c r="AC16" s="5">
+        <v>1.2013888888888888E-2</v>
+      </c>
+      <c r="AD16" s="5">
+        <v>1.1736111111111109E-2</v>
+      </c>
+      <c r="AE16" s="5">
+        <v>1.1423611111111112E-2</v>
+      </c>
+      <c r="AF16" s="6">
+        <v>1.1423611111111112E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17">
+        <v>2029</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1.5856481481481479E-3</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="6">
+        <v>1.5856481481481479E-3</v>
+      </c>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17">
+        <v>2027</v>
+      </c>
+      <c r="L17" s="4">
+        <v>3.5648148148148154E-3</v>
+      </c>
+      <c r="M17" s="5">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="N17" s="5">
+        <v>3.3680555555555551E-3</v>
+      </c>
+      <c r="O17" s="5"/>
+      <c r="P17" s="6">
+        <v>3.3680555555555551E-3</v>
+      </c>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="S17">
+        <v>2027</v>
+      </c>
+      <c r="T17" s="4">
+        <v>7.6851851851851847E-3</v>
+      </c>
+      <c r="U17" s="5">
+        <v>7.5231481481481477E-3</v>
+      </c>
+      <c r="V17" s="5">
+        <v>7.4189814814814813E-3</v>
+      </c>
+      <c r="W17" s="5"/>
+      <c r="X17" s="6">
+        <v>7.4189814814814813E-3</v>
+      </c>
+      <c r="Y17" s="8"/>
+      <c r="Z17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA17">
+        <v>2026</v>
+      </c>
+      <c r="AB17" s="4">
+        <v>1.3032407407407407E-2</v>
+      </c>
+      <c r="AC17" s="5">
+        <v>1.1701388888888891E-2</v>
+      </c>
+      <c r="AD17" s="5">
+        <v>1.0925925925925924E-2</v>
+      </c>
+      <c r="AE17" s="5">
+        <v>1.0439814814814813E-2</v>
+      </c>
+      <c r="AF17" s="6">
+        <v>1.0439814814814813E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18">
+        <v>2027</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1.5856481481481479E-3</v>
+      </c>
+      <c r="E18" s="5">
+        <v>1.5162037037037036E-3</v>
+      </c>
+      <c r="F18" s="5">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="6">
+        <v>1.4930555555555556E-3</v>
+      </c>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18">
+        <v>2026</v>
+      </c>
+      <c r="L18" s="4">
+        <v>3.5763888888888894E-3</v>
+      </c>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5">
+        <v>3.425925925925926E-3</v>
+      </c>
+      <c r="O18" s="5">
+        <v>3.1712962962962958E-3</v>
+      </c>
+      <c r="P18" s="6">
+        <v>3.1712962962962958E-3</v>
+      </c>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="S18">
+        <v>2029</v>
+      </c>
+      <c r="T18" s="4">
+        <v>7.6851851851851847E-3</v>
+      </c>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="6">
+        <v>7.6851851851851847E-3</v>
+      </c>
+      <c r="Y18" s="8"/>
+      <c r="Z18" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA18">
+        <v>2027</v>
+      </c>
+      <c r="AB18" s="4">
+        <v>1.3055555555555556E-2</v>
+      </c>
+      <c r="AC18" s="5">
+        <v>1.2789351851851852E-2</v>
+      </c>
+      <c r="AD18" s="5">
+        <v>1.2511574074074073E-2</v>
+      </c>
+      <c r="AE18" s="5"/>
+      <c r="AF18" s="6">
+        <v>1.2511574074074073E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19">
+        <v>2027</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1.5972222222222221E-3</v>
+      </c>
+      <c r="E19" s="5">
+        <v>1.4467592592592594E-3</v>
+      </c>
+      <c r="F19" s="5">
+        <v>1.4814814814814814E-3</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="6">
+        <v>1.4467592592592594E-3</v>
+      </c>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19">
+        <v>2029</v>
+      </c>
+      <c r="L19" s="4">
+        <v>3.5995370370370369E-3</v>
+      </c>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="6">
+        <v>3.5995370370370369E-3</v>
+      </c>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="S19">
+        <v>2028</v>
+      </c>
+      <c r="T19" s="4">
+        <v>7.7546296296296287E-3</v>
+      </c>
+      <c r="U19" s="5">
+        <v>7.2453703703703708E-3</v>
+      </c>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="6">
+        <v>7.2453703703703708E-3</v>
+      </c>
+      <c r="Y19" s="8"/>
+      <c r="Z19" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA19">
+        <v>2026</v>
+      </c>
+      <c r="AB19" s="4">
+        <v>1.306712962962963E-2</v>
+      </c>
+      <c r="AC19" s="5">
+        <v>1.2905092592592591E-2</v>
+      </c>
+      <c r="AD19" s="5">
+        <v>1.2002314814814815E-2</v>
+      </c>
+      <c r="AE19" s="5">
+        <v>1.224537037037037E-2</v>
+      </c>
+      <c r="AF19" s="6">
+        <v>1.2002314814814815E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20">
+        <v>2028</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1.5972222222222221E-3</v>
+      </c>
+      <c r="E20" s="5">
+        <v>1.5509259259259261E-3</v>
+      </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="6">
+        <v>1.5509259259259261E-3</v>
+      </c>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K20">
+        <v>2028</v>
+      </c>
+      <c r="L20" s="4">
+        <v>3.6111111111111114E-3</v>
+      </c>
+      <c r="M20" s="5">
+        <v>3.7962962962962963E-3</v>
+      </c>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="6">
+        <v>3.6111111111111114E-3</v>
+      </c>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="S20">
+        <v>2026</v>
+      </c>
+      <c r="T20" s="4">
+        <v>7.8356481481481489E-3</v>
+      </c>
+      <c r="U20" s="5">
+        <v>6.9907407407407409E-3</v>
+      </c>
+      <c r="V20" s="5">
+        <v>6.4351851851851861E-3</v>
+      </c>
+      <c r="W20" s="5">
+        <v>6.4120370370370364E-3</v>
+      </c>
+      <c r="X20" s="6">
+        <v>6.4120370370370364E-3</v>
+      </c>
+      <c r="Y20" s="8"/>
+      <c r="Z20" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA20">
+        <v>2027</v>
+      </c>
+      <c r="AB20" s="4">
+        <v>1.34375E-2</v>
+      </c>
+      <c r="AC20" s="5">
+        <v>1.2314814814814815E-2</v>
+      </c>
+      <c r="AD20" s="5">
+        <v>1.2268518518518519E-2</v>
+      </c>
+      <c r="AE20" s="5"/>
+      <c r="AF20" s="6">
+        <v>1.2268518518518519E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21">
+        <v>2028</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1.6087962962962963E-3</v>
+      </c>
+      <c r="E21" s="5">
+        <v>1.5162037037037036E-3</v>
+      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="6">
+        <v>1.5162037037037036E-3</v>
+      </c>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21">
+        <v>2027</v>
+      </c>
+      <c r="L21" s="4">
+        <v>3.6574074074074074E-3</v>
+      </c>
+      <c r="M21" s="5">
+        <v>3.4027777777777784E-3</v>
+      </c>
+      <c r="N21" s="5">
+        <v>3.2870370370370367E-3</v>
+      </c>
+      <c r="O21" s="5"/>
+      <c r="P21" s="6">
+        <v>3.2870370370370367E-3</v>
+      </c>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="S21">
+        <v>2027</v>
+      </c>
+      <c r="T21" s="4">
+        <v>7.858796296296296E-3</v>
+      </c>
+      <c r="U21" s="5">
+        <v>7.6504629629629631E-3</v>
+      </c>
+      <c r="V21" s="5">
+        <v>7.7314814814814815E-3</v>
+      </c>
+      <c r="W21" s="5"/>
+      <c r="X21" s="6">
+        <v>7.6504629629629631E-3</v>
+      </c>
+      <c r="Y21" s="8"/>
+      <c r="Z21" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA21">
+        <v>2027</v>
+      </c>
+      <c r="AB21" s="4">
+        <v>1.3449074074074073E-2</v>
+      </c>
+      <c r="AC21" s="5">
+        <v>1.2129629629629629E-2</v>
+      </c>
+      <c r="AD21" s="5">
+        <v>1.2152777777777778E-2</v>
+      </c>
+      <c r="AE21" s="5"/>
+      <c r="AF21" s="6">
+        <v>1.2129629629629629E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22">
+        <v>2028</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1.6319444444444445E-3</v>
+      </c>
+      <c r="E22" s="5">
+        <v>1.5393518518518519E-3</v>
+      </c>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="6">
+        <v>1.5393518518518519E-3</v>
+      </c>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K22">
+        <v>2027</v>
+      </c>
+      <c r="L22" s="4">
+        <v>3.6805555555555554E-3</v>
+      </c>
+      <c r="M22" s="5">
+        <v>3.4606481481481485E-3</v>
+      </c>
+      <c r="N22" s="5">
+        <v>3.3101851851851851E-3</v>
+      </c>
+      <c r="O22" s="5"/>
+      <c r="P22" s="6">
+        <v>3.3101851851851851E-3</v>
+      </c>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="S22">
+        <v>2026</v>
+      </c>
+      <c r="T22" s="4">
+        <v>7.8703703703703713E-3</v>
+      </c>
+      <c r="U22" s="5">
+        <v>7.6157407407407415E-3</v>
+      </c>
+      <c r="V22" s="5">
+        <v>7.4074074074074068E-3</v>
+      </c>
+      <c r="W22" s="5"/>
+      <c r="X22" s="6">
+        <v>7.4074074074074068E-3</v>
+      </c>
+      <c r="Y22" s="8"/>
+      <c r="Z22" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA22">
+        <v>2029</v>
+      </c>
+      <c r="AB22" s="4">
+        <v>1.3483796296296298E-2</v>
+      </c>
+      <c r="AC22" s="5"/>
+      <c r="AD22" s="5"/>
+      <c r="AE22" s="5"/>
+      <c r="AF22" s="6">
+        <v>1.3483796296296298E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23">
+        <v>2027</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1.6319444444444445E-3</v>
+      </c>
+      <c r="E23" s="5">
+        <v>1.5624999999999999E-3</v>
+      </c>
+      <c r="F23" s="5">
+        <v>1.4583333333333334E-3</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="6">
+        <v>1.4583333333333334E-3</v>
+      </c>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K23">
+        <v>2026</v>
+      </c>
+      <c r="L23" s="4">
+        <v>3.6921296296296298E-3</v>
+      </c>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5">
+        <v>3.1712962962962958E-3</v>
+      </c>
+      <c r="O23" s="5">
+        <v>3.4027777777777784E-3</v>
+      </c>
+      <c r="P23" s="6">
+        <v>3.1712962962962958E-3</v>
+      </c>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="S23">
+        <v>2027</v>
+      </c>
+      <c r="T23" s="4">
+        <v>7.9398148148148145E-3</v>
+      </c>
+      <c r="U23" s="5">
+        <v>7.5347222222222213E-3</v>
+      </c>
+      <c r="V23" s="5">
+        <v>8.2986111111111108E-3</v>
+      </c>
+      <c r="W23" s="5"/>
+      <c r="X23" s="6">
+        <v>7.5347222222222213E-3</v>
+      </c>
+      <c r="Y23" s="8"/>
+      <c r="Z23" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA23">
+        <v>2028</v>
+      </c>
+      <c r="AB23" s="4">
+        <v>1.3530092592592594E-2</v>
+      </c>
+      <c r="AC23" s="5">
+        <v>1.3287037037037036E-2</v>
+      </c>
+      <c r="AD23" s="5"/>
+      <c r="AE23" s="5"/>
+      <c r="AF23" s="6">
+        <v>1.3287037037037036E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24">
+        <v>2028</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1.6435185185185183E-3</v>
+      </c>
+      <c r="E24" s="5">
+        <v>1.689814814814815E-3</v>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="6">
+        <v>1.6435185185185183E-3</v>
+      </c>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="K24">
+        <v>2027</v>
+      </c>
+      <c r="L24" s="4">
+        <v>3.7037037037037034E-3</v>
+      </c>
+      <c r="M24" s="5">
+        <v>3.37962962962963E-3</v>
+      </c>
+      <c r="N24" s="5">
+        <v>3.1597222222222222E-3</v>
+      </c>
+      <c r="O24" s="5"/>
+      <c r="P24" s="6">
+        <v>3.1597222222222222E-3</v>
+      </c>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="S24">
+        <v>2029</v>
+      </c>
+      <c r="T24" s="4">
+        <v>7.951388888888888E-3</v>
+      </c>
+      <c r="U24" s="5"/>
+      <c r="V24" s="5"/>
+      <c r="W24" s="5"/>
+      <c r="X24" s="6">
+        <v>7.951388888888888E-3</v>
+      </c>
+      <c r="Y24" s="8"/>
+      <c r="Z24" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA24">
+        <v>2029</v>
+      </c>
+      <c r="AB24" s="4">
+        <v>1.3668981481481482E-2</v>
+      </c>
+      <c r="AC24" s="5"/>
+      <c r="AD24" s="5"/>
+      <c r="AE24" s="5"/>
+      <c r="AF24" s="6">
+        <v>1.3668981481481482E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25">
+        <v>2027</v>
+      </c>
+      <c r="D25" s="4">
+        <v>1.6435185185185183E-3</v>
+      </c>
+      <c r="E25" s="5">
+        <v>1.5046296296296294E-3</v>
+      </c>
+      <c r="F25" s="5">
+        <v>1.4699074074074074E-3</v>
+      </c>
+      <c r="G25" s="5"/>
+      <c r="H25" s="6">
+        <v>1.4699074074074074E-3</v>
+      </c>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="K25">
+        <v>2028</v>
+      </c>
+      <c r="L25" s="4">
+        <v>3.7152777777777774E-3</v>
+      </c>
+      <c r="M25" s="5">
+        <v>3.2291666666666666E-3</v>
+      </c>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="6">
+        <v>3.2291666666666666E-3</v>
+      </c>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="S25">
+        <v>2027</v>
+      </c>
+      <c r="T25" s="4">
+        <v>7.9745370370370369E-3</v>
+      </c>
+      <c r="U25" s="5">
+        <v>7.3958333333333341E-3</v>
+      </c>
+      <c r="V25" s="5">
+        <v>7.2569444444444443E-3</v>
+      </c>
+      <c r="W25" s="5"/>
+      <c r="X25" s="6">
+        <v>7.2569444444444443E-3</v>
+      </c>
+      <c r="Y25" s="8"/>
+      <c r="Z25" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA25">
+        <v>2026</v>
+      </c>
+      <c r="AB25" s="4">
+        <v>1.3703703703703704E-2</v>
+      </c>
+      <c r="AC25" s="5">
+        <v>1.238425925925926E-2</v>
+      </c>
+      <c r="AD25" s="5">
+        <v>1.1678240740740741E-2</v>
+      </c>
+      <c r="AE25" s="5">
+        <v>1.1805555555555555E-2</v>
+      </c>
+      <c r="AF25" s="6">
+        <v>1.1678240740740741E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26">
+        <v>2028</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1.6550925925925926E-3</v>
+      </c>
+      <c r="E26" s="5">
+        <v>1.5162037037037036E-3</v>
+      </c>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="6">
+        <v>1.5162037037037036E-3</v>
+      </c>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K26">
+        <v>2027</v>
+      </c>
+      <c r="L26" s="4">
+        <v>3.7384259259259263E-3</v>
+      </c>
+      <c r="M26" s="5">
+        <v>3.7847222222222223E-3</v>
+      </c>
+      <c r="N26" s="5">
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="O26" s="5"/>
+      <c r="P26" s="6">
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="S26">
+        <v>2027</v>
+      </c>
+      <c r="T26" s="4">
+        <v>7.9861111111111122E-3</v>
+      </c>
+      <c r="U26" s="5">
+        <v>7.4074074074074068E-3</v>
+      </c>
+      <c r="V26" s="5">
+        <v>7.1180555555555554E-3</v>
+      </c>
+      <c r="W26" s="5"/>
+      <c r="X26" s="6">
+        <v>7.1180555555555554E-3</v>
+      </c>
+      <c r="Y26" s="8"/>
+      <c r="Z26" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA26">
+        <v>2028</v>
+      </c>
+      <c r="AB26" s="4">
+        <v>1.3703703703703704E-2</v>
+      </c>
+      <c r="AC26" s="5">
+        <v>1.3645833333333331E-2</v>
+      </c>
+      <c r="AD26" s="5"/>
+      <c r="AE26" s="5"/>
+      <c r="AF26" s="6">
+        <v>1.3645833333333331E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:32">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27">
+        <v>2026</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1.6550925925925926E-3</v>
+      </c>
+      <c r="E27" s="5">
+        <v>1.5046296296296294E-3</v>
+      </c>
+      <c r="F27" s="5">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="G27" s="5">
+        <v>1.2962962962962963E-3</v>
+      </c>
+      <c r="H27" s="6">
+        <v>1.2962962962962963E-3</v>
+      </c>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K27">
+        <v>2028</v>
+      </c>
+      <c r="L27" s="4">
+        <v>3.8310185185185183E-3</v>
+      </c>
+      <c r="M27" s="5">
+        <v>3.7037037037037034E-3</v>
+      </c>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="6">
+        <v>3.7037037037037034E-3</v>
+      </c>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="S27">
+        <v>2027</v>
+      </c>
+      <c r="T27" s="4">
+        <v>8.1944444444444452E-3</v>
+      </c>
+      <c r="U27" s="5">
+        <v>7.8472222222222224E-3</v>
+      </c>
+      <c r="V27" s="5">
+        <v>7.2106481481481475E-3</v>
+      </c>
+      <c r="W27" s="5"/>
+      <c r="X27" s="6">
+        <v>7.2106481481481475E-3</v>
+      </c>
+      <c r="Y27" s="8"/>
+      <c r="Z27" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA27">
+        <v>2027</v>
+      </c>
+      <c r="AB27" s="4">
+        <v>1.3715277777777778E-2</v>
+      </c>
+      <c r="AC27" s="5">
+        <v>1.2824074074074073E-2</v>
+      </c>
+      <c r="AD27" s="5">
+        <v>1.238425925925926E-2</v>
+      </c>
+      <c r="AE27" s="5"/>
+      <c r="AF27" s="6">
+        <v>1.238425925925926E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28">
+        <v>2027</v>
+      </c>
+      <c r="D28" s="4">
+        <v>1.6782407407407406E-3</v>
+      </c>
+      <c r="E28" s="5">
+        <v>1.712962962962963E-3</v>
+      </c>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="6">
+        <v>1.6782407407407406E-3</v>
+      </c>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="K28">
+        <v>2026</v>
+      </c>
+      <c r="L28" s="4">
+        <v>3.8657407407407408E-3</v>
+      </c>
+      <c r="M28" s="5">
+        <v>3.5648148148148154E-3</v>
+      </c>
+      <c r="N28" s="5">
+        <v>3.5069444444444445E-3</v>
+      </c>
+      <c r="O28" s="5"/>
+      <c r="P28" s="6">
+        <v>3.5069444444444445E-3</v>
+      </c>
+      <c r="Q28" s="8"/>
+      <c r="R28" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="S28">
+        <v>2029</v>
+      </c>
+      <c r="T28" s="4">
+        <v>8.2407407407407412E-3</v>
+      </c>
+      <c r="U28" s="5"/>
+      <c r="V28" s="5"/>
+      <c r="W28" s="5"/>
+      <c r="X28" s="6">
+        <v>8.2407407407407412E-3</v>
+      </c>
+      <c r="Y28" s="8"/>
+      <c r="Z28" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA28">
+        <v>2029</v>
+      </c>
+      <c r="AB28" s="4">
+        <v>1.3738425925925926E-2</v>
+      </c>
+      <c r="AC28" s="5"/>
+      <c r="AD28" s="5"/>
+      <c r="AE28" s="5"/>
+      <c r="AF28" s="6">
+        <v>1.3738425925925926E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29">
+        <v>2029</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1.7013888888888892E-3</v>
+      </c>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="6">
+        <v>1.7013888888888892E-3</v>
+      </c>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="K29">
+        <v>2029</v>
+      </c>
+      <c r="L29" s="4">
+        <v>3.8773148148148143E-3</v>
+      </c>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="6">
+        <v>3.8773148148148143E-3</v>
+      </c>
+      <c r="Q29" s="8"/>
+      <c r="R29" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S29">
+        <v>2028</v>
+      </c>
+      <c r="T29" s="4">
+        <v>8.2523148148148148E-3</v>
+      </c>
+      <c r="U29" s="5">
+        <v>7.8472222222222224E-3</v>
+      </c>
+      <c r="V29" s="5"/>
+      <c r="W29" s="5"/>
+      <c r="X29" s="6">
+        <v>7.8472222222222224E-3</v>
+      </c>
+      <c r="Y29" s="8"/>
+      <c r="Z29" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA29">
+        <v>2028</v>
+      </c>
+      <c r="AB29" s="4">
+        <v>1.3773148148148147E-2</v>
+      </c>
+      <c r="AC29" s="5">
+        <v>1.3194444444444444E-2</v>
+      </c>
+      <c r="AD29" s="5"/>
+      <c r="AE29" s="5"/>
+      <c r="AF29" s="6">
+        <v>1.3194444444444444E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:32">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30">
+        <v>2028</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1.7013888888888892E-3</v>
+      </c>
+      <c r="E30" s="5">
+        <v>1.6666666666666668E-3</v>
+      </c>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="6">
+        <v>1.6666666666666668E-3</v>
+      </c>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K30">
+        <v>2028</v>
+      </c>
+      <c r="L30" s="4">
+        <v>3.8888888888888883E-3</v>
+      </c>
+      <c r="M30" s="5">
+        <v>3.6805555555555554E-3</v>
+      </c>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="6">
+        <v>3.6805555555555554E-3</v>
+      </c>
+      <c r="Q30" s="8"/>
+      <c r="R30" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S30">
+        <v>2028</v>
+      </c>
+      <c r="T30" s="4">
+        <v>8.2754629629629619E-3</v>
+      </c>
+      <c r="U30" s="5"/>
+      <c r="V30" s="5"/>
+      <c r="W30" s="5"/>
+      <c r="X30" s="6">
+        <v>8.2754629629629619E-3</v>
+      </c>
+      <c r="Y30" s="8"/>
+      <c r="Z30" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA30">
+        <v>2028</v>
+      </c>
+      <c r="AB30" s="4">
+        <v>1.3784722222222224E-2</v>
+      </c>
+      <c r="AC30" s="5">
+        <v>1.3020833333333334E-2</v>
+      </c>
+      <c r="AD30" s="5"/>
+      <c r="AE30" s="5"/>
+      <c r="AF30" s="6">
+        <v>1.3020833333333334E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31">
+        <v>2029</v>
+      </c>
+      <c r="D31" s="4">
+        <v>1.712962962962963E-3</v>
+      </c>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="6">
+        <v>1.712962962962963E-3</v>
+      </c>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="K31">
+        <v>2029</v>
+      </c>
+      <c r="L31" s="4">
+        <v>3.9583333333333337E-3</v>
+      </c>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="6">
+        <v>3.9583333333333337E-3</v>
+      </c>
+      <c r="Q31" s="8"/>
+      <c r="R31" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="S31">
+        <v>2028</v>
+      </c>
+      <c r="T31" s="4">
+        <v>8.3912037037037045E-3</v>
+      </c>
+      <c r="U31" s="5">
+        <v>8.4259259259259253E-3</v>
+      </c>
+      <c r="V31" s="5"/>
+      <c r="W31" s="5"/>
+      <c r="X31" s="6">
+        <v>8.3912037037037045E-3</v>
+      </c>
+      <c r="Y31" s="8"/>
+      <c r="Z31" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA31">
+        <v>2028</v>
+      </c>
+      <c r="AB31" s="4">
+        <v>1.3993055555555555E-2</v>
+      </c>
+      <c r="AC31" s="5">
+        <v>1.3310185185185187E-2</v>
+      </c>
+      <c r="AD31" s="5"/>
+      <c r="AE31" s="5"/>
+      <c r="AF31" s="6">
+        <v>1.3310185185185187E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:32">
+      <c r="A32" s="8"/>
+      <c r="B32" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32">
+        <v>2029</v>
+      </c>
+      <c r="D32" s="4">
+        <v>1.736111111111111E-3</v>
+      </c>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="6">
+        <v>1.736111111111111E-3</v>
+      </c>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="K32">
+        <v>2027</v>
+      </c>
+      <c r="L32" s="4">
+        <v>3.9583333333333337E-3</v>
+      </c>
+      <c r="M32" s="5">
+        <v>3.6111111111111114E-3</v>
+      </c>
+      <c r="N32" s="5">
+        <v>3.3680555555555551E-3</v>
+      </c>
+      <c r="O32" s="5"/>
+      <c r="P32" s="6">
+        <v>3.3680555555555551E-3</v>
+      </c>
+      <c r="Q32" s="8"/>
+      <c r="R32" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="S32">
+        <v>2027</v>
+      </c>
+      <c r="T32" s="4">
+        <v>8.4490740740740741E-3</v>
+      </c>
+      <c r="U32" s="5">
+        <v>7.7662037037037031E-3</v>
+      </c>
+      <c r="V32" s="5">
+        <v>7.4652777777777781E-3</v>
+      </c>
+      <c r="W32" s="5"/>
+      <c r="X32" s="6">
+        <v>7.4652777777777781E-3</v>
+      </c>
+      <c r="Y32" s="8"/>
+      <c r="Z32" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA32">
+        <v>2029</v>
+      </c>
+      <c r="AB32" s="4">
+        <v>1.4039351851851851E-2</v>
+      </c>
+      <c r="AC32" s="5"/>
+      <c r="AD32" s="5"/>
+      <c r="AE32" s="5"/>
+      <c r="AF32" s="6">
+        <v>1.4039351851851851E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:32">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33">
+        <v>2029</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1.736111111111111E-3</v>
+      </c>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="6">
+        <v>1.736111111111111E-3</v>
+      </c>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="K33">
+        <v>2029</v>
+      </c>
+      <c r="L33" s="4">
+        <v>3.9699074074074072E-3</v>
+      </c>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="6">
+        <v>3.9699074074074072E-3</v>
+      </c>
+      <c r="Q33" s="8"/>
+      <c r="R33" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="S33">
+        <v>2029</v>
+      </c>
+      <c r="T33" s="4">
+        <v>8.5879629629629622E-3</v>
+      </c>
+      <c r="U33" s="5"/>
+      <c r="V33" s="5"/>
+      <c r="W33" s="5"/>
+      <c r="X33" s="6">
+        <v>8.5879629629629622E-3</v>
+      </c>
+      <c r="Y33" s="8"/>
+      <c r="Z33" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA33">
+        <v>2027</v>
+      </c>
+      <c r="AB33" s="4">
+        <v>1.4097222222222221E-2</v>
+      </c>
+      <c r="AC33" s="5">
+        <v>1.5335648148148147E-2</v>
+      </c>
+      <c r="AD33" s="5">
+        <v>1.3877314814814815E-2</v>
+      </c>
+      <c r="AE33" s="5"/>
+      <c r="AF33" s="6">
+        <v>1.3877314814814815E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:32">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34">
+        <v>2026</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1.7476851851851852E-3</v>
+      </c>
+      <c r="E34" s="5">
+        <v>1.712962962962963E-3</v>
+      </c>
+      <c r="F34" s="5">
+        <v>1.689814814814815E-3</v>
+      </c>
+      <c r="G34" s="5"/>
+      <c r="H34" s="6">
+        <v>1.689814814814815E-3</v>
+      </c>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="K34">
+        <v>2027</v>
+      </c>
+      <c r="L34" s="4">
+        <v>3.9930555555555561E-3</v>
+      </c>
+      <c r="M34" s="5">
+        <v>3.7037037037037034E-3</v>
+      </c>
+      <c r="N34" s="5">
+        <v>3.3680555555555551E-3</v>
+      </c>
+      <c r="O34" s="5"/>
+      <c r="P34" s="6">
+        <v>3.3680555555555551E-3</v>
+      </c>
+      <c r="Q34" s="8"/>
+      <c r="R34" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="S34">
+        <v>2029</v>
+      </c>
+      <c r="T34" s="4">
+        <v>8.6226851851851846E-3</v>
+      </c>
+      <c r="U34" s="5"/>
+      <c r="V34" s="5"/>
+      <c r="W34" s="5"/>
+      <c r="X34" s="6">
+        <v>8.6226851851851846E-3</v>
+      </c>
+      <c r="Y34" s="8"/>
+      <c r="Z34" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA34">
+        <v>2027</v>
+      </c>
+      <c r="AB34" s="4">
+        <v>1.4189814814814815E-2</v>
+      </c>
+      <c r="AC34" s="5">
+        <v>1.2337962962962962E-2</v>
+      </c>
+      <c r="AD34" s="5">
+        <v>1.2037037037037035E-2</v>
+      </c>
+      <c r="AE34" s="5"/>
+      <c r="AF34" s="6">
+        <v>1.2037037037037035E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:32">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35">
+        <v>2029</v>
+      </c>
+      <c r="D35" s="4">
+        <v>1.7708333333333332E-3</v>
+      </c>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="6">
+        <v>1.7708333333333332E-3</v>
+      </c>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K35">
+        <v>2027</v>
+      </c>
+      <c r="L35" s="4">
+        <v>3.9930555555555561E-3</v>
+      </c>
+      <c r="M35" s="5">
+        <v>4.0046296296296297E-3</v>
+      </c>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="6">
+        <v>3.9930555555555561E-3</v>
+      </c>
+      <c r="Q35" s="8"/>
+      <c r="R35" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="S35">
+        <v>2027</v>
+      </c>
+      <c r="T35" s="4">
+        <v>8.6342592592592599E-3</v>
+      </c>
+      <c r="U35" s="5"/>
+      <c r="V35" s="5">
+        <v>7.5115740740740742E-3</v>
+      </c>
+      <c r="W35" s="5"/>
+      <c r="X35" s="6">
+        <v>7.5115740740740742E-3</v>
+      </c>
+      <c r="Y35" s="8"/>
+      <c r="Z35" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA35">
+        <v>2029</v>
+      </c>
+      <c r="AB35" s="4">
+        <v>1.4201388888888888E-2</v>
+      </c>
+      <c r="AC35" s="5"/>
+      <c r="AD35" s="5"/>
+      <c r="AE35" s="5"/>
+      <c r="AF35" s="6">
+        <v>1.4201388888888888E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:32">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36">
+        <v>2029</v>
+      </c>
+      <c r="D36" s="4">
+        <v>1.7824074074074072E-3</v>
+      </c>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="6">
+        <v>1.7824074074074072E-3</v>
+      </c>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K36">
+        <v>2029</v>
+      </c>
+      <c r="L36" s="4">
+        <v>4.0162037037037033E-3</v>
+      </c>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="6">
+        <v>4.0162037037037033E-3</v>
+      </c>
+      <c r="Q36" s="8"/>
+      <c r="R36" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="S36">
+        <v>2027</v>
+      </c>
+      <c r="T36" s="4">
+        <v>8.6458333333333335E-3</v>
+      </c>
+      <c r="U36" s="5"/>
+      <c r="V36" s="5"/>
+      <c r="W36" s="5"/>
+      <c r="X36" s="6">
+        <v>8.6458333333333335E-3</v>
+      </c>
+      <c r="Y36" s="8"/>
+      <c r="Z36" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA36">
+        <v>2027</v>
+      </c>
+      <c r="AB36" s="4">
+        <v>1.4456018518518519E-2</v>
+      </c>
+      <c r="AC36" s="5">
+        <v>1.2569444444444446E-2</v>
+      </c>
+      <c r="AD36" s="5">
+        <v>1.2175925925925929E-2</v>
+      </c>
+      <c r="AE36" s="5"/>
+      <c r="AF36" s="6">
+        <v>1.2175925925925929E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:32">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37">
+        <v>2027</v>
+      </c>
+      <c r="D37" s="4">
+        <v>1.8055555555555557E-3</v>
+      </c>
+      <c r="E37" s="5">
+        <v>1.712962962962963E-3</v>
+      </c>
+      <c r="F37" s="5">
+        <v>1.5624999999999999E-3</v>
+      </c>
+      <c r="G37" s="5"/>
+      <c r="H37" s="6">
+        <v>1.5624999999999999E-3</v>
+      </c>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K37">
+        <v>2029</v>
+      </c>
+      <c r="L37" s="4">
+        <v>4.0277777777777777E-3</v>
+      </c>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="6">
+        <v>4.0277777777777777E-3</v>
+      </c>
+      <c r="Q37" s="8"/>
+      <c r="R37" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="S37">
+        <v>2029</v>
+      </c>
+      <c r="T37" s="4">
+        <v>8.6574074074074071E-3</v>
+      </c>
+      <c r="U37" s="5"/>
+      <c r="V37" s="5"/>
+      <c r="W37" s="5"/>
+      <c r="X37" s="6">
+        <v>8.6574074074074071E-3</v>
+      </c>
+      <c r="Y37" s="8"/>
+      <c r="Z37" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA37">
+        <v>2027</v>
+      </c>
+      <c r="AB37" s="4">
+        <v>1.503472222222222E-2</v>
+      </c>
+      <c r="AC37" s="5">
+        <v>1.4780092592592595E-2</v>
+      </c>
+      <c r="AD37" s="5">
+        <v>1.5439814814814816E-2</v>
+      </c>
+      <c r="AE37" s="5"/>
+      <c r="AF37" s="6">
+        <v>1.4780092592592595E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:32">
+      <c r="A38" s="8"/>
+      <c r="B38" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38">
+        <v>2027</v>
+      </c>
+      <c r="D38" s="4">
+        <v>1.8055555555555557E-3</v>
+      </c>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5">
+        <v>1.6782407407407406E-3</v>
+      </c>
+      <c r="G38" s="5"/>
+      <c r="H38" s="6">
+        <v>1.6782407407407406E-3</v>
+      </c>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K38">
+        <v>2029</v>
+      </c>
+      <c r="L38" s="4">
+        <v>4.0393518518518521E-3</v>
+      </c>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="6">
+        <v>4.0393518518518521E-3</v>
+      </c>
+      <c r="Q38" s="8"/>
+      <c r="R38" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="S38">
+        <v>2027</v>
+      </c>
+      <c r="T38" s="4">
+        <v>8.9583333333333338E-3</v>
+      </c>
+      <c r="U38" s="5"/>
+      <c r="V38" s="5">
+        <v>8.3796296296296292E-3</v>
+      </c>
+      <c r="W38" s="5"/>
+      <c r="X38" s="6">
+        <v>8.3796296296296292E-3</v>
+      </c>
+      <c r="Y38" s="8"/>
+      <c r="Z38" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA38">
+        <v>2027</v>
+      </c>
+      <c r="AB38" s="4">
+        <v>1.5208333333333332E-2</v>
+      </c>
+      <c r="AC38" s="5">
+        <v>1.2025462962962962E-2</v>
+      </c>
+      <c r="AD38" s="5">
+        <v>1.1469907407407408E-2</v>
+      </c>
+      <c r="AE38" s="5"/>
+      <c r="AF38" s="6">
+        <v>1.1469907407407408E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:32">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39">
+        <v>2027</v>
+      </c>
+      <c r="D39" s="4">
+        <v>1.8055555555555557E-3</v>
+      </c>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5">
+        <v>1.6319444444444445E-3</v>
+      </c>
+      <c r="G39" s="5"/>
+      <c r="H39" s="6">
+        <v>1.6319444444444445E-3</v>
+      </c>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="K39">
+        <v>2027</v>
+      </c>
+      <c r="L39" s="4">
+        <v>4.0624999999999993E-3</v>
+      </c>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5">
+        <v>3.8657407407407408E-3</v>
+      </c>
+      <c r="O39" s="5"/>
+      <c r="P39" s="6">
+        <v>3.8657407407407408E-3</v>
+      </c>
+      <c r="Q39" s="8"/>
+      <c r="R39" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="S39">
+        <v>2027</v>
+      </c>
+      <c r="T39" s="4">
+        <v>9.0046296296296298E-3</v>
+      </c>
+      <c r="U39" s="5"/>
+      <c r="V39" s="5">
+        <v>8.1712962962962963E-3</v>
+      </c>
+      <c r="W39" s="5"/>
+      <c r="X39" s="6">
+        <v>8.1712962962962963E-3</v>
+      </c>
+      <c r="Y39" s="8"/>
+      <c r="Z39" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA39">
+        <v>2029</v>
+      </c>
+      <c r="AB39" s="4">
+        <v>1.5289351851851851E-2</v>
+      </c>
+      <c r="AC39" s="5"/>
+      <c r="AD39" s="5"/>
+      <c r="AE39" s="5"/>
+      <c r="AF39" s="6">
+        <v>1.5289351851851851E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:32">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40">
+        <v>2029</v>
+      </c>
+      <c r="D40" s="4">
+        <v>1.8171296296296297E-3</v>
+      </c>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="6">
+        <v>1.8171296296296297E-3</v>
+      </c>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K40">
+        <v>2027</v>
+      </c>
+      <c r="L40" s="4">
+        <v>4.0856481481481481E-3</v>
+      </c>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5">
+        <v>3.7268518518518514E-3</v>
+      </c>
+      <c r="O40" s="5"/>
+      <c r="P40" s="6">
+        <v>3.7268518518518514E-3</v>
+      </c>
+      <c r="Q40" s="8"/>
+      <c r="R40" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="S40">
+        <v>2027</v>
+      </c>
+      <c r="T40" s="4">
+        <v>9.1203703703703707E-3</v>
+      </c>
+      <c r="U40" s="5"/>
+      <c r="V40" s="5">
+        <v>8.3101851851851861E-3</v>
+      </c>
+      <c r="W40" s="5"/>
+      <c r="X40" s="6">
+        <v>8.3101851851851861E-3</v>
+      </c>
+      <c r="Y40" s="8"/>
+      <c r="Z40" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA40">
+        <v>2027</v>
+      </c>
+      <c r="AB40" s="4">
+        <v>1.53125E-2</v>
+      </c>
+      <c r="AC40" s="5">
+        <v>1.4143518518518519E-2</v>
+      </c>
+      <c r="AD40" s="5">
+        <v>1.3541666666666667E-2</v>
+      </c>
+      <c r="AE40" s="5"/>
+      <c r="AF40" s="6">
+        <v>1.3541666666666667E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:32">
+      <c r="A41" s="8"/>
+      <c r="B41" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41">
+        <v>2027</v>
+      </c>
+      <c r="D41" s="4">
+        <v>1.8287037037037037E-3</v>
+      </c>
+      <c r="E41" s="5">
+        <v>1.7245370370370372E-3</v>
+      </c>
+      <c r="F41" s="5">
+        <v>1.6319444444444445E-3</v>
+      </c>
+      <c r="G41" s="5"/>
+      <c r="H41" s="6">
+        <v>1.6319444444444445E-3</v>
+      </c>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="K41">
+        <v>2029</v>
+      </c>
+      <c r="L41" s="4">
+        <v>4.1319444444444442E-3</v>
+      </c>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="6">
+        <v>4.1319444444444442E-3</v>
+      </c>
+      <c r="Q41" s="8"/>
+      <c r="R41" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="S41">
+        <v>2028</v>
+      </c>
+      <c r="T41" s="4">
+        <v>9.1550925925925931E-3</v>
+      </c>
+      <c r="U41" s="5">
+        <v>9.3749999999999997E-3</v>
+      </c>
+      <c r="V41" s="5"/>
+      <c r="W41" s="5"/>
+      <c r="X41" s="6">
+        <v>9.1550925925925931E-3</v>
+      </c>
+      <c r="Y41" s="8"/>
+      <c r="Z41" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA41">
+        <v>2027</v>
+      </c>
+      <c r="AB41" s="4">
+        <v>1.5428240740740741E-2</v>
+      </c>
+      <c r="AC41" s="5">
+        <v>1.2442129629629629E-2</v>
+      </c>
+      <c r="AD41" s="5">
+        <v>1.3981481481481482E-2</v>
+      </c>
+      <c r="AE41" s="5"/>
+      <c r="AF41" s="6">
+        <v>1.2442129629629629E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:32">
+      <c r="A42" s="8"/>
+      <c r="B42" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42">
+        <v>2027</v>
+      </c>
+      <c r="D42" s="4">
+        <v>1.8634259259259261E-3</v>
+      </c>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="6">
+        <v>1.8634259259259261E-3</v>
+      </c>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="K42">
+        <v>2029</v>
+      </c>
+      <c r="L42" s="4">
+        <v>4.155092592592593E-3</v>
+      </c>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="6">
+        <v>4.155092592592593E-3</v>
+      </c>
+      <c r="Q42" s="8"/>
+      <c r="R42" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="S42">
+        <v>2029</v>
+      </c>
+      <c r="T42" s="4">
+        <v>9.2013888888888892E-3</v>
+      </c>
+      <c r="U42" s="5"/>
+      <c r="V42" s="5"/>
+      <c r="W42" s="5"/>
+      <c r="X42" s="6">
+        <v>9.2013888888888892E-3</v>
+      </c>
+      <c r="Y42" s="8"/>
+      <c r="Z42" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA42">
+        <v>2029</v>
+      </c>
+      <c r="AB42" s="4">
+        <v>1.6469907407407405E-2</v>
+      </c>
+      <c r="AC42" s="5"/>
+      <c r="AD42" s="5"/>
+      <c r="AE42" s="5"/>
+      <c r="AF42" s="6">
+        <v>1.6469907407407405E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:32">
+      <c r="A43" s="8"/>
+      <c r="B43" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43">
+        <v>2029</v>
+      </c>
+      <c r="D43" s="4">
+        <v>1.8634259259259261E-3</v>
+      </c>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="6">
+        <v>1.8634259259259261E-3</v>
+      </c>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="K43">
+        <v>2028</v>
+      </c>
+      <c r="L43" s="4">
+        <v>4.2129629629629626E-3</v>
+      </c>
+      <c r="M43" s="5">
+        <v>3.9699074074074072E-3</v>
+      </c>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="6">
+        <v>3.9699074074074072E-3</v>
+      </c>
+      <c r="Q43" s="8"/>
+      <c r="R43" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="S43">
+        <v>2026</v>
+      </c>
+      <c r="T43" s="4">
+        <v>9.2129629629629627E-3</v>
+      </c>
+      <c r="U43" s="5">
+        <v>8.3217592592592596E-3</v>
+      </c>
+      <c r="V43" s="5">
+        <v>7.8935185185185185E-3</v>
+      </c>
+      <c r="W43" s="5">
+        <v>7.8125E-3</v>
+      </c>
+      <c r="X43" s="6">
+        <v>7.8125E-3</v>
+      </c>
+      <c r="Y43" s="8"/>
+      <c r="Z43" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA43">
+        <v>2027</v>
+      </c>
+      <c r="AB43" s="4">
+        <v>1.6840277777777777E-2</v>
+      </c>
+      <c r="AC43" s="5">
+        <v>1.238425925925926E-2</v>
+      </c>
+      <c r="AD43" s="5">
+        <v>1.3541666666666667E-2</v>
+      </c>
+      <c r="AE43" s="5"/>
+      <c r="AF43" s="6">
+        <v>1.238425925925926E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:32">
+      <c r="A44" s="8"/>
+      <c r="B44" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44">
+        <v>2026</v>
+      </c>
+      <c r="D44" s="4">
+        <v>1.8750000000000001E-3</v>
+      </c>
+      <c r="E44" s="5">
+        <v>1.7245370370370372E-3</v>
+      </c>
+      <c r="F44" s="5">
+        <v>1.6782407407407406E-3</v>
+      </c>
+      <c r="G44" s="5">
+        <v>1.6435185185185183E-3</v>
+      </c>
+      <c r="H44" s="6">
+        <v>1.6435185185185183E-3</v>
+      </c>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K44">
+        <v>2026</v>
+      </c>
+      <c r="L44" s="4">
+        <v>4.2824074074074075E-3</v>
+      </c>
+      <c r="M44" s="5">
+        <v>3.9120370370370368E-3</v>
+      </c>
+      <c r="N44" s="5">
+        <v>3.6805555555555554E-3</v>
+      </c>
+      <c r="O44" s="5">
+        <v>3.5879629629629629E-3</v>
+      </c>
+      <c r="P44" s="6">
+        <v>3.5879629629629629E-3</v>
+      </c>
+      <c r="Q44" s="8"/>
+      <c r="R44" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="S44">
+        <v>2029</v>
+      </c>
+      <c r="T44" s="4">
+        <v>9.386574074074075E-3</v>
+      </c>
+      <c r="U44" s="5"/>
+      <c r="V44" s="5"/>
+      <c r="W44" s="5"/>
+      <c r="X44" s="6">
+        <v>9.386574074074075E-3</v>
+      </c>
+      <c r="Y44" s="8"/>
+      <c r="Z44" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA44">
+        <v>2028</v>
+      </c>
+      <c r="AB44" s="4">
+        <v>1.6944444444444443E-2</v>
+      </c>
+      <c r="AC44" s="5">
+        <v>1.4432870370370372E-2</v>
+      </c>
+      <c r="AD44" s="5"/>
+      <c r="AE44" s="5"/>
+      <c r="AF44" s="6">
+        <v>1.4432870370370372E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:32">
+      <c r="A45" s="8"/>
+      <c r="B45" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C45">
+        <v>2029</v>
+      </c>
+      <c r="D45" s="4">
+        <v>1.8865740740740742E-3</v>
+      </c>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="6">
+        <v>1.8865740740740742E-3</v>
+      </c>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K45">
+        <v>2027</v>
+      </c>
+      <c r="L45" s="4">
+        <v>4.2939814814814811E-3</v>
+      </c>
+      <c r="M45" s="5">
+        <v>4.5023148148148149E-3</v>
+      </c>
+      <c r="N45" s="5">
+        <v>3.8310185185185183E-3</v>
+      </c>
+      <c r="O45" s="5"/>
+      <c r="P45" s="6">
+        <v>3.8310185185185183E-3</v>
+      </c>
+      <c r="Q45" s="8"/>
+      <c r="R45" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="S45">
+        <v>2027</v>
+      </c>
+      <c r="T45" s="4">
+        <v>1.074074074074074E-2</v>
+      </c>
+      <c r="U45" s="5">
+        <v>9.2129629629629627E-3</v>
+      </c>
+      <c r="V45" s="5"/>
+      <c r="W45" s="5"/>
+      <c r="X45" s="6">
+        <v>9.2129629629629627E-3</v>
+      </c>
+      <c r="Y45" s="8"/>
+      <c r="Z45" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA45">
+        <v>2027</v>
+      </c>
+      <c r="AB45" s="4">
+        <v>1.8564814814814815E-2</v>
+      </c>
+      <c r="AC45" s="5">
+        <v>1.6168981481481482E-2</v>
+      </c>
+      <c r="AD45" s="5">
+        <v>1.5231481481481483E-2</v>
+      </c>
+      <c r="AE45" s="5"/>
+      <c r="AF45" s="6">
+        <v>1.5231481481481483E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:32">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46">
+        <v>2027</v>
+      </c>
+      <c r="D46" s="4">
+        <v>2.0023148148148148E-3</v>
+      </c>
+      <c r="E46" s="5">
+        <v>2.0138888888888888E-3</v>
+      </c>
+      <c r="F46" s="5">
+        <v>1.7245370370370372E-3</v>
+      </c>
+      <c r="G46" s="5"/>
+      <c r="H46" s="6">
+        <v>1.7245370370370372E-3</v>
+      </c>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="K46">
+        <v>2027</v>
+      </c>
+      <c r="L46" s="4">
+        <v>4.340277777777778E-3</v>
+      </c>
+      <c r="M46" s="5">
+        <v>3.7731481481481483E-3</v>
+      </c>
+      <c r="N46" s="5">
+        <v>3.4490740740740745E-3</v>
+      </c>
+      <c r="O46" s="5"/>
+      <c r="P46" s="6">
+        <v>3.4490740740740745E-3</v>
+      </c>
+      <c r="Q46" s="8"/>
+      <c r="R46" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="S46">
+        <v>2027</v>
+      </c>
+      <c r="T46" s="4">
+        <v>1.1400462962962965E-2</v>
+      </c>
+      <c r="U46" s="5"/>
+      <c r="V46" s="5"/>
+      <c r="W46" s="5"/>
+      <c r="X46" s="6">
+        <v>1.1400462962962965E-2</v>
+      </c>
+      <c r="Y46" s="8"/>
+      <c r="Z46" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA46">
+        <v>2026</v>
+      </c>
+      <c r="AB46" s="4"/>
+      <c r="AC46" s="5"/>
+      <c r="AD46" s="5"/>
+      <c r="AE46" s="5">
+        <v>1.136574074074074E-2</v>
+      </c>
+      <c r="AF46" s="6">
+        <v>1.136574074074074E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:32">
+      <c r="A47" s="8"/>
+      <c r="B47" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47">
+        <v>2027</v>
+      </c>
+      <c r="D47" s="4">
+        <v>2.0601851851851853E-3</v>
+      </c>
+      <c r="E47" s="5">
+        <v>1.9212962962962962E-3</v>
+      </c>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="6">
+        <v>1.9212962962962962E-3</v>
+      </c>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="K47">
+        <v>2028</v>
+      </c>
+      <c r="L47" s="4">
+        <v>4.3518518518518515E-3</v>
+      </c>
+      <c r="M47" s="5">
+        <v>4.409722222222222E-3</v>
+      </c>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="6">
+        <v>4.3518518518518515E-3</v>
+      </c>
+      <c r="Q47" s="8"/>
+      <c r="R47" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="S47">
+        <v>2027</v>
+      </c>
+      <c r="T47" s="4"/>
+      <c r="U47" s="5"/>
+      <c r="V47" s="5">
+        <v>8.6342592592592599E-3</v>
+      </c>
+      <c r="W47" s="5"/>
+      <c r="X47" s="6">
+        <v>8.6342592592592599E-3</v>
+      </c>
+      <c r="Y47" s="8"/>
+      <c r="Z47" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA47">
+        <v>2027</v>
+      </c>
+      <c r="AB47" s="4"/>
+      <c r="AC47" s="5">
+        <v>1.4733796296296295E-2</v>
+      </c>
+      <c r="AD47" s="5">
+        <v>1.4004629629629631E-2</v>
+      </c>
+      <c r="AE47" s="5"/>
+      <c r="AF47" s="6">
+        <v>1.4004629629629631E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:32">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C48">
+        <v>2027</v>
+      </c>
+      <c r="D48" s="4">
+        <v>2.2916666666666667E-3</v>
+      </c>
+      <c r="E48" s="5">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="6">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="I48" s="8"/>
+      <c r="J48" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K48">
+        <v>2027</v>
+      </c>
+      <c r="L48" s="4">
+        <v>4.5370370370370365E-3</v>
+      </c>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="6">
+        <v>4.5370370370370365E-3</v>
+      </c>
+      <c r="Q48" s="8"/>
+      <c r="R48" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="S48">
+        <v>2028</v>
+      </c>
+      <c r="T48" s="4"/>
+      <c r="U48" s="5">
+        <v>8.4375000000000006E-3</v>
+      </c>
+      <c r="V48" s="5"/>
+      <c r="W48" s="5"/>
+      <c r="X48" s="6">
+        <v>8.4375000000000006E-3</v>
+      </c>
+      <c r="Y48" s="8"/>
+      <c r="Z48" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA48">
+        <v>2027</v>
+      </c>
+      <c r="AB48" s="4"/>
+      <c r="AC48" s="5"/>
+      <c r="AD48" s="5">
+        <v>1.4687499999999999E-2</v>
+      </c>
+      <c r="AE48" s="5"/>
+      <c r="AF48" s="6">
+        <v>1.4687499999999999E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:32">
+      <c r="A49" s="8"/>
+      <c r="B49" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49">
+        <v>2027</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="5">
+        <v>2.0138888888888888E-3</v>
+      </c>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="6">
+        <v>2.0138888888888888E-3</v>
+      </c>
+      <c r="I49" s="8"/>
+      <c r="J49" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="K49">
+        <v>2027</v>
+      </c>
+      <c r="L49" s="4">
+        <v>4.8611111111111112E-3</v>
+      </c>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="6">
+        <v>4.8611111111111112E-3</v>
+      </c>
+      <c r="Q49" s="9"/>
+      <c r="R49" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="S49">
+        <v>2026</v>
+      </c>
+      <c r="T49" s="4"/>
+      <c r="U49" s="5"/>
+      <c r="V49" s="5">
+        <v>7.8935185185185185E-3</v>
+      </c>
+      <c r="W49" s="5">
+        <v>8.0555555555555554E-3</v>
+      </c>
+      <c r="X49" s="6">
+        <v>7.8935185185185185E-3</v>
+      </c>
+      <c r="Y49" s="8"/>
+      <c r="Z49" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA49">
+        <v>2026</v>
+      </c>
+      <c r="AB49" s="4"/>
+      <c r="AC49" s="5"/>
+      <c r="AD49" s="5">
+        <v>1.2905092592592591E-2</v>
+      </c>
+      <c r="AE49" s="5"/>
+      <c r="AF49" s="6">
+        <v>1.2905092592592591E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:32">
+      <c r="A50" s="8"/>
+      <c r="B50" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C50">
+        <v>2026</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5">
+        <v>1.4699074074074074E-3</v>
+      </c>
+      <c r="G50" s="5">
+        <v>1.423611111111111E-3</v>
+      </c>
+      <c r="H50" s="6">
+        <v>1.423611111111111E-3</v>
+      </c>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K50">
+        <v>2027</v>
+      </c>
+      <c r="L50" s="4">
+        <v>5.5208333333333333E-3</v>
+      </c>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="6">
+        <v>5.5208333333333333E-3</v>
+      </c>
+      <c r="Y50" s="9"/>
+      <c r="Z50" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA50">
+        <v>2026</v>
+      </c>
+      <c r="AB50" s="4"/>
+      <c r="AC50" s="5">
+        <v>1.4282407407407409E-2</v>
+      </c>
+      <c r="AD50" s="5">
+        <v>1.3680555555555555E-2</v>
+      </c>
+      <c r="AE50" s="5"/>
+      <c r="AF50" s="6">
+        <v>1.3680555555555555E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:32">
+      <c r="A51" s="8"/>
+      <c r="B51" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C51">
+        <v>2027</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="5">
+        <v>1.7013888888888892E-3</v>
+      </c>
+      <c r="F51" s="5">
+        <v>1.8287037037037037E-3</v>
+      </c>
+      <c r="G51" s="5"/>
+      <c r="H51" s="6">
+        <v>1.7013888888888892E-3</v>
+      </c>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="K51">
+        <v>2026</v>
+      </c>
+      <c r="L51" s="4"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5">
+        <v>3.5185185185185185E-3</v>
+      </c>
+      <c r="O51" s="5">
+        <v>3.3680555555555551E-3</v>
+      </c>
+      <c r="P51" s="6">
+        <v>3.3680555555555551E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:32">
+      <c r="A52" s="8"/>
+      <c r="B52" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C52">
+        <v>2026</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="5">
+        <v>1.4467592592592594E-3</v>
+      </c>
+      <c r="F52" s="5">
+        <v>1.3657407407407409E-3</v>
+      </c>
+      <c r="G52" s="5">
+        <v>1.3773148148148147E-3</v>
+      </c>
+      <c r="H52" s="6">
+        <v>1.3657407407407409E-3</v>
+      </c>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K52">
+        <v>2027</v>
+      </c>
+      <c r="L52" s="4"/>
+      <c r="M52" s="5">
+        <v>3.7500000000000003E-3</v>
+      </c>
+      <c r="N52" s="5">
+        <v>3.9004629629629632E-3</v>
+      </c>
+      <c r="O52" s="5"/>
+      <c r="P52" s="6">
+        <v>3.7500000000000003E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:32">
+      <c r="A53" s="9"/>
+      <c r="B53" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53">
+        <v>2028</v>
+      </c>
+      <c r="D53" s="4"/>
+      <c r="E53" s="5">
+        <v>1.689814814814815E-3</v>
+      </c>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="6">
+        <v>1.689814814814815E-3</v>
+      </c>
+      <c r="I53" s="9"/>
+      <c r="J53" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="K53">
+        <v>2026</v>
+      </c>
+      <c r="L53" s="4"/>
+      <c r="M53" s="5">
+        <v>3.3449074074074071E-3</v>
+      </c>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="6">
+        <v>3.3449074074074071E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="K2:K53">
+    <cfRule type="cellIs" dxfId="15" priority="13" operator="equal">
+      <formula>2029</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="14" operator="equal">
+      <formula>2028</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
+      <formula>2027</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="16" stopIfTrue="1" operator="equal">
+      <formula>2026</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S49">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
+      <formula>2029</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
+      <formula>2028</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+      <formula>2027</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="12" stopIfTrue="1" operator="equal">
+      <formula>2026</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C53">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+      <formula>2029</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+      <formula>2028</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+      <formula>2027</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="8" stopIfTrue="1" operator="equal">
+      <formula>2026</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA50">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>2029</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>2028</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>2027</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="4" stopIfTrue="1" operator="equal">
+      <formula>2026</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>